--- a/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
+++ b/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9115\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D039CD5-7FD4-4E8D-843F-DF1C916ED276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214E761F-26BC-473C-B37D-922F60803EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="182">
   <si>
     <t xml:space="preserve">Banco Comafi:
 Cons. Prop. Edif. Yrigoyen 9115 CUIT: 30-56975974-5
@@ -532,52 +532,49 @@
     <t>Macarena perez ruiz</t>
   </si>
   <si>
-    <t>VTO: 14/07</t>
-  </si>
-  <si>
-    <t>PERIODO: JUNIO</t>
-  </si>
-  <si>
-    <t>MES DE JUNIO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Servisur 12/06 - Reconeccion circuito pulsadores y reemplazo de 6 de los mismos </t>
   </si>
   <si>
-    <t>Fumigacion Lanus 09/06</t>
-  </si>
-  <si>
     <t>Debito 09/06</t>
   </si>
   <si>
     <t>Debito 13/06</t>
   </si>
   <si>
-    <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable -  cuota 2 de 4</t>
-  </si>
-  <si>
     <t>Casa monini - Compra de pulsadores y compra de teclas de luz</t>
   </si>
   <si>
-    <t>Antonio Santillan - Gasista matriculado - Transferencia 02/06 y 05/06 - Arreglo perdida de gas 9A</t>
-  </si>
-  <si>
-    <t>Imputacion de gasto incorrecta - Mes anterior - Destapacion Italoamericana - Mantenimiento de cañerias, repaso de camaras de cloacas, salida colectora AYSA</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza - Transf 11/06</t>
-  </si>
-  <si>
     <t>Sueldo encargada - Jimena Borges y SAC</t>
   </si>
   <si>
     <t>Servisur 27/05 - Reemplazo de tres lamparas en pasillos y en el 10A - Material y mano de obra</t>
   </si>
   <si>
-    <t xml:space="preserve">Urbeco - Cambio de tapa y marco de tanques cisternas de vombeo </t>
-  </si>
-  <si>
     <t>macarena en febrero no le contamos un pago de 109277 , por lo que viene arrastrando una deuda inexistente, hay que corregirlo</t>
+  </si>
+  <si>
+    <t>VTO: 14/08</t>
+  </si>
+  <si>
+    <t>PERIODO: JULIO</t>
+  </si>
+  <si>
+    <t>MES DE JULIO</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Transf 17/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romanatti Carlos - Escribano - Certificacion 1 firma </t>
+  </si>
+  <si>
+    <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable -  cuota 3 de 4</t>
+  </si>
+  <si>
+    <t>Fumigacion Lanus 12/07</t>
+  </si>
+  <si>
+    <t>Examen medico</t>
   </si>
 </sst>
 </file>
@@ -585,14 +582,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -1408,10 +1405,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1431,7 +1428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1440,11 +1437,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1457,7 +1454,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1469,7 +1466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1477,15 +1474,15 @@
     <xf numFmtId="10" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1516,7 +1513,7 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1526,17 +1523,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1552,28 +1549,28 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="26" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1584,48 +1581,48 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1638,31 +1635,31 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="32" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1670,7 +1667,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1690,35 +1687,118 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1750,10 +1830,10 @@
     <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1789,12 +1869,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1813,83 +1887,8 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2307,26 +2306,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="70" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="70" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="70" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="70" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="70" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="70" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="70" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="70" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="70" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" style="70" customWidth="1"/>
     <col min="11" max="11" width="9" style="70" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2335,13 +2334,13 @@
       <c r="F1" s="4"/>
       <c r="G1" s="3" t="str">
         <f>Gastos!C8</f>
-        <v>PERIODO: JUNIO</v>
+        <v>PERIODO: JULIO</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="str">
         <f>Gastos!G8</f>
-        <v>VTO: 14/07</v>
+        <v>VTO: 14/08</v>
       </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2349,7 +2348,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -2366,7 +2365,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12">
@@ -2374,20 +2373,20 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="170" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="172"/>
+      <c r="F3" s="172" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="174"/>
       <c r="K3" s="147"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -2395,40 +2394,40 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="145"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="175"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="176"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="177"/>
       <c r="K4" s="147"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15"/>
-      <c r="B5" s="179">
+      <c r="B5" s="181">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="179"/>
+      <c r="C5" s="181"/>
       <c r="D5" s="16"/>
       <c r="E5" s="146">
         <v>0</v>
       </c>
-      <c r="F5" s="173"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="175"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="177"/>
       <c r="K5" s="148"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15"/>
       <c r="B6" s="17" t="s">
         <v>2</v>
@@ -2436,24 +2435,24 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="145"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="179"/>
+      <c r="H6" s="179"/>
+      <c r="I6" s="179"/>
+      <c r="J6" s="180"/>
       <c r="K6" s="148"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
-      <c r="B7" s="179">
+      <c r="B7" s="181">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="179"/>
+      <c r="C7" s="181"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -2467,7 +2466,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>3</v>
       </c>
@@ -2514,7 +2513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>1</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>550800</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2</v>
       </c>
@@ -2616,7 +2615,7 @@
         <v>146880</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>3</v>
       </c>
@@ -2666,7 +2665,7 @@
         <v>130507.3074845599</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>4</v>
       </c>
@@ -2718,7 +2717,7 @@
       </c>
       <c r="P12" s="38"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>5</v>
       </c>
@@ -2771,7 +2770,7 @@
         <v>88230</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>6</v>
       </c>
@@ -2821,7 +2820,7 @@
         <v>142154.26324766575</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>7</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>8</v>
       </c>
@@ -2925,7 +2924,7 @@
         <v>109649.99999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>9</v>
       </c>
@@ -2977,7 +2976,7 @@
         <v>267258.6557100396</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>10</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>11</v>
       </c>
@@ -3083,7 +3082,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>12</v>
       </c>
@@ -3133,7 +3132,7 @@
         <v>189846.22250868671</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>13</v>
       </c>
@@ -3186,7 +3185,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>14</v>
       </c>
@@ -3237,7 +3236,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>15</v>
       </c>
@@ -3290,7 +3289,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>16</v>
       </c>
@@ -3342,7 +3341,7 @@
         <v>238407.18050032918</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="36">
         <v>17</v>
       </c>
@@ -3393,7 +3392,7 @@
         <v>126989.77062953995</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>18</v>
       </c>
@@ -3444,7 +3443,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>19</v>
       </c>
@@ -3495,7 +3494,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>20</v>
       </c>
@@ -3543,7 +3542,7 @@
         <v>252361.89852420762</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>21</v>
       </c>
@@ -3596,7 +3595,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>22</v>
       </c>
@@ -3649,7 +3648,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>23</v>
       </c>
@@ -3697,7 +3696,7 @@
         <v>537341.03369272652</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>24</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>686031.04451645561</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <f>A32+1</f>
         <v>25</v>
@@ -3800,7 +3799,7 @@
         <v>137983.29341615291</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <f t="shared" ref="A34:A42" si="8">A33+1</f>
         <v>26</v>
@@ -3854,7 +3853,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -3907,7 +3906,7 @@
       </c>
       <c r="P35" s="87"/>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -3961,7 +3960,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -4015,7 +4014,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -4035,7 +4034,7 @@
       <c r="F38" s="18">
         <v>344673.7297766995</v>
       </c>
-      <c r="G38" s="236">
+      <c r="G38" s="170">
         <v>107500</v>
       </c>
       <c r="H38" s="32">
@@ -4068,7 +4067,7 @@
         <v>358824.72050340049</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <f t="shared" si="8"/>
         <v>31</v>
@@ -4122,7 +4121,7 @@
         <v>69360</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -4174,7 +4173,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <f t="shared" si="8"/>
         <v>33</v>
@@ -4228,7 +4227,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="57">
         <f t="shared" si="8"/>
         <v>34</v>
@@ -4282,7 +4281,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="62"/>
       <c r="B43" s="62"/>
       <c r="C43" s="63"/>
@@ -4330,9 +4329,9 @@
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G45" s="237" t="s">
-        <v>182</v>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G45" s="171" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -4350,20 +4349,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="25.44140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -4373,27 +4372,27 @@
       <c r="G1" s="72"/>
       <c r="H1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="38"/>
-      <c r="D2" s="222"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="224"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D2" s="193"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="194"/>
+      <c r="G2" s="194"/>
+      <c r="H2" s="195"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="225" t="s">
+      <c r="E3" s="196" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="225"/>
-      <c r="G3" s="225"/>
-      <c r="H3" s="226"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="197"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="38"/>
       <c r="D4" s="74" t="s">
         <v>90</v>
@@ -4403,7 +4402,7 @@
       </c>
       <c r="H4" s="76"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="38"/>
       <c r="D5" s="74" t="s">
         <v>92</v>
@@ -4413,7 +4412,7 @@
       </c>
       <c r="H5" s="76"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="38"/>
       <c r="D6" s="74" t="s">
         <v>93</v>
@@ -4423,30 +4422,30 @@
       </c>
       <c r="H6" s="76"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="38"/>
       <c r="D7" s="74" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="76"/>
     </row>
-    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="78" t="s">
         <v>96</v>
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H8" s="81"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>97</v>
       </c>
@@ -4458,19 +4457,19 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="227" t="s">
+    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="198" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="228"/>
-      <c r="C10" s="228"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="228"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="228"/>
-      <c r="H10" s="229"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="199"/>
+      <c r="E10" s="199"/>
+      <c r="F10" s="199"/>
+      <c r="G10" s="199"/>
+      <c r="H10" s="200"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="14"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4480,21 +4479,21 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="230" t="s">
+    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="201" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="230"/>
-      <c r="C12" s="230"/>
-      <c r="D12" s="230"/>
-      <c r="E12" s="230"/>
-      <c r="F12" s="230"/>
-      <c r="G12" s="230"/>
-      <c r="H12" s="230"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="201"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="201"/>
+      <c r="E12" s="201"/>
+      <c r="F12" s="201"/>
+      <c r="G12" s="201"/>
+      <c r="H12" s="201"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="153" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B13" s="154"/>
       <c r="C13" s="154"/>
@@ -4506,7 +4505,7 @@
         <v>1552501</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="153" t="s">
         <v>143</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="155" t="s">
         <v>101</v>
       </c>
@@ -4535,7 +4534,7 @@
         <v>-337668.97</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="156" t="s">
         <v>100</v>
       </c>
@@ -4551,19 +4550,19 @@
       </c>
       <c r="I16" s="83"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="231" t="s">
+    <row r="17" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="202" t="s">
         <v>164</v>
       </c>
-      <c r="B17" s="231"/>
-      <c r="C17" s="231"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="231"/>
-      <c r="G17" s="231"/>
-      <c r="H17" s="231"/>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="202"/>
+      <c r="C17" s="202"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="202"/>
+      <c r="G17" s="202"/>
+      <c r="H17" s="202"/>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="85" t="s">
         <v>160</v>
       </c>
@@ -4575,7 +4574,7 @@
       <c r="G18" s="154"/>
       <c r="H18" s="82"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="85" t="s">
         <v>159</v>
       </c>
@@ -4587,7 +4586,7 @@
       <c r="G19" s="154"/>
       <c r="H19" s="82"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="154"/>
       <c r="B20" s="154"/>
       <c r="C20" s="154"/>
@@ -4597,7 +4596,7 @@
       <c r="G20" s="154"/>
       <c r="H20" s="82"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="154" t="s">
         <v>102</v>
       </c>
@@ -4612,35 +4611,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="231" t="s">
+    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="202" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="231"/>
-      <c r="C22" s="231"/>
-      <c r="D22" s="231"/>
-      <c r="E22" s="231"/>
-      <c r="F22" s="231"/>
-      <c r="G22" s="231"/>
-      <c r="H22" s="231"/>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="202"/>
+      <c r="C22" s="202"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="202"/>
+      <c r="G22" s="202"/>
+      <c r="H22" s="202"/>
+    </row>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="153" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="158" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C23" s="158"/>
       <c r="D23" s="158"/>
       <c r="E23" s="158"/>
       <c r="F23" s="158"/>
       <c r="G23" s="154"/>
-      <c r="H23" s="82">
-        <v>94123.39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H23" s="238">
+        <v>137308.57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="153" t="s">
         <v>151</v>
       </c>
@@ -4653,11 +4652,11 @@
       <c r="E24" s="158"/>
       <c r="F24" s="158"/>
       <c r="G24" s="154"/>
-      <c r="H24" s="82">
-        <v>48546.96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H24" s="238">
+        <v>69862.55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="153" t="s">
         <v>105</v>
       </c>
@@ -4670,27 +4669,27 @@
       <c r="E25" s="158"/>
       <c r="F25" s="158"/>
       <c r="G25" s="154"/>
-      <c r="H25" s="82">
-        <v>5394.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H25" s="238">
+        <v>7762.51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="153" t="s">
         <v>157</v>
       </c>
       <c r="B26" s="154" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158"/>
       <c r="E26" s="158"/>
       <c r="F26" s="158"/>
       <c r="G26" s="154"/>
-      <c r="H26" s="82">
-        <v>496397.21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H26" s="238">
+        <v>714361.65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="153"/>
       <c r="B27" s="154"/>
       <c r="C27" s="158"/>
@@ -4702,7 +4701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="157" t="s">
         <v>106</v>
       </c>
@@ -4714,22 +4713,22 @@
       <c r="G28" s="157"/>
       <c r="H28" s="84">
         <f>SUM(H23:H27)</f>
-        <v>644461.67000000004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="221" t="s">
+        <v>929295.28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="192" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="221"/>
-      <c r="C29" s="221"/>
-      <c r="D29" s="221"/>
-      <c r="E29" s="221"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="221"/>
-      <c r="H29" s="221"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="192"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="192"/>
+      <c r="E29" s="192"/>
+      <c r="F29" s="192"/>
+      <c r="G29" s="192"/>
+      <c r="H29" s="192"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="154" t="s">
         <v>108</v>
       </c>
@@ -4739,11 +4738,11 @@
       <c r="E30" s="154"/>
       <c r="F30" s="154"/>
       <c r="G30" s="154"/>
-      <c r="H30" s="82">
-        <v>4128.4799999999996</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H30" s="238">
+        <v>200.93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="154" t="s">
         <v>109</v>
       </c>
@@ -4760,7 +4759,7 @@
       </c>
       <c r="I31" s="87"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="159" t="s">
         <v>111</v>
       </c>
@@ -4772,11 +4771,11 @@
       <c r="E32" s="154"/>
       <c r="F32" s="154"/>
       <c r="G32" s="154"/>
-      <c r="H32" s="82">
-        <v>189273</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H32" s="238">
+        <v>203720.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="157" t="s">
         <v>100</v>
       </c>
@@ -4788,22 +4787,22 @@
       <c r="G33" s="157"/>
       <c r="H33" s="160">
         <f>SUM(H30:H32)</f>
-        <v>1422418.64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="221" t="s">
+        <v>1432938.4899999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="192" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="221"/>
-      <c r="C34" s="221"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="221"/>
-      <c r="F34" s="221"/>
-      <c r="G34" s="221"/>
-      <c r="H34" s="221"/>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="192"/>
+      <c r="C34" s="192"/>
+      <c r="D34" s="192"/>
+      <c r="E34" s="192"/>
+      <c r="F34" s="192"/>
+      <c r="G34" s="192"/>
+      <c r="H34" s="192"/>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="85"/>
       <c r="B35" s="161"/>
       <c r="C35" s="154"/>
@@ -4813,7 +4812,7 @@
       <c r="G35" s="154"/>
       <c r="H35" s="82"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="85" t="s">
         <v>158</v>
       </c>
@@ -4823,13 +4822,13 @@
       <c r="E36" s="154"/>
       <c r="F36" s="154"/>
       <c r="G36" s="154"/>
-      <c r="H36" s="82">
+      <c r="H36" s="238">
         <v>140000</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="85" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B37" s="162"/>
       <c r="C37" s="85"/>
@@ -4837,28 +4836,28 @@
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="82">
+      <c r="H37" s="238">
         <v>40000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
-    <row r="38" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="180" t="s">
+    <row r="38" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="209" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="210"/>
+      <c r="C38" s="210"/>
+      <c r="D38" s="210"/>
+      <c r="E38" s="210"/>
+      <c r="F38" s="210"/>
+      <c r="G38" s="211"/>
+      <c r="H38" s="238">
+        <v>32240.45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="85" t="s">
         <v>177</v>
-      </c>
-      <c r="B38" s="181"/>
-      <c r="C38" s="181"/>
-      <c r="D38" s="181"/>
-      <c r="E38" s="181"/>
-      <c r="F38" s="181"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="82">
-        <v>-58000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="85" t="s">
-        <v>178</v>
       </c>
       <c r="B39" s="161"/>
       <c r="C39" s="154"/>
@@ -4866,32 +4865,29 @@
       <c r="E39" s="154"/>
       <c r="F39" s="154"/>
       <c r="G39" s="154"/>
-      <c r="H39" s="82">
-        <v>53150</v>
+      <c r="H39" s="238">
+        <v>101540</v>
       </c>
       <c r="I39" s="149"/>
-      <c r="J39" s="183"/>
-    </row>
-    <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="180" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40" s="181"/>
-      <c r="C40" s="181"/>
-      <c r="D40" s="181"/>
-      <c r="E40" s="181"/>
-      <c r="F40" s="181"/>
-      <c r="G40" s="182"/>
-      <c r="H40" s="82">
-        <f>500000+245000</f>
-        <v>745000</v>
-      </c>
-      <c r="J40" s="183"/>
-    </row>
-    <row r="41" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="96" t="s">
-        <v>181</v>
-      </c>
+      <c r="J39" s="212"/>
+    </row>
+    <row r="40" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="209" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="210"/>
+      <c r="C40" s="210"/>
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="210"/>
+      <c r="G40" s="211"/>
+      <c r="H40" s="238">
+        <v>741000</v>
+      </c>
+      <c r="J40" s="212"/>
+    </row>
+    <row r="41" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="96"/>
       <c r="B41" s="168"/>
       <c r="C41" s="168"/>
       <c r="D41" s="168"/>
@@ -4901,11 +4897,11 @@
       <c r="H41" s="82">
         <v>500000</v>
       </c>
-      <c r="J41" s="183"/>
-    </row>
-    <row r="42" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J41" s="212"/>
+    </row>
+    <row r="42" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="96" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B42" s="168"/>
       <c r="C42" s="168"/>
@@ -4913,14 +4909,14 @@
       <c r="E42" s="168"/>
       <c r="F42" s="168"/>
       <c r="G42" s="169"/>
-      <c r="H42" s="82">
-        <v>1200000</v>
-      </c>
-      <c r="J42" s="183"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H42" s="238">
+        <v>36300</v>
+      </c>
+      <c r="J42" s="212"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="85" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B43" s="161"/>
       <c r="C43" s="154"/>
@@ -4931,11 +4927,11 @@
       <c r="H43" s="82">
         <v>160000</v>
       </c>
-      <c r="J43" s="183"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="212"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="85" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B44" s="161"/>
       <c r="C44" s="154"/>
@@ -4948,9 +4944,9 @@
       </c>
       <c r="J44" s="167"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="85" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B45" s="161"/>
       <c r="C45" s="154"/>
@@ -4963,7 +4959,7 @@
       </c>
       <c r="I45" s="149"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="154" t="s">
         <v>100</v>
       </c>
@@ -4975,55 +4971,55 @@
       <c r="G46" s="154"/>
       <c r="H46" s="84">
         <f>SUM(H35:H45)</f>
-        <v>2994577.12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="221" t="s">
+        <v>1965507.5699999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="221"/>
-      <c r="C47" s="221"/>
-      <c r="D47" s="221"/>
-      <c r="E47" s="221"/>
-      <c r="F47" s="221"/>
-      <c r="G47" s="221"/>
-      <c r="H47" s="221"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="192"/>
+      <c r="C47" s="192"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
+      <c r="F47" s="192"/>
+      <c r="G47" s="192"/>
+      <c r="H47" s="192"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="154" t="s">
         <v>115</v>
       </c>
       <c r="B48" s="154"/>
       <c r="C48" s="154" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D48" s="163"/>
       <c r="E48" s="154"/>
       <c r="F48" s="154"/>
       <c r="G48" s="154"/>
-      <c r="H48" s="82">
+      <c r="H48" s="239">
         <v>250000</v>
       </c>
       <c r="J48" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="164" t="s">
         <v>147</v>
       </c>
       <c r="B49" s="154"/>
-      <c r="C49" s="201"/>
-      <c r="D49" s="202"/>
+      <c r="C49" s="230"/>
+      <c r="D49" s="231"/>
       <c r="E49" s="165"/>
       <c r="F49" s="158"/>
       <c r="G49" s="154"/>
-      <c r="H49" s="82">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H49" s="238">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="154"/>
       <c r="B50" s="154"/>
       <c r="C50" s="158"/>
@@ -5033,7 +5029,7 @@
       <c r="G50" s="154"/>
       <c r="H50" s="82"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="157" t="s">
         <v>100</v>
       </c>
@@ -5045,22 +5041,22 @@
       <c r="G51" s="157"/>
       <c r="H51" s="84">
         <f>SUM(H48:H50)</f>
-        <v>278000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="232" t="s">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="203" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="233"/>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="234"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B52" s="204"/>
+      <c r="C52" s="204"/>
+      <c r="D52" s="204"/>
+      <c r="E52" s="204"/>
+      <c r="F52" s="204"/>
+      <c r="G52" s="204"/>
+      <c r="H52" s="205"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="154" t="s">
         <v>117</v>
       </c>
@@ -5074,7 +5070,7 @@
         <v>89235.14</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="154"/>
       <c r="B54" s="154"/>
       <c r="C54" s="154"/>
@@ -5084,7 +5080,7 @@
       <c r="G54" s="154"/>
       <c r="H54" s="82"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="157" t="s">
         <v>106</v>
       </c>
@@ -5099,20 +5095,20 @@
         <v>89235.14</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="232" t="s">
+    <row r="56" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="203" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="233"/>
-      <c r="C56" s="233"/>
-      <c r="D56" s="233"/>
-      <c r="E56" s="233"/>
-      <c r="F56" s="233"/>
-      <c r="G56" s="233"/>
-      <c r="H56" s="234"/>
+      <c r="B56" s="204"/>
+      <c r="C56" s="204"/>
+      <c r="D56" s="204"/>
+      <c r="E56" s="204"/>
+      <c r="F56" s="204"/>
+      <c r="G56" s="204"/>
+      <c r="H56" s="205"/>
       <c r="I56" s="87"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="85" t="s">
         <v>140</v>
       </c>
@@ -5127,7 +5123,7 @@
       </c>
       <c r="I57" s="87"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="85" t="s">
         <v>141</v>
       </c>
@@ -5142,7 +5138,7 @@
       </c>
       <c r="I58" s="87"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="85" t="s">
         <v>100</v>
       </c>
@@ -5159,19 +5155,19 @@
       <c r="I59" s="87"/>
       <c r="K59" s="83"/>
     </row>
-    <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="203" t="s">
+    <row r="60" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="206" t="s">
         <v>119</v>
       </c>
-      <c r="B60" s="204"/>
-      <c r="C60" s="204"/>
-      <c r="D60" s="204"/>
-      <c r="E60" s="204"/>
-      <c r="F60" s="204"/>
-      <c r="G60" s="204"/>
-      <c r="H60" s="235"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="207"/>
+      <c r="C60" s="207"/>
+      <c r="D60" s="207"/>
+      <c r="E60" s="207"/>
+      <c r="F60" s="207"/>
+      <c r="G60" s="207"/>
+      <c r="H60" s="208"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="86"/>
       <c r="B61" s="86"/>
       <c r="C61" s="86"/>
@@ -5181,7 +5177,7 @@
       <c r="G61" s="86"/>
       <c r="H61" s="90"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="86"/>
       <c r="B62" s="86"/>
       <c r="C62" s="86"/>
@@ -5191,7 +5187,7 @@
       <c r="G62" s="86"/>
       <c r="H62" s="90"/>
     </row>
-    <row r="63" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A63" s="91" t="s">
         <v>100</v>
       </c>
@@ -5203,7 +5199,7 @@
       <c r="G63" s="89"/>
       <c r="H63" s="92"/>
     </row>
-    <row r="64" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="A64" s="93"/>
       <c r="B64" s="132"/>
       <c r="C64" s="132"/>
@@ -5213,7 +5209,7 @@
       <c r="G64" s="132"/>
       <c r="H64" s="94"/>
     </row>
-    <row r="65" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="91"/>
       <c r="B65" s="89"/>
       <c r="C65" s="89"/>
@@ -5223,19 +5219,19 @@
       <c r="G65" s="89"/>
       <c r="H65" s="92"/>
     </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="203" t="s">
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="206" t="s">
         <v>152</v>
       </c>
-      <c r="B66" s="204"/>
-      <c r="C66" s="204"/>
-      <c r="D66" s="204"/>
-      <c r="E66" s="204"/>
-      <c r="F66" s="204"/>
-      <c r="G66" s="204"/>
+      <c r="B66" s="207"/>
+      <c r="C66" s="207"/>
+      <c r="D66" s="207"/>
+      <c r="E66" s="207"/>
+      <c r="F66" s="207"/>
+      <c r="G66" s="207"/>
       <c r="H66" s="128"/>
     </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="91"/>
       <c r="B67" s="89"/>
       <c r="C67" s="89"/>
@@ -5245,7 +5241,7 @@
       <c r="G67" s="89"/>
       <c r="H67" s="92"/>
     </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="91"/>
       <c r="B68" s="89"/>
       <c r="C68" s="89"/>
@@ -5255,7 +5251,7 @@
       <c r="G68" s="89"/>
       <c r="H68" s="92"/>
     </row>
-    <row r="69" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="129" t="s">
         <v>100</v>
       </c>
@@ -5270,7 +5266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A70" s="91"/>
       <c r="B70" s="89"/>
       <c r="C70" s="89"/>
@@ -5280,29 +5276,29 @@
       <c r="G70" s="89"/>
       <c r="H70" s="92"/>
     </row>
-    <row r="71" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A71" s="195" t="s">
+    <row r="71" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A71" s="224" t="s">
         <v>120</v>
       </c>
-      <c r="B71" s="195"/>
-      <c r="C71" s="195"/>
-      <c r="D71" s="195"/>
-      <c r="E71" s="195"/>
-      <c r="F71" s="195"/>
-      <c r="G71" s="195"/>
+      <c r="B71" s="224"/>
+      <c r="C71" s="224"/>
+      <c r="D71" s="224"/>
+      <c r="E71" s="224"/>
+      <c r="F71" s="224"/>
+      <c r="G71" s="224"/>
       <c r="H71" s="95"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="180"/>
-      <c r="B72" s="181"/>
-      <c r="C72" s="181"/>
-      <c r="D72" s="181"/>
-      <c r="E72" s="181"/>
-      <c r="F72" s="181"/>
-      <c r="G72" s="182"/>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="209"/>
+      <c r="B72" s="210"/>
+      <c r="C72" s="210"/>
+      <c r="D72" s="210"/>
+      <c r="E72" s="210"/>
+      <c r="F72" s="210"/>
+      <c r="G72" s="211"/>
       <c r="H72" s="124"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="96"/>
       <c r="B73" s="97"/>
       <c r="C73" s="97"/>
@@ -5312,19 +5308,19 @@
       <c r="G73" s="98"/>
       <c r="H73" s="124"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="196"/>
-      <c r="B74" s="197"/>
-      <c r="C74" s="197"/>
-      <c r="D74" s="197"/>
-      <c r="E74" s="197"/>
-      <c r="F74" s="197"/>
-      <c r="G74" s="198"/>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="225"/>
+      <c r="B74" s="226"/>
+      <c r="C74" s="226"/>
+      <c r="D74" s="226"/>
+      <c r="E74" s="226"/>
+      <c r="F74" s="226"/>
+      <c r="G74" s="227"/>
       <c r="H74" s="82">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="133"/>
       <c r="B75" s="134"/>
       <c r="C75" s="134"/>
@@ -5336,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="133"/>
       <c r="B76" s="134"/>
       <c r="C76" s="134"/>
@@ -5348,7 +5344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="137" t="s">
         <v>100</v>
       </c>
@@ -5363,7 +5359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="138"/>
       <c r="B78" s="138"/>
       <c r="C78" s="138"/>
@@ -5374,128 +5370,128 @@
       <c r="H78" s="139"/>
       <c r="I78" s="87"/>
     </row>
-    <row r="79" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="199" t="s">
+    <row r="79" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="228" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="200"/>
-      <c r="C79" s="200"/>
-      <c r="D79" s="200"/>
-      <c r="E79" s="200"/>
-      <c r="F79" s="200"/>
-      <c r="G79" s="200"/>
+      <c r="B79" s="229"/>
+      <c r="C79" s="229"/>
+      <c r="D79" s="229"/>
+      <c r="E79" s="229"/>
+      <c r="F79" s="229"/>
+      <c r="G79" s="229"/>
       <c r="H79" s="140">
         <f>H77</f>
         <v>0</v>
       </c>
       <c r="I79" s="87"/>
     </row>
-    <row r="80" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="192" t="s">
+    <row r="80" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="221" t="s">
         <v>122</v>
       </c>
-      <c r="B80" s="193"/>
-      <c r="C80" s="193"/>
-      <c r="D80" s="193"/>
-      <c r="E80" s="193"/>
-      <c r="F80" s="193"/>
-      <c r="G80" s="194"/>
+      <c r="B80" s="222"/>
+      <c r="C80" s="222"/>
+      <c r="D80" s="222"/>
+      <c r="E80" s="222"/>
+      <c r="F80" s="222"/>
+      <c r="G80" s="223"/>
       <c r="H80" s="140"/>
       <c r="I80" s="88"/>
     </row>
-    <row r="81" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="205" t="s">
+    <row r="81" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="232" t="s">
         <v>142</v>
       </c>
-      <c r="B81" s="206"/>
-      <c r="C81" s="206"/>
-      <c r="D81" s="206"/>
-      <c r="E81" s="206"/>
-      <c r="F81" s="206"/>
-      <c r="G81" s="207"/>
+      <c r="B81" s="233"/>
+      <c r="C81" s="233"/>
+      <c r="D81" s="233"/>
+      <c r="E81" s="233"/>
+      <c r="F81" s="233"/>
+      <c r="G81" s="234"/>
       <c r="H81" s="140"/>
       <c r="I81" s="87"/>
       <c r="J81" s="83"/>
     </row>
-    <row r="82" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A82" s="199" t="s">
+    <row r="82" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A82" s="228" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="200"/>
-      <c r="C82" s="200"/>
-      <c r="D82" s="200"/>
-      <c r="E82" s="200"/>
-      <c r="F82" s="200"/>
-      <c r="G82" s="200"/>
+      <c r="B82" s="229"/>
+      <c r="C82" s="229"/>
+      <c r="D82" s="229"/>
+      <c r="E82" s="229"/>
+      <c r="F82" s="229"/>
+      <c r="G82" s="229"/>
       <c r="H82" s="140">
         <f>H63+H59+H55+H51+H46+H33+H16+H21+H28+H69</f>
-        <v>6696913.4500000002</v>
+        <v>5965197.3600000003</v>
       </c>
       <c r="I82" s="83"/>
     </row>
-    <row r="83" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A83" s="208" t="s">
+    <row r="83" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A83" s="235" t="s">
         <v>124</v>
       </c>
-      <c r="B83" s="209"/>
-      <c r="C83" s="209"/>
-      <c r="D83" s="209"/>
-      <c r="E83" s="209"/>
-      <c r="F83" s="209"/>
-      <c r="G83" s="210"/>
+      <c r="B83" s="236"/>
+      <c r="C83" s="236"/>
+      <c r="D83" s="236"/>
+      <c r="E83" s="236"/>
+      <c r="F83" s="236"/>
+      <c r="G83" s="237"/>
       <c r="H83" s="141">
         <f>H82+H80</f>
-        <v>6696913.4500000002</v>
+        <v>5965197.3600000003</v>
       </c>
       <c r="I83" s="83"/>
       <c r="K83" s="149"/>
     </row>
-    <row r="84" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A84" s="208" t="s">
+    <row r="84" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A84" s="235" t="s">
         <v>125</v>
       </c>
-      <c r="B84" s="209"/>
-      <c r="C84" s="209"/>
-      <c r="D84" s="209"/>
-      <c r="E84" s="209"/>
-      <c r="F84" s="209"/>
-      <c r="G84" s="210"/>
+      <c r="B84" s="236"/>
+      <c r="C84" s="236"/>
+      <c r="D84" s="236"/>
+      <c r="E84" s="236"/>
+      <c r="F84" s="236"/>
+      <c r="G84" s="237"/>
       <c r="H84" s="142">
         <f>H79+H81</f>
         <v>0</v>
       </c>
       <c r="I84" s="83"/>
     </row>
-    <row r="85" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="211" t="s">
+    <row r="85" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="182" t="s">
         <v>126</v>
       </c>
-      <c r="B85" s="212"/>
-      <c r="C85" s="212"/>
-      <c r="D85" s="212"/>
-      <c r="E85" s="212"/>
-      <c r="F85" s="212"/>
-      <c r="G85" s="212"/>
+      <c r="B85" s="183"/>
+      <c r="C85" s="183"/>
+      <c r="D85" s="183"/>
+      <c r="E85" s="183"/>
+      <c r="F85" s="183"/>
+      <c r="G85" s="183"/>
       <c r="H85" s="143">
         <f>H82+H79</f>
-        <v>6696913.4500000002</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="213" t="s">
+        <v>5965197.3600000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="184" t="s">
         <v>127</v>
       </c>
-      <c r="B86" s="214"/>
-      <c r="C86" s="214"/>
-      <c r="D86" s="214"/>
-      <c r="E86" s="214"/>
-      <c r="F86" s="214"/>
-      <c r="G86" s="214"/>
+      <c r="B86" s="185"/>
+      <c r="C86" s="185"/>
+      <c r="D86" s="185"/>
+      <c r="E86" s="185"/>
+      <c r="F86" s="185"/>
+      <c r="G86" s="185"/>
       <c r="H86" s="100">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="101"/>
       <c r="B87" s="101"/>
       <c r="C87" s="101"/>
@@ -5505,29 +5501,29 @@
       <c r="G87" s="101"/>
       <c r="H87" s="102"/>
     </row>
-    <row r="88" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="215" t="s">
+    <row r="88" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="186" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="216"/>
-      <c r="C88" s="216"/>
-      <c r="D88" s="216"/>
-      <c r="E88" s="216"/>
-      <c r="F88" s="216"/>
-      <c r="G88" s="216"/>
-      <c r="H88" s="217"/>
-    </row>
-    <row r="89" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="218"/>
-      <c r="B89" s="219"/>
-      <c r="C89" s="219"/>
-      <c r="D89" s="219"/>
-      <c r="E89" s="219"/>
-      <c r="F89" s="219"/>
-      <c r="G89" s="219"/>
-      <c r="H89" s="220"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B88" s="187"/>
+      <c r="C88" s="187"/>
+      <c r="D88" s="187"/>
+      <c r="E88" s="187"/>
+      <c r="F88" s="187"/>
+      <c r="G88" s="187"/>
+      <c r="H88" s="188"/>
+    </row>
+    <row r="89" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="189"/>
+      <c r="B89" s="190"/>
+      <c r="C89" s="190"/>
+      <c r="D89" s="190"/>
+      <c r="E89" s="190"/>
+      <c r="F89" s="190"/>
+      <c r="G89" s="190"/>
+      <c r="H89" s="191"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -5537,19 +5533,19 @@
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
     </row>
-    <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A91" s="184" t="s">
+    <row r="91" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A91" s="213" t="s">
         <v>128</v>
       </c>
-      <c r="B91" s="185"/>
-      <c r="C91" s="185"/>
-      <c r="D91" s="185"/>
-      <c r="E91" s="185"/>
-      <c r="F91" s="185"/>
-      <c r="G91" s="185"/>
-      <c r="H91" s="186"/>
-    </row>
-    <row r="92" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B91" s="214"/>
+      <c r="C91" s="214"/>
+      <c r="D91" s="214"/>
+      <c r="E91" s="214"/>
+      <c r="F91" s="214"/>
+      <c r="G91" s="214"/>
+      <c r="H91" s="215"/>
+    </row>
+    <row r="92" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A92" s="103" t="s">
         <v>129</v>
       </c>
@@ -5563,7 +5559,7 @@
         <v>1280791.0346397704</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="8" t="s">
         <v>130</v>
       </c>
@@ -5578,7 +5574,7 @@
         <v>4581518.1130966982</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="107" t="s">
         <v>136</v>
       </c>
@@ -5590,10 +5586,10 @@
       <c r="G94" s="108"/>
       <c r="H94" s="123">
         <f>-H85</f>
-        <v>-6696913.4500000002</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+        <v>-5965197.3600000003</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="107" t="s">
         <v>131</v>
       </c>
@@ -5608,7 +5604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="107" t="s">
         <v>153</v>
       </c>
@@ -5623,7 +5619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A97" s="110" t="s">
         <v>132</v>
       </c>
@@ -5635,23 +5631,23 @@
       <c r="G97" s="111"/>
       <c r="H97" s="112">
         <f>SUM(H92:H96)</f>
-        <v>-834604.30226353183</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="99" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="187" t="s">
+        <v>-102888.21226353198</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="99" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="216" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="188"/>
-      <c r="C99" s="188"/>
-      <c r="D99" s="188"/>
-      <c r="E99" s="188"/>
-      <c r="F99" s="188"/>
-      <c r="G99" s="188"/>
-      <c r="H99" s="189"/>
-    </row>
-    <row r="100" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="217"/>
+      <c r="C99" s="217"/>
+      <c r="D99" s="217"/>
+      <c r="E99" s="217"/>
+      <c r="F99" s="217"/>
+      <c r="G99" s="217"/>
+      <c r="H99" s="218"/>
+    </row>
+    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="113" t="s">
         <v>129</v>
       </c>
@@ -5665,7 +5661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="115"/>
       <c r="C101" s="108"/>
@@ -5675,7 +5671,7 @@
       <c r="G101" s="6"/>
       <c r="H101" s="18"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="116"/>
       <c r="C102" s="6"/>
@@ -5685,7 +5681,7 @@
       <c r="G102" s="6"/>
       <c r="H102" s="18"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -5695,7 +5691,7 @@
       <c r="G103" s="6"/>
       <c r="H103" s="18"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="117" t="s">
         <v>132</v>
       </c>
@@ -5709,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="125" t="s">
         <v>145</v>
       </c>
@@ -5717,19 +5713,19 @@
       <c r="C106" s="126"/>
       <c r="D106" s="126"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
       <c r="D107" s="18"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
       <c r="D108" s="18"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="119" t="s">
         <v>100</v>
       </c>
@@ -5740,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="125" t="s">
         <v>146</v>
       </c>
@@ -5748,43 +5744,59 @@
       <c r="C111" s="119"/>
       <c r="D111" s="119"/>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="99"/>
       <c r="C112" s="99"/>
       <c r="D112" s="121"/>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
       <c r="D113" s="127"/>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
       <c r="D114" s="127"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
       <c r="D115" s="127"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="120" t="s">
         <v>100</v>
       </c>
       <c r="B116" s="120"/>
-      <c r="C116" s="190">
+      <c r="C116" s="219">
         <f>SUM(D112:D115)</f>
         <v>0</v>
       </c>
-      <c r="D116" s="191"/>
+      <c r="D116" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A85:G85"/>
     <mergeCell ref="A86:G86"/>
     <mergeCell ref="A88:H89"/>
@@ -5801,22 +5813,6 @@
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A84:G84"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
+++ b/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9115\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214E761F-26BC-473C-B37D-922F60803EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3E4C24-C17A-454C-8D07-124B384FBBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
     <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$118</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$114</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="179">
   <si>
     <t xml:space="preserve">Banco Comafi:
 Cons. Prop. Edif. Yrigoyen 9115 CUIT: 30-56975974-5
@@ -516,9 +516,6 @@
     <t>QUIEN NO INFORME EL PAGO DE LA MANERA SOLICITADA CORRE EL RIESGO DE NO VER EL MISMO IMPUTADO. SE SOSTIENE EL MONTO DE EXPENSAS YA QUE SE PROCEDERA A LIMPIAR LOS TANQUES DE AGUA Y DESPUES DE LA ASAMBLEA SE DECIDIRA LA OBRA QUE SE REALIZARA EN LOS MISMOS.</t>
   </si>
   <si>
-    <t>AUMENTADOS EN abri 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nazareno e Ivon Iriarte
 </t>
   </si>
@@ -532,24 +529,12 @@
     <t>Macarena perez ruiz</t>
   </si>
   <si>
-    <t xml:space="preserve">Servisur 12/06 - Reconeccion circuito pulsadores y reemplazo de 6 de los mismos </t>
-  </si>
-  <si>
     <t>Debito 09/06</t>
   </si>
   <si>
-    <t>Debito 13/06</t>
-  </si>
-  <si>
-    <t>Casa monini - Compra de pulsadores y compra de teclas de luz</t>
-  </si>
-  <si>
     <t>Sueldo encargada - Jimena Borges y SAC</t>
   </si>
   <si>
-    <t>Servisur 27/05 - Reemplazo de tres lamparas en pasillos y en el 10A - Material y mano de obra</t>
-  </si>
-  <si>
     <t>macarena en febrero no le contamos un pago de 109277 , por lo que viene arrastrando una deuda inexistente, hay que corregirlo</t>
   </si>
   <si>
@@ -574,7 +559,13 @@
     <t>Fumigacion Lanus 12/07</t>
   </si>
   <si>
-    <t>Examen medico</t>
+    <t>Debito 14/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Examen medico - Presentacion Sra. Encargada </t>
+  </si>
+  <si>
+    <t>AUMENTADOS EN juli 2025</t>
   </si>
 </sst>
 </file>
@@ -582,14 +573,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -1405,10 +1396,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1428,7 +1419,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1437,11 +1428,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1454,7 +1445,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1466,7 +1457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1474,15 +1465,15 @@
     <xf numFmtId="10" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1513,7 +1504,7 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1523,17 +1514,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1549,28 +1540,28 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="26" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1581,48 +1572,48 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="31" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1635,31 +1626,31 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="32" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1667,7 +1658,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1678,45 +1669,137 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1779,7 +1862,7 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1791,104 +1874,9 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2306,26 +2294,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="70" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="70" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="70" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="70" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="70" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="70" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="70" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="70" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="70" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="70" customWidth="1"/>
     <col min="11" max="11" width="9" style="70" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2348,7 +2336,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -2365,7 +2353,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12">
@@ -2373,20 +2361,20 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="172" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="174"/>
+      <c r="F3" s="173" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="175"/>
       <c r="K3" s="147"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -2394,40 +2382,40 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="145"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="176"/>
-      <c r="I4" s="176"/>
-      <c r="J4" s="177"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="177"/>
+      <c r="H4" s="177"/>
+      <c r="I4" s="177"/>
+      <c r="J4" s="178"/>
       <c r="K4" s="147"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="181">
+      <c r="B5" s="182">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="181"/>
+      <c r="C5" s="182"/>
       <c r="D5" s="16"/>
       <c r="E5" s="146">
         <v>0</v>
       </c>
-      <c r="F5" s="175"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="177"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="178"/>
       <c r="K5" s="148"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15"/>
       <c r="B6" s="17" t="s">
         <v>2</v>
@@ -2435,24 +2423,24 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="145"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="179"/>
-      <c r="H6" s="179"/>
-      <c r="I6" s="179"/>
-      <c r="J6" s="180"/>
+      <c r="F6" s="179"/>
+      <c r="G6" s="180"/>
+      <c r="H6" s="180"/>
+      <c r="I6" s="180"/>
+      <c r="J6" s="181"/>
       <c r="K6" s="148"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
-      <c r="B7" s="181">
+      <c r="B7" s="182">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="181"/>
+      <c r="C7" s="182"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -2466,7 +2454,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>3</v>
       </c>
@@ -2513,7 +2501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>1</v>
       </c>
@@ -2564,7 +2552,7 @@
         <v>550800</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2</v>
       </c>
@@ -2615,7 +2603,7 @@
         <v>146880</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <v>3</v>
       </c>
@@ -2665,7 +2653,7 @@
         <v>130507.3074845599</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>4</v>
       </c>
@@ -2717,7 +2705,7 @@
       </c>
       <c r="P12" s="38"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
         <v>5</v>
       </c>
@@ -2770,7 +2758,7 @@
         <v>88230</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>6</v>
       </c>
@@ -2820,7 +2808,7 @@
         <v>142154.26324766575</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>7</v>
       </c>
@@ -2871,7 +2859,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>8</v>
       </c>
@@ -2924,7 +2912,7 @@
         <v>109649.99999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>9</v>
       </c>
@@ -2976,7 +2964,7 @@
         <v>267258.6557100396</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>10</v>
       </c>
@@ -3029,7 +3017,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
         <v>11</v>
       </c>
@@ -3040,7 +3028,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E19" s="30">
         <v>2.4899999999999999E-2</v>
@@ -3082,7 +3070,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>12</v>
       </c>
@@ -3132,7 +3120,7 @@
         <v>189846.22250868671</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>13</v>
       </c>
@@ -3185,7 +3173,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>14</v>
       </c>
@@ -3236,7 +3224,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
         <v>15</v>
       </c>
@@ -3289,7 +3277,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>16</v>
       </c>
@@ -3341,7 +3329,7 @@
         <v>238407.18050032918</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36">
         <v>17</v>
       </c>
@@ -3392,7 +3380,7 @@
         <v>126989.77062953995</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>18</v>
       </c>
@@ -3443,7 +3431,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
         <v>19</v>
       </c>
@@ -3494,7 +3482,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <v>20</v>
       </c>
@@ -3542,7 +3530,7 @@
         <v>252361.89852420762</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
         <v>21</v>
       </c>
@@ -3595,7 +3583,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>22</v>
       </c>
@@ -3648,7 +3636,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>23</v>
       </c>
@@ -3696,7 +3684,7 @@
         <v>537341.03369272652</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="36">
         <v>24</v>
       </c>
@@ -3746,7 +3734,7 @@
         <v>686031.04451645561</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <f>A32+1</f>
         <v>25</v>
@@ -3799,7 +3787,7 @@
         <v>137983.29341615291</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <f t="shared" ref="A34:A42" si="8">A33+1</f>
         <v>26</v>
@@ -3853,7 +3841,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -3906,7 +3894,7 @@
       </c>
       <c r="P35" s="87"/>
     </row>
-    <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -3960,7 +3948,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -3972,7 +3960,7 @@
         <v>76</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E37" s="30">
         <v>2.4899999999999999E-2</v>
@@ -4014,7 +4002,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -4026,7 +4014,7 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E38" s="30">
         <v>2.1499999999999998E-2</v>
@@ -4034,7 +4022,7 @@
       <c r="F38" s="18">
         <v>344673.7297766995</v>
       </c>
-      <c r="G38" s="170">
+      <c r="G38" s="169">
         <v>107500</v>
       </c>
       <c r="H38" s="32">
@@ -4067,7 +4055,7 @@
         <v>358824.72050340049</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <f t="shared" si="8"/>
         <v>31</v>
@@ -4121,7 +4109,7 @@
         <v>69360</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -4173,7 +4161,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <f t="shared" si="8"/>
         <v>33</v>
@@ -4227,7 +4215,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="57">
         <f t="shared" si="8"/>
         <v>34</v>
@@ -4281,7 +4269,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
       <c r="B43" s="62"/>
       <c r="C43" s="63"/>
@@ -4329,9 +4317,9 @@
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G45" s="171" t="s">
-        <v>173</v>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G45" s="170" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4348,21 +4336,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="25.44140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -4372,27 +4360,27 @@
       <c r="G1" s="72"/>
       <c r="H1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="193"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="195"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D2" s="225"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="227"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="196" t="s">
+      <c r="E3" s="228" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="197"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F3" s="228"/>
+      <c r="G3" s="228"/>
+      <c r="H3" s="229"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
       <c r="D4" s="74" t="s">
         <v>90</v>
@@ -4402,7 +4390,7 @@
       </c>
       <c r="H4" s="76"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="D5" s="74" t="s">
         <v>92</v>
@@ -4412,7 +4400,7 @@
       </c>
       <c r="H5" s="76"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="D6" s="74" t="s">
         <v>93</v>
@@ -4422,30 +4410,30 @@
       </c>
       <c r="H6" s="76"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="D7" s="74" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="76"/>
     </row>
-    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="78" t="s">
         <v>96</v>
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H8" s="81"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>97</v>
       </c>
@@ -4457,19 +4445,19 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="198" t="s">
+    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="230" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="199"/>
-      <c r="C10" s="199"/>
-      <c r="D10" s="199"/>
-      <c r="E10" s="199"/>
-      <c r="F10" s="199"/>
-      <c r="G10" s="199"/>
-      <c r="H10" s="200"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+      <c r="D10" s="231"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="231"/>
+      <c r="G10" s="231"/>
+      <c r="H10" s="232"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4479,21 +4467,21 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="201" t="s">
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="233" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="201"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="201"/>
-      <c r="E12" s="201"/>
-      <c r="F12" s="201"/>
-      <c r="G12" s="201"/>
-      <c r="H12" s="201"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="233"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="233"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="233"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="153" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B13" s="154"/>
       <c r="C13" s="154"/>
@@ -4501,11 +4489,11 @@
       <c r="E13" s="154"/>
       <c r="F13" s="154"/>
       <c r="G13" s="154"/>
-      <c r="H13" s="82">
+      <c r="H13" s="172">
         <v>1552501</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="153" t="s">
         <v>143</v>
       </c>
@@ -4515,11 +4503,11 @@
       <c r="E14" s="154"/>
       <c r="F14" s="154"/>
       <c r="G14" s="154"/>
-      <c r="H14" s="82">
+      <c r="H14" s="172">
         <v>0.97</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="155" t="s">
         <v>101</v>
       </c>
@@ -4529,12 +4517,12 @@
       <c r="E15" s="155"/>
       <c r="F15" s="155"/>
       <c r="G15" s="155"/>
-      <c r="H15" s="82">
+      <c r="H15" s="172">
         <f>-337668.97</f>
         <v>-337668.97</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="156" t="s">
         <v>100</v>
       </c>
@@ -4550,19 +4538,19 @@
       </c>
       <c r="I16" s="83"/>
     </row>
-    <row r="17" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="202" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="202"/>
-      <c r="C17" s="202"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="202"/>
-      <c r="F17" s="202"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="202"/>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="234" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="234"/>
+      <c r="C17" s="234"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="234"/>
+      <c r="F17" s="234"/>
+      <c r="G17" s="234"/>
+      <c r="H17" s="234"/>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="85" t="s">
         <v>160</v>
       </c>
@@ -4574,7 +4562,7 @@
       <c r="G18" s="154"/>
       <c r="H18" s="82"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="85" t="s">
         <v>159</v>
       </c>
@@ -4586,7 +4574,7 @@
       <c r="G19" s="154"/>
       <c r="H19" s="82"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="154"/>
       <c r="B20" s="154"/>
       <c r="C20" s="154"/>
@@ -4596,7 +4584,7 @@
       <c r="G20" s="154"/>
       <c r="H20" s="82"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="154" t="s">
         <v>102</v>
       </c>
@@ -4611,85 +4599,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="202" t="s">
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="234" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="202"/>
-      <c r="C22" s="202"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="234"/>
+      <c r="C22" s="234"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="234"/>
+      <c r="F22" s="234"/>
+      <c r="G22" s="234"/>
+      <c r="H22" s="234"/>
+    </row>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="153" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="158" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C23" s="158"/>
       <c r="D23" s="158"/>
       <c r="E23" s="158"/>
       <c r="F23" s="158"/>
       <c r="G23" s="154"/>
-      <c r="H23" s="238">
+      <c r="H23" s="171">
         <v>137308.57</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="153" t="s">
         <v>151</v>
       </c>
       <c r="B24" s="154" t="str">
         <f>B23</f>
-        <v>Debito 13/06</v>
+        <v>Debito 14/07</v>
       </c>
       <c r="C24" s="158"/>
       <c r="D24" s="158"/>
       <c r="E24" s="158"/>
       <c r="F24" s="158"/>
       <c r="G24" s="154"/>
-      <c r="H24" s="238">
+      <c r="H24" s="171">
         <v>69862.55</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="153" t="s">
         <v>105</v>
       </c>
       <c r="B25" s="154" t="str">
         <f>B24</f>
-        <v>Debito 13/06</v>
+        <v>Debito 14/07</v>
       </c>
       <c r="C25" s="158"/>
       <c r="D25" s="158"/>
       <c r="E25" s="158"/>
       <c r="F25" s="158"/>
       <c r="G25" s="154"/>
-      <c r="H25" s="238">
+      <c r="H25" s="171">
         <v>7762.51</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="153" t="s">
         <v>157</v>
       </c>
       <c r="B26" s="154" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158"/>
       <c r="E26" s="158"/>
       <c r="F26" s="158"/>
       <c r="G26" s="154"/>
-      <c r="H26" s="238">
+      <c r="H26" s="171">
         <v>714361.65</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="153"/>
       <c r="B27" s="154"/>
       <c r="C27" s="158"/>
@@ -4701,7 +4689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="157" t="s">
         <v>106</v>
       </c>
@@ -4716,19 +4704,19 @@
         <v>929295.28</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="192" t="s">
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="224" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="192"/>
-      <c r="C29" s="192"/>
-      <c r="D29" s="192"/>
-      <c r="E29" s="192"/>
-      <c r="F29" s="192"/>
-      <c r="G29" s="192"/>
-      <c r="H29" s="192"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="224"/>
+      <c r="C29" s="224"/>
+      <c r="D29" s="224"/>
+      <c r="E29" s="224"/>
+      <c r="F29" s="224"/>
+      <c r="G29" s="224"/>
+      <c r="H29" s="224"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="154" t="s">
         <v>108</v>
       </c>
@@ -4738,11 +4726,11 @@
       <c r="E30" s="154"/>
       <c r="F30" s="154"/>
       <c r="G30" s="154"/>
-      <c r="H30" s="238">
+      <c r="H30" s="171">
         <v>200.93</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="154" t="s">
         <v>109</v>
       </c>
@@ -4759,7 +4747,7 @@
       </c>
       <c r="I31" s="87"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="159" t="s">
         <v>111</v>
       </c>
@@ -4771,11 +4759,11 @@
       <c r="E32" s="154"/>
       <c r="F32" s="154"/>
       <c r="G32" s="154"/>
-      <c r="H32" s="238">
+      <c r="H32" s="171">
         <v>203720.4</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="157" t="s">
         <v>100</v>
       </c>
@@ -4790,19 +4778,19 @@
         <v>1432938.4899999998</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="192" t="s">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="224" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="192"/>
-      <c r="C34" s="192"/>
-      <c r="D34" s="192"/>
-      <c r="E34" s="192"/>
-      <c r="F34" s="192"/>
-      <c r="G34" s="192"/>
-      <c r="H34" s="192"/>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="85"/>
       <c r="B35" s="161"/>
       <c r="C35" s="154"/>
@@ -4812,7 +4800,7 @@
       <c r="G35" s="154"/>
       <c r="H35" s="82"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="85" t="s">
         <v>158</v>
       </c>
@@ -4822,13 +4810,13 @@
       <c r="E36" s="154"/>
       <c r="F36" s="154"/>
       <c r="G36" s="154"/>
-      <c r="H36" s="238">
+      <c r="H36" s="171">
         <v>140000</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="85" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B37" s="162"/>
       <c r="C37" s="85"/>
@@ -4836,28 +4824,28 @@
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="238">
+      <c r="H37" s="171">
         <v>40000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
-    <row r="38" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="209" t="s">
-        <v>181</v>
-      </c>
-      <c r="B38" s="210"/>
-      <c r="C38" s="210"/>
-      <c r="D38" s="210"/>
-      <c r="E38" s="210"/>
-      <c r="F38" s="210"/>
-      <c r="G38" s="211"/>
-      <c r="H38" s="238">
+    <row r="38" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="183" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="184"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="185"/>
+      <c r="H38" s="171">
         <v>32240.45</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="85" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B39" s="161"/>
       <c r="C39" s="154"/>
@@ -4865,173 +4853,166 @@
       <c r="E39" s="154"/>
       <c r="F39" s="154"/>
       <c r="G39" s="154"/>
-      <c r="H39" s="238">
+      <c r="H39" s="171">
         <v>101540</v>
       </c>
       <c r="I39" s="149"/>
-      <c r="J39" s="212"/>
-    </row>
-    <row r="40" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="209" t="s">
-        <v>179</v>
-      </c>
-      <c r="B40" s="210"/>
-      <c r="C40" s="210"/>
-      <c r="D40" s="210"/>
-      <c r="E40" s="210"/>
-      <c r="F40" s="210"/>
-      <c r="G40" s="211"/>
-      <c r="H40" s="238">
+      <c r="J39" s="186"/>
+    </row>
+    <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="183" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="184"/>
+      <c r="C40" s="184"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="184"/>
+      <c r="G40" s="185"/>
+      <c r="H40" s="171">
         <v>741000</v>
       </c>
-      <c r="J40" s="212"/>
-    </row>
-    <row r="41" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="96"/>
-      <c r="B41" s="168"/>
-      <c r="C41" s="168"/>
-      <c r="D41" s="168"/>
-      <c r="E41" s="168"/>
-      <c r="F41" s="168"/>
-      <c r="G41" s="169"/>
-      <c r="H41" s="82">
-        <v>500000</v>
-      </c>
-      <c r="J41" s="212"/>
-    </row>
-    <row r="42" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="96" t="s">
-        <v>178</v>
-      </c>
-      <c r="B42" s="168"/>
-      <c r="C42" s="168"/>
-      <c r="D42" s="168"/>
-      <c r="E42" s="168"/>
-      <c r="F42" s="168"/>
-      <c r="G42" s="169"/>
-      <c r="H42" s="238">
+      <c r="J40" s="186"/>
+    </row>
+    <row r="41" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="96" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="167"/>
+      <c r="C41" s="167"/>
+      <c r="D41" s="167"/>
+      <c r="E41" s="167"/>
+      <c r="F41" s="167"/>
+      <c r="G41" s="168"/>
+      <c r="H41" s="171">
         <v>36300</v>
       </c>
-      <c r="J42" s="212"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="85" t="s">
-        <v>167</v>
-      </c>
-      <c r="B43" s="161"/>
-      <c r="C43" s="154"/>
-      <c r="D43" s="154"/>
-      <c r="E43" s="154"/>
-      <c r="F43" s="154"/>
-      <c r="G43" s="154"/>
-      <c r="H43" s="82">
-        <v>160000</v>
-      </c>
-      <c r="J43" s="212"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="85" t="s">
-        <v>172</v>
-      </c>
-      <c r="B44" s="161"/>
-      <c r="C44" s="154"/>
-      <c r="D44" s="154"/>
+      <c r="J41" s="186"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="154" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="154"/>
+      <c r="C42" s="154"/>
+      <c r="D42" s="154"/>
+      <c r="E42" s="154"/>
+      <c r="F42" s="154"/>
+      <c r="G42" s="154"/>
+      <c r="H42" s="84">
+        <f>SUM(H35:H41)</f>
+        <v>1091080.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="224" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="224"/>
+      <c r="C43" s="224"/>
+      <c r="D43" s="224"/>
+      <c r="E43" s="224"/>
+      <c r="F43" s="224"/>
+      <c r="G43" s="224"/>
+      <c r="H43" s="224"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="154" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="154"/>
+      <c r="C44" s="154" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="163"/>
       <c r="E44" s="154"/>
       <c r="F44" s="154"/>
       <c r="G44" s="154"/>
-      <c r="H44" s="82">
-        <v>57535</v>
-      </c>
-      <c r="J44" s="167"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="85" t="s">
-        <v>170</v>
-      </c>
-      <c r="B45" s="161"/>
-      <c r="C45" s="154"/>
-      <c r="D45" s="154"/>
-      <c r="E45" s="154"/>
-      <c r="F45" s="154"/>
+      <c r="H44" s="171">
+        <v>265000</v>
+      </c>
+      <c r="J44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="164" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" s="154"/>
+      <c r="C45" s="204"/>
+      <c r="D45" s="205"/>
+      <c r="E45" s="165"/>
+      <c r="F45" s="158"/>
       <c r="G45" s="154"/>
-      <c r="H45" s="82">
-        <v>156892.12</v>
-      </c>
-      <c r="I45" s="149"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="154" t="s">
+      <c r="H45" s="171">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="154"/>
+      <c r="B46" s="154"/>
+      <c r="C46" s="158"/>
+      <c r="D46" s="158"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="154"/>
+      <c r="H46" s="82"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="157" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="154"/>
-      <c r="C46" s="154"/>
-      <c r="D46" s="154"/>
-      <c r="E46" s="154"/>
-      <c r="F46" s="154"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="84">
-        <f>SUM(H35:H45)</f>
-        <v>1965507.5699999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="192" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="192"/>
-      <c r="C47" s="192"/>
-      <c r="D47" s="192"/>
-      <c r="E47" s="192"/>
-      <c r="F47" s="192"/>
-      <c r="G47" s="192"/>
-      <c r="H47" s="192"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="154" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" s="154"/>
-      <c r="C48" s="154" t="s">
-        <v>176</v>
-      </c>
-      <c r="D48" s="163"/>
-      <c r="E48" s="154"/>
-      <c r="F48" s="154"/>
-      <c r="G48" s="154"/>
-      <c r="H48" s="239">
-        <v>250000</v>
-      </c>
-      <c r="J48" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="164" t="s">
-        <v>147</v>
+      <c r="B47" s="157"/>
+      <c r="C47" s="157"/>
+      <c r="D47" s="157"/>
+      <c r="E47" s="157"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="84">
+        <f>SUM(H44:H46)</f>
+        <v>295000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="235" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="236"/>
+      <c r="C48" s="236"/>
+      <c r="D48" s="236"/>
+      <c r="E48" s="236"/>
+      <c r="F48" s="236"/>
+      <c r="G48" s="236"/>
+      <c r="H48" s="237"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="154" t="s">
+        <v>117</v>
       </c>
       <c r="B49" s="154"/>
-      <c r="C49" s="230"/>
-      <c r="D49" s="231"/>
-      <c r="E49" s="165"/>
-      <c r="F49" s="158"/>
+      <c r="C49" s="154"/>
+      <c r="D49" s="154"/>
+      <c r="E49" s="154"/>
+      <c r="F49" s="154"/>
       <c r="G49" s="154"/>
-      <c r="H49" s="238">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H49" s="172">
+        <v>89235.14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="154"/>
       <c r="B50" s="154"/>
-      <c r="C50" s="158"/>
-      <c r="D50" s="158"/>
-      <c r="E50" s="158"/>
-      <c r="F50" s="158"/>
+      <c r="C50" s="154"/>
+      <c r="D50" s="154"/>
+      <c r="E50" s="154"/>
+      <c r="F50" s="154"/>
       <c r="G50" s="154"/>
       <c r="H50" s="82"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="157" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B51" s="157"/>
       <c r="C51" s="157"/>
@@ -5039,158 +5020,149 @@
       <c r="E51" s="157"/>
       <c r="F51" s="157"/>
       <c r="G51" s="157"/>
-      <c r="H51" s="84">
-        <f>SUM(H48:H50)</f>
-        <v>280000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="203" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="204"/>
-      <c r="C52" s="204"/>
-      <c r="D52" s="204"/>
-      <c r="E52" s="204"/>
-      <c r="F52" s="204"/>
-      <c r="G52" s="204"/>
-      <c r="H52" s="205"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="154" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="154"/>
-      <c r="C53" s="154"/>
-      <c r="D53" s="154"/>
-      <c r="E53" s="154"/>
-      <c r="F53" s="154"/>
-      <c r="G53" s="154"/>
-      <c r="H53" s="82">
+      <c r="H51" s="160">
+        <f>SUM(H49:H50)</f>
         <v>89235.14</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="154"/>
-      <c r="B54" s="154"/>
-      <c r="C54" s="154"/>
-      <c r="D54" s="154"/>
-      <c r="E54" s="154"/>
-      <c r="F54" s="154"/>
-      <c r="G54" s="154"/>
-      <c r="H54" s="82"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="157" t="s">
-        <v>106</v>
-      </c>
-      <c r="B55" s="157"/>
-      <c r="C55" s="157"/>
-      <c r="D55" s="157"/>
-      <c r="E55" s="157"/>
-      <c r="F55" s="157"/>
-      <c r="G55" s="157"/>
-      <c r="H55" s="160">
+    <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="235" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" s="236"/>
+      <c r="C52" s="236"/>
+      <c r="D52" s="236"/>
+      <c r="E52" s="236"/>
+      <c r="F52" s="236"/>
+      <c r="G52" s="236"/>
+      <c r="H52" s="237"/>
+      <c r="I52" s="87"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="85"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="85"/>
+      <c r="E53" s="85"/>
+      <c r="F53" s="85"/>
+      <c r="G53" s="85"/>
+      <c r="H53" s="172">
+        <v>49889.86</v>
+      </c>
+      <c r="I53" s="87"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="85" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" s="85"/>
+      <c r="C54" s="85"/>
+      <c r="D54" s="85"/>
+      <c r="E54" s="85"/>
+      <c r="F54" s="85"/>
+      <c r="G54" s="85"/>
+      <c r="H54" s="172">
+        <v>3498.02</v>
+      </c>
+      <c r="I54" s="87"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="85"/>
+      <c r="C55" s="85"/>
+      <c r="D55" s="85"/>
+      <c r="E55" s="85"/>
+      <c r="F55" s="85"/>
+      <c r="G55" s="85"/>
+      <c r="H55" s="84">
         <f>SUM(H53:H54)</f>
-        <v>89235.14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="203" t="s">
-        <v>118</v>
-      </c>
-      <c r="B56" s="204"/>
-      <c r="C56" s="204"/>
-      <c r="D56" s="204"/>
-      <c r="E56" s="204"/>
-      <c r="F56" s="204"/>
-      <c r="G56" s="204"/>
-      <c r="H56" s="205"/>
-      <c r="I56" s="87"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="85" t="s">
-        <v>140</v>
-      </c>
-      <c r="B57" s="85"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="85"/>
-      <c r="H57" s="82">
-        <v>49889.86</v>
-      </c>
-      <c r="I57" s="87"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="B58" s="85"/>
-      <c r="C58" s="85"/>
-      <c r="D58" s="85"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
-      <c r="H58" s="82">
-        <v>3498.02</v>
-      </c>
-      <c r="I58" s="87"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="85" t="s">
+        <v>53387.88</v>
+      </c>
+      <c r="I55" s="87"/>
+      <c r="K55" s="83"/>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="206" t="s">
+        <v>119</v>
+      </c>
+      <c r="B56" s="207"/>
+      <c r="C56" s="207"/>
+      <c r="D56" s="207"/>
+      <c r="E56" s="207"/>
+      <c r="F56" s="207"/>
+      <c r="G56" s="207"/>
+      <c r="H56" s="238"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="86"/>
+      <c r="B57" s="86"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
+      <c r="H57" s="90"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="86"/>
+      <c r="B58" s="86"/>
+      <c r="C58" s="86"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
+      <c r="H58" s="90"/>
+    </row>
+    <row r="59" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="85"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="85"/>
-      <c r="E59" s="85"/>
-      <c r="F59" s="85"/>
-      <c r="G59" s="85"/>
-      <c r="H59" s="84">
-        <f>SUM(H57:H58)</f>
-        <v>53387.88</v>
-      </c>
-      <c r="I59" s="87"/>
-      <c r="K59" s="83"/>
-    </row>
-    <row r="60" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="206" t="s">
-        <v>119</v>
-      </c>
-      <c r="B60" s="207"/>
-      <c r="C60" s="207"/>
-      <c r="D60" s="207"/>
-      <c r="E60" s="207"/>
-      <c r="F60" s="207"/>
-      <c r="G60" s="207"/>
-      <c r="H60" s="208"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61" s="86"/>
-      <c r="B61" s="86"/>
-      <c r="C61" s="86"/>
-      <c r="D61" s="86"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="86"/>
-      <c r="H61" s="90"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="86"/>
-      <c r="B62" s="86"/>
-      <c r="C62" s="86"/>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
-      <c r="H62" s="90"/>
-    </row>
-    <row r="63" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A63" s="91" t="s">
-        <v>100</v>
-      </c>
+      <c r="B59" s="89"/>
+      <c r="C59" s="89"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="89"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="89"/>
+      <c r="H59" s="92"/>
+    </row>
+    <row r="60" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="93"/>
+      <c r="B60" s="132"/>
+      <c r="C60" s="132"/>
+      <c r="D60" s="132"/>
+      <c r="E60" s="132"/>
+      <c r="F60" s="132"/>
+      <c r="G60" s="132"/>
+      <c r="H60" s="94"/>
+    </row>
+    <row r="61" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="91"/>
+      <c r="B61" s="89"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
+      <c r="H61" s="92"/>
+    </row>
+    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="206" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="207"/>
+      <c r="C62" s="207"/>
+      <c r="D62" s="207"/>
+      <c r="E62" s="207"/>
+      <c r="F62" s="207"/>
+      <c r="G62" s="207"/>
+      <c r="H62" s="128"/>
+    </row>
+    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="91"/>
       <c r="B63" s="89"/>
       <c r="C63" s="89"/>
       <c r="D63" s="89"/>
@@ -5199,607 +5171,549 @@
       <c r="G63" s="89"/>
       <c r="H63" s="92"/>
     </row>
-    <row r="64" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A64" s="93"/>
-      <c r="B64" s="132"/>
-      <c r="C64" s="132"/>
-      <c r="D64" s="132"/>
-      <c r="E64" s="132"/>
-      <c r="F64" s="132"/>
-      <c r="G64" s="132"/>
-      <c r="H64" s="94"/>
-    </row>
-    <row r="65" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="91"/>
-      <c r="B65" s="89"/>
-      <c r="C65" s="89"/>
-      <c r="D65" s="89"/>
-      <c r="E65" s="89"/>
-      <c r="F65" s="89"/>
-      <c r="G65" s="89"/>
-      <c r="H65" s="92"/>
-    </row>
-    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="206" t="s">
-        <v>152</v>
-      </c>
-      <c r="B66" s="207"/>
-      <c r="C66" s="207"/>
-      <c r="D66" s="207"/>
-      <c r="E66" s="207"/>
-      <c r="F66" s="207"/>
-      <c r="G66" s="207"/>
-      <c r="H66" s="128"/>
-    </row>
-    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="91"/>
-      <c r="B67" s="89"/>
-      <c r="C67" s="89"/>
-      <c r="D67" s="89"/>
-      <c r="E67" s="89"/>
-      <c r="F67" s="89"/>
-      <c r="G67" s="89"/>
-      <c r="H67" s="92"/>
-    </row>
-    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="91"/>
-      <c r="B68" s="89"/>
-      <c r="C68" s="89"/>
-      <c r="D68" s="89"/>
-      <c r="E68" s="89"/>
-      <c r="F68" s="89"/>
-      <c r="G68" s="89"/>
-      <c r="H68" s="92"/>
-    </row>
-    <row r="69" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="129" t="s">
+    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="91"/>
+      <c r="B64" s="89"/>
+      <c r="C64" s="89"/>
+      <c r="D64" s="89"/>
+      <c r="E64" s="89"/>
+      <c r="F64" s="89"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="92"/>
+    </row>
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="129" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="132"/>
-      <c r="C69" s="132"/>
-      <c r="D69" s="132"/>
-      <c r="E69" s="132"/>
-      <c r="F69" s="132"/>
-      <c r="G69" s="132"/>
-      <c r="H69" s="94">
-        <f>SUM(H67:H68)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A70" s="91"/>
-      <c r="B70" s="89"/>
-      <c r="C70" s="89"/>
-      <c r="D70" s="89"/>
-      <c r="E70" s="89"/>
-      <c r="F70" s="89"/>
-      <c r="G70" s="89"/>
-      <c r="H70" s="92"/>
-    </row>
-    <row r="71" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A71" s="224" t="s">
+      <c r="B65" s="132"/>
+      <c r="C65" s="132"/>
+      <c r="D65" s="132"/>
+      <c r="E65" s="132"/>
+      <c r="F65" s="132"/>
+      <c r="G65" s="132"/>
+      <c r="H65" s="94">
+        <f>SUM(H63:H64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="91"/>
+      <c r="B66" s="89"/>
+      <c r="C66" s="89"/>
+      <c r="D66" s="89"/>
+      <c r="E66" s="89"/>
+      <c r="F66" s="89"/>
+      <c r="G66" s="89"/>
+      <c r="H66" s="92"/>
+    </row>
+    <row r="67" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A67" s="198" t="s">
         <v>120</v>
       </c>
-      <c r="B71" s="224"/>
-      <c r="C71" s="224"/>
-      <c r="D71" s="224"/>
-      <c r="E71" s="224"/>
-      <c r="F71" s="224"/>
-      <c r="G71" s="224"/>
-      <c r="H71" s="95"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="209"/>
-      <c r="B72" s="210"/>
-      <c r="C72" s="210"/>
-      <c r="D72" s="210"/>
-      <c r="E72" s="210"/>
-      <c r="F72" s="210"/>
-      <c r="G72" s="211"/>
-      <c r="H72" s="124"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="96"/>
-      <c r="B73" s="97"/>
-      <c r="C73" s="97"/>
-      <c r="D73" s="97"/>
-      <c r="E73" s="97"/>
-      <c r="F73" s="97"/>
-      <c r="G73" s="98"/>
-      <c r="H73" s="124"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="225"/>
-      <c r="B74" s="226"/>
-      <c r="C74" s="226"/>
-      <c r="D74" s="226"/>
-      <c r="E74" s="226"/>
-      <c r="F74" s="226"/>
-      <c r="G74" s="227"/>
-      <c r="H74" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="133"/>
-      <c r="B75" s="134"/>
-      <c r="C75" s="134"/>
-      <c r="D75" s="134"/>
-      <c r="E75" s="134"/>
-      <c r="F75" s="134"/>
-      <c r="G75" s="135"/>
-      <c r="H75" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="133"/>
-      <c r="B76" s="134"/>
-      <c r="C76" s="134"/>
-      <c r="D76" s="134"/>
-      <c r="E76" s="134"/>
-      <c r="F76" s="134"/>
-      <c r="G76" s="135"/>
-      <c r="H76" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="137" t="s">
+      <c r="B67" s="198"/>
+      <c r="C67" s="198"/>
+      <c r="D67" s="198"/>
+      <c r="E67" s="198"/>
+      <c r="F67" s="198"/>
+      <c r="G67" s="198"/>
+      <c r="H67" s="95"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="183"/>
+      <c r="B68" s="184"/>
+      <c r="C68" s="184"/>
+      <c r="D68" s="184"/>
+      <c r="E68" s="184"/>
+      <c r="F68" s="184"/>
+      <c r="G68" s="185"/>
+      <c r="H68" s="124"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="96"/>
+      <c r="B69" s="97"/>
+      <c r="C69" s="97"/>
+      <c r="D69" s="97"/>
+      <c r="E69" s="97"/>
+      <c r="F69" s="97"/>
+      <c r="G69" s="98"/>
+      <c r="H69" s="124"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="199"/>
+      <c r="B70" s="200"/>
+      <c r="C70" s="200"/>
+      <c r="D70" s="200"/>
+      <c r="E70" s="200"/>
+      <c r="F70" s="200"/>
+      <c r="G70" s="201"/>
+      <c r="H70" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="133"/>
+      <c r="B71" s="134"/>
+      <c r="C71" s="134"/>
+      <c r="D71" s="134"/>
+      <c r="E71" s="134"/>
+      <c r="F71" s="134"/>
+      <c r="G71" s="135"/>
+      <c r="H71" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="133"/>
+      <c r="B72" s="134"/>
+      <c r="C72" s="134"/>
+      <c r="D72" s="134"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="135"/>
+      <c r="H72" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="137" t="s">
         <v>100</v>
       </c>
-      <c r="B77" s="85"/>
-      <c r="C77" s="85"/>
-      <c r="D77" s="85"/>
-      <c r="E77" s="85"/>
-      <c r="F77" s="85"/>
-      <c r="G77" s="85"/>
-      <c r="H77" s="84">
-        <f>SUM(H72:H76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="138"/>
-      <c r="B78" s="138"/>
-      <c r="C78" s="138"/>
-      <c r="D78" s="138"/>
-      <c r="E78" s="138"/>
-      <c r="F78" s="138"/>
-      <c r="G78" s="138"/>
-      <c r="H78" s="139"/>
-      <c r="I78" s="87"/>
-    </row>
-    <row r="79" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="228" t="s">
+      <c r="B73" s="85"/>
+      <c r="C73" s="85"/>
+      <c r="D73" s="85"/>
+      <c r="E73" s="85"/>
+      <c r="F73" s="85"/>
+      <c r="G73" s="85"/>
+      <c r="H73" s="84">
+        <f>SUM(H68:H72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="138"/>
+      <c r="B74" s="138"/>
+      <c r="C74" s="138"/>
+      <c r="D74" s="138"/>
+      <c r="E74" s="138"/>
+      <c r="F74" s="138"/>
+      <c r="G74" s="138"/>
+      <c r="H74" s="139"/>
+      <c r="I74" s="87"/>
+    </row>
+    <row r="75" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="202" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="229"/>
-      <c r="C79" s="229"/>
-      <c r="D79" s="229"/>
-      <c r="E79" s="229"/>
-      <c r="F79" s="229"/>
-      <c r="G79" s="229"/>
-      <c r="H79" s="140">
-        <f>H77</f>
-        <v>0</v>
-      </c>
-      <c r="I79" s="87"/>
-    </row>
-    <row r="80" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="221" t="s">
+      <c r="B75" s="203"/>
+      <c r="C75" s="203"/>
+      <c r="D75" s="203"/>
+      <c r="E75" s="203"/>
+      <c r="F75" s="203"/>
+      <c r="G75" s="203"/>
+      <c r="H75" s="140">
+        <f>H73</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="87"/>
+    </row>
+    <row r="76" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="195" t="s">
         <v>122</v>
       </c>
-      <c r="B80" s="222"/>
-      <c r="C80" s="222"/>
-      <c r="D80" s="222"/>
-      <c r="E80" s="222"/>
-      <c r="F80" s="222"/>
-      <c r="G80" s="223"/>
-      <c r="H80" s="140"/>
-      <c r="I80" s="88"/>
-    </row>
-    <row r="81" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="232" t="s">
+      <c r="B76" s="196"/>
+      <c r="C76" s="196"/>
+      <c r="D76" s="196"/>
+      <c r="E76" s="196"/>
+      <c r="F76" s="196"/>
+      <c r="G76" s="197"/>
+      <c r="H76" s="140"/>
+      <c r="I76" s="88"/>
+    </row>
+    <row r="77" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="208" t="s">
         <v>142</v>
       </c>
-      <c r="B81" s="233"/>
-      <c r="C81" s="233"/>
-      <c r="D81" s="233"/>
-      <c r="E81" s="233"/>
-      <c r="F81" s="233"/>
-      <c r="G81" s="234"/>
-      <c r="H81" s="140"/>
-      <c r="I81" s="87"/>
-      <c r="J81" s="83"/>
-    </row>
-    <row r="82" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A82" s="228" t="s">
+      <c r="B77" s="209"/>
+      <c r="C77" s="209"/>
+      <c r="D77" s="209"/>
+      <c r="E77" s="209"/>
+      <c r="F77" s="209"/>
+      <c r="G77" s="210"/>
+      <c r="H77" s="140"/>
+      <c r="I77" s="87"/>
+      <c r="J77" s="83"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A78" s="202" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="229"/>
-      <c r="C82" s="229"/>
-      <c r="D82" s="229"/>
-      <c r="E82" s="229"/>
-      <c r="F82" s="229"/>
-      <c r="G82" s="229"/>
-      <c r="H82" s="140">
-        <f>H63+H59+H55+H51+H46+H33+H16+H21+H28+H69</f>
-        <v>5965197.3600000003</v>
-      </c>
-      <c r="I82" s="83"/>
-    </row>
-    <row r="83" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A83" s="235" t="s">
+      <c r="B78" s="203"/>
+      <c r="C78" s="203"/>
+      <c r="D78" s="203"/>
+      <c r="E78" s="203"/>
+      <c r="F78" s="203"/>
+      <c r="G78" s="203"/>
+      <c r="H78" s="140">
+        <f>H59+H55+H51+H47+H42+H33+H16+H21+H28+H65</f>
+        <v>5105770.24</v>
+      </c>
+      <c r="I78" s="83"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A79" s="211" t="s">
         <v>124</v>
       </c>
-      <c r="B83" s="236"/>
-      <c r="C83" s="236"/>
-      <c r="D83" s="236"/>
-      <c r="E83" s="236"/>
-      <c r="F83" s="236"/>
-      <c r="G83" s="237"/>
-      <c r="H83" s="141">
-        <f>H82+H80</f>
-        <v>5965197.3600000003</v>
-      </c>
-      <c r="I83" s="83"/>
-      <c r="K83" s="149"/>
-    </row>
-    <row r="84" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A84" s="235" t="s">
+      <c r="B79" s="212"/>
+      <c r="C79" s="212"/>
+      <c r="D79" s="212"/>
+      <c r="E79" s="212"/>
+      <c r="F79" s="212"/>
+      <c r="G79" s="213"/>
+      <c r="H79" s="141">
+        <f>H78+H76</f>
+        <v>5105770.24</v>
+      </c>
+      <c r="I79" s="83"/>
+      <c r="K79" s="149"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A80" s="211" t="s">
         <v>125</v>
       </c>
-      <c r="B84" s="236"/>
-      <c r="C84" s="236"/>
-      <c r="D84" s="236"/>
-      <c r="E84" s="236"/>
-      <c r="F84" s="236"/>
-      <c r="G84" s="237"/>
-      <c r="H84" s="142">
-        <f>H79+H81</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="83"/>
-    </row>
-    <row r="85" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="182" t="s">
+      <c r="B80" s="212"/>
+      <c r="C80" s="212"/>
+      <c r="D80" s="212"/>
+      <c r="E80" s="212"/>
+      <c r="F80" s="212"/>
+      <c r="G80" s="213"/>
+      <c r="H80" s="142">
+        <f>H75+H77</f>
+        <v>0</v>
+      </c>
+      <c r="I80" s="83"/>
+    </row>
+    <row r="81" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="214" t="s">
         <v>126</v>
       </c>
-      <c r="B85" s="183"/>
-      <c r="C85" s="183"/>
-      <c r="D85" s="183"/>
-      <c r="E85" s="183"/>
-      <c r="F85" s="183"/>
-      <c r="G85" s="183"/>
-      <c r="H85" s="143">
-        <f>H82+H79</f>
-        <v>5965197.3600000003</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="184" t="s">
+      <c r="B81" s="215"/>
+      <c r="C81" s="215"/>
+      <c r="D81" s="215"/>
+      <c r="E81" s="215"/>
+      <c r="F81" s="215"/>
+      <c r="G81" s="215"/>
+      <c r="H81" s="143">
+        <f>H78+H75</f>
+        <v>5105770.24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="216" t="s">
         <v>127</v>
       </c>
-      <c r="B86" s="185"/>
-      <c r="C86" s="185"/>
-      <c r="D86" s="185"/>
-      <c r="E86" s="185"/>
-      <c r="F86" s="185"/>
-      <c r="G86" s="185"/>
-      <c r="H86" s="100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="101"/>
-      <c r="B87" s="101"/>
-      <c r="C87" s="101"/>
-      <c r="D87" s="101"/>
-      <c r="E87" s="101"/>
-      <c r="F87" s="101"/>
-      <c r="G87" s="101"/>
-      <c r="H87" s="102"/>
-    </row>
-    <row r="88" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="186" t="s">
+      <c r="B82" s="217"/>
+      <c r="C82" s="217"/>
+      <c r="D82" s="217"/>
+      <c r="E82" s="217"/>
+      <c r="F82" s="217"/>
+      <c r="G82" s="217"/>
+      <c r="H82" s="100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="101"/>
+      <c r="B83" s="101"/>
+      <c r="C83" s="101"/>
+      <c r="D83" s="101"/>
+      <c r="E83" s="101"/>
+      <c r="F83" s="101"/>
+      <c r="G83" s="101"/>
+      <c r="H83" s="102"/>
+    </row>
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="218" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="187"/>
-      <c r="C88" s="187"/>
-      <c r="D88" s="187"/>
-      <c r="E88" s="187"/>
-      <c r="F88" s="187"/>
-      <c r="G88" s="187"/>
-      <c r="H88" s="188"/>
-    </row>
-    <row r="89" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="189"/>
-      <c r="B89" s="190"/>
-      <c r="C89" s="190"/>
-      <c r="D89" s="190"/>
-      <c r="E89" s="190"/>
-      <c r="F89" s="190"/>
-      <c r="G89" s="190"/>
-      <c r="H89" s="191"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-    </row>
-    <row r="91" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A91" s="213" t="s">
+      <c r="B84" s="219"/>
+      <c r="C84" s="219"/>
+      <c r="D84" s="219"/>
+      <c r="E84" s="219"/>
+      <c r="F84" s="219"/>
+      <c r="G84" s="219"/>
+      <c r="H84" s="220"/>
+    </row>
+    <row r="85" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="221"/>
+      <c r="B85" s="222"/>
+      <c r="C85" s="222"/>
+      <c r="D85" s="222"/>
+      <c r="E85" s="222"/>
+      <c r="F85" s="222"/>
+      <c r="G85" s="222"/>
+      <c r="H85" s="223"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+    </row>
+    <row r="87" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A87" s="187" t="s">
         <v>128</v>
       </c>
-      <c r="B91" s="214"/>
-      <c r="C91" s="214"/>
-      <c r="D91" s="214"/>
-      <c r="E91" s="214"/>
-      <c r="F91" s="214"/>
-      <c r="G91" s="214"/>
-      <c r="H91" s="215"/>
-    </row>
-    <row r="92" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A92" s="103" t="s">
+      <c r="B87" s="188"/>
+      <c r="C87" s="188"/>
+      <c r="D87" s="188"/>
+      <c r="E87" s="188"/>
+      <c r="F87" s="188"/>
+      <c r="G87" s="188"/>
+      <c r="H87" s="189"/>
+    </row>
+    <row r="88" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A88" s="103" t="s">
         <v>129</v>
       </c>
-      <c r="B92" s="104"/>
-      <c r="C92" s="104"/>
-      <c r="D92" s="104"/>
-      <c r="E92" s="104"/>
-      <c r="F92" s="104"/>
-      <c r="G92" s="104"/>
-      <c r="H92" s="105">
+      <c r="B88" s="104"/>
+      <c r="C88" s="104"/>
+      <c r="D88" s="104"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="104"/>
+      <c r="G88" s="104"/>
+      <c r="H88" s="105">
         <v>1280791.0346397704</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" s="8" t="s">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B93" s="106"/>
-      <c r="C93" s="106"/>
-      <c r="D93" s="106"/>
-      <c r="E93" s="106"/>
-      <c r="F93" s="106"/>
-      <c r="G93" s="106"/>
-      <c r="H93" s="18">
+      <c r="B89" s="106"/>
+      <c r="C89" s="106"/>
+      <c r="D89" s="106"/>
+      <c r="E89" s="106"/>
+      <c r="F89" s="106"/>
+      <c r="G89" s="106"/>
+      <c r="H89" s="18">
         <f>Planilla!G43</f>
         <v>4581518.1130966982</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A94" s="107" t="s">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="107" t="s">
         <v>136</v>
       </c>
-      <c r="B94" s="108"/>
-      <c r="C94" s="108"/>
-      <c r="D94" s="108"/>
-      <c r="E94" s="108"/>
-      <c r="F94" s="108"/>
-      <c r="G94" s="108"/>
-      <c r="H94" s="123">
-        <f>-H85</f>
-        <v>-5965197.3600000003</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A95" s="107" t="s">
+      <c r="B90" s="108"/>
+      <c r="C90" s="108"/>
+      <c r="D90" s="108"/>
+      <c r="E90" s="108"/>
+      <c r="F90" s="108"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="123">
+        <f>-H81</f>
+        <v>-5105770.24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="107" t="s">
         <v>131</v>
       </c>
-      <c r="B95" s="108"/>
-      <c r="C95" s="108"/>
-      <c r="D95" s="108"/>
-      <c r="E95" s="108"/>
-      <c r="F95" s="108"/>
-      <c r="G95" s="108"/>
-      <c r="H95" s="31">
-        <f>D109</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" s="107" t="s">
+      <c r="B91" s="108"/>
+      <c r="C91" s="108"/>
+      <c r="D91" s="108"/>
+      <c r="E91" s="108"/>
+      <c r="F91" s="108"/>
+      <c r="G91" s="108"/>
+      <c r="H91" s="31">
+        <f>D105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="107" t="s">
         <v>153</v>
       </c>
-      <c r="B96" s="109"/>
-      <c r="C96" s="108"/>
-      <c r="D96" s="108"/>
-      <c r="E96" s="108"/>
-      <c r="F96" s="108"/>
-      <c r="G96" s="108"/>
-      <c r="H96" s="131">
-        <f>-H69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A97" s="110" t="s">
+      <c r="B92" s="109"/>
+      <c r="C92" s="108"/>
+      <c r="D92" s="108"/>
+      <c r="E92" s="108"/>
+      <c r="F92" s="108"/>
+      <c r="G92" s="108"/>
+      <c r="H92" s="131">
+        <f>-H65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A93" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="B97" s="111"/>
-      <c r="C97" s="111"/>
-      <c r="D97" s="111"/>
-      <c r="E97" s="111"/>
-      <c r="F97" s="111"/>
-      <c r="G97" s="111"/>
-      <c r="H97" s="112">
-        <f>SUM(H92:H96)</f>
-        <v>-102888.21226353198</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="99" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="216" t="s">
+      <c r="B93" s="111"/>
+      <c r="C93" s="111"/>
+      <c r="D93" s="111"/>
+      <c r="E93" s="111"/>
+      <c r="F93" s="111"/>
+      <c r="G93" s="111"/>
+      <c r="H93" s="112">
+        <f>SUM(H88:H92)</f>
+        <v>756538.90773646813</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="190" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="217"/>
-      <c r="C99" s="217"/>
-      <c r="D99" s="217"/>
-      <c r="E99" s="217"/>
-      <c r="F99" s="217"/>
-      <c r="G99" s="217"/>
-      <c r="H99" s="218"/>
-    </row>
-    <row r="100" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="113" t="s">
+      <c r="B95" s="191"/>
+      <c r="C95" s="191"/>
+      <c r="D95" s="191"/>
+      <c r="E95" s="191"/>
+      <c r="F95" s="191"/>
+      <c r="G95" s="191"/>
+      <c r="H95" s="192"/>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="B100" s="113"/>
-      <c r="C100" s="113"/>
-      <c r="D100" s="113"/>
-      <c r="E100" s="113"/>
-      <c r="F100" s="113"/>
-      <c r="G100" s="113"/>
-      <c r="H100" s="114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="115"/>
-      <c r="C101" s="108"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="18"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="116"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="18"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B96" s="113"/>
+      <c r="C96" s="113"/>
+      <c r="D96" s="113"/>
+      <c r="E96" s="113"/>
+      <c r="F96" s="113"/>
+      <c r="G96" s="113"/>
+      <c r="H96" s="114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="6"/>
+      <c r="B97" s="115"/>
+      <c r="C97" s="108"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="18"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="6"/>
+      <c r="B98" s="116"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="18"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="18"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="B100" s="117"/>
+      <c r="C100" s="117"/>
+      <c r="D100" s="117"/>
+      <c r="E100" s="117"/>
+      <c r="F100" s="117"/>
+      <c r="G100" s="117"/>
+      <c r="H100" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="B102" s="126"/>
+      <c r="C102" s="126"/>
+      <c r="D102" s="126"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="18"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="117" t="s">
-        <v>132</v>
-      </c>
-      <c r="B104" s="117"/>
-      <c r="C104" s="117"/>
-      <c r="D104" s="117"/>
-      <c r="E104" s="117"/>
-      <c r="F104" s="117"/>
-      <c r="G104" s="117"/>
-      <c r="H104" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="125" t="s">
-        <v>145</v>
-      </c>
-      <c r="B106" s="126"/>
-      <c r="C106" s="126"/>
-      <c r="D106" s="126"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="18"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D103" s="18"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="18"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="119" t="s">
+        <v>100</v>
+      </c>
+      <c r="B105" s="126"/>
+      <c r="C105" s="126"/>
+      <c r="D105" s="136">
+        <f>SUM(D103:D104)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="125" t="s">
+        <v>146</v>
+      </c>
+      <c r="B107" s="119"/>
+      <c r="C107" s="119"/>
+      <c r="D107" s="119"/>
+    </row>
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="18"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="119" t="s">
+      <c r="B108" s="99"/>
+      <c r="C108" s="99"/>
+      <c r="D108" s="121"/>
+    </row>
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="127"/>
+    </row>
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="127"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="127"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="126"/>
-      <c r="C109" s="126"/>
-      <c r="D109" s="136">
-        <f>SUM(D107:D108)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="125" t="s">
-        <v>146</v>
-      </c>
-      <c r="B111" s="119"/>
-      <c r="C111" s="119"/>
-      <c r="D111" s="119"/>
-    </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="99"/>
-      <c r="C112" s="99"/>
-      <c r="D112" s="121"/>
-    </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="127"/>
-    </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="127"/>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="127"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="120" t="s">
-        <v>100</v>
-      </c>
-      <c r="B116" s="120"/>
-      <c r="C116" s="219">
-        <f>SUM(D112:D115)</f>
-        <v>0</v>
-      </c>
-      <c r="D116" s="220"/>
+      <c r="B112" s="120"/>
+      <c r="C112" s="193">
+        <f>SUM(D108:D111)</f>
+        <v>0</v>
+      </c>
+      <c r="D112" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="A66:G66"/>
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A88:H89"/>
+    <mergeCell ref="A84:H85"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="E3:H3"/>
@@ -5808,11 +5722,27 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A60:H60"/>
     <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A80:G80"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
+++ b/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3E4C24-C17A-454C-8D07-124B384FBBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B59582E-ADA9-4FF7-B475-F929478080A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
     <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$115</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="181">
   <si>
     <t xml:space="preserve">Banco Comafi:
 Cons. Prop. Edif. Yrigoyen 9115 CUIT: 30-56975974-5
@@ -529,15 +529,9 @@
     <t>Macarena perez ruiz</t>
   </si>
   <si>
-    <t>Debito 09/06</t>
-  </si>
-  <si>
     <t>Sueldo encargada - Jimena Borges y SAC</t>
   </si>
   <si>
-    <t>macarena en febrero no le contamos un pago de 109277 , por lo que viene arrastrando una deuda inexistente, hay que corregirlo</t>
-  </si>
-  <si>
     <t>VTO: 14/08</t>
   </si>
   <si>
@@ -566,6 +560,18 @@
   </si>
   <si>
     <t>AUMENTADOS EN juli 2025</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados</t>
+  </si>
+  <si>
+    <t>Debito 04/07</t>
+  </si>
+  <si>
+    <t>Debito 23/07</t>
+  </si>
+  <si>
+    <t>Debito 10/07</t>
   </si>
 </sst>
 </file>
@@ -813,7 +819,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -868,12 +874,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="43">
     <border>
@@ -1600,7 +1600,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1642,9 +1641,7 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1675,10 +1672,13 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="16" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1709,6 +1709,87 @@
     <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1778,12 +1859,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1801,81 +1876,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2368,7 +2368,7 @@
       <c r="H3" s="174"/>
       <c r="I3" s="174"/>
       <c r="J3" s="175"/>
-      <c r="K3" s="147"/>
+      <c r="K3" s="146"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -2381,13 +2381,13 @@
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="145"/>
+      <c r="E4" s="144"/>
       <c r="F4" s="176"/>
       <c r="G4" s="177"/>
       <c r="H4" s="177"/>
       <c r="I4" s="177"/>
       <c r="J4" s="178"/>
-      <c r="K4" s="147"/>
+      <c r="K4" s="146"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C5" s="182"/>
       <c r="D5" s="16"/>
-      <c r="E5" s="146">
+      <c r="E5" s="145">
         <v>0</v>
       </c>
       <c r="F5" s="176"/>
@@ -2409,7 +2409,7 @@
       <c r="H5" s="177"/>
       <c r="I5" s="177"/>
       <c r="J5" s="178"/>
-      <c r="K5" s="148"/>
+      <c r="K5" s="147"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -2422,13 +2422,13 @@
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
-      <c r="E6" s="145"/>
+      <c r="E6" s="144"/>
       <c r="F6" s="179"/>
       <c r="G6" s="180"/>
       <c r="H6" s="180"/>
       <c r="I6" s="180"/>
       <c r="J6" s="181"/>
-      <c r="K6" s="148"/>
+      <c r="K6" s="147"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -2518,7 +2518,7 @@
       <c r="F9" s="31">
         <v>540000</v>
       </c>
-      <c r="G9" s="150">
+      <c r="G9" s="172">
         <f>F9</f>
         <v>540000</v>
       </c>
@@ -2569,7 +2569,7 @@
       <c r="F10" s="31">
         <v>144000</v>
       </c>
-      <c r="G10" s="151">
+      <c r="G10" s="168">
         <f>F10</f>
         <v>144000</v>
       </c>
@@ -2618,10 +2618,10 @@
         <v>2.5600000000000001E-2</v>
       </c>
       <c r="F11" s="31">
-        <v>127948.34067113716</v>
-      </c>
-      <c r="G11" s="151">
-        <v>128000</v>
+        <v>130507</v>
+      </c>
+      <c r="G11" s="168">
+        <v>130508</v>
       </c>
       <c r="H11" s="32">
         <f t="shared" si="0"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="J11" s="32">
         <f t="shared" si="2"/>
-        <v>51.659328862835537</v>
+        <v>1</v>
       </c>
       <c r="K11" s="32"/>
       <c r="L11" s="33">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="N11" s="34">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>127948.34067113716</v>
+        <v>127999</v>
       </c>
       <c r="O11" s="35">
         <f t="shared" si="6"/>
-        <v>130507.3074845599</v>
+        <v>130558.98</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
       <c r="F12" s="31">
         <v>107499.99999999999</v>
       </c>
-      <c r="G12" s="151">
+      <c r="G12" s="168">
         <f>F12</f>
         <v>107499.99999999999</v>
       </c>
@@ -2724,7 +2724,7 @@
       <c r="F13" s="31">
         <v>88230</v>
       </c>
-      <c r="G13" s="151">
+      <c r="G13" s="168">
         <f>F13</f>
         <v>88230</v>
       </c>
@@ -2773,10 +2773,10 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F14" s="31">
-        <v>138866.92475261347</v>
-      </c>
-      <c r="G14" s="151">
-        <v>139000</v>
+        <v>139366.92475261347</v>
+      </c>
+      <c r="G14" s="168">
+        <v>140000</v>
       </c>
       <c r="H14" s="32">
         <f t="shared" si="0"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="J14" s="32">
         <f t="shared" si="2"/>
-        <v>133.07524738652864</v>
+        <v>633.07524738652864</v>
       </c>
       <c r="K14" s="32"/>
       <c r="L14" s="33">
@@ -2801,11 +2801,11 @@
       </c>
       <c r="N14" s="34">
         <f t="shared" si="5"/>
-        <v>139366.92475261347</v>
+        <v>138866.92475261347</v>
       </c>
       <c r="O14" s="35">
         <f t="shared" si="6"/>
-        <v>142154.26324766575</v>
+        <v>141644.26324766575</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2825,7 +2825,7 @@
       <c r="F15" s="31">
         <v>124499.99999999999</v>
       </c>
-      <c r="G15" s="151">
+      <c r="G15" s="168">
         <f>F15</f>
         <v>124499.99999999999</v>
       </c>
@@ -2878,7 +2878,7 @@
       <c r="F16" s="31">
         <v>107499.99999999999</v>
       </c>
-      <c r="G16" s="151">
+      <c r="G16" s="168">
         <f>F16</f>
         <v>107499.99999999999</v>
       </c>
@@ -2929,18 +2929,18 @@
         <v>1.3599999999999999E-2</v>
       </c>
       <c r="F17" s="31">
-        <v>288367.27175903256</v>
-      </c>
-      <c r="G17" s="151">
-        <v>100000</v>
+        <v>262018.28991180353</v>
+      </c>
+      <c r="G17" s="168">
+        <v>50000</v>
       </c>
       <c r="H17" s="32">
         <f t="shared" si="0"/>
-        <v>188367.27175903256</v>
+        <v>212018.28991180353</v>
       </c>
       <c r="I17" s="32">
         <f t="shared" si="1"/>
-        <v>5651.0181527709765</v>
+        <v>6360.5486973541056</v>
       </c>
       <c r="J17" s="32">
         <f t="shared" si="2"/>
@@ -2957,11 +2957,11 @@
       </c>
       <c r="N17" s="34">
         <f t="shared" si="5"/>
-        <v>262018.28991180353</v>
+        <v>286378.8386091576</v>
       </c>
       <c r="O17" s="35">
         <f t="shared" si="6"/>
-        <v>267258.6557100396</v>
+        <v>292106.41538134078</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2983,7 +2983,7 @@
       <c r="F18" s="31">
         <v>139500</v>
       </c>
-      <c r="G18" s="151">
+      <c r="G18" s="168">
         <f t="shared" ref="G18:G23" si="7">F18</f>
         <v>139500</v>
       </c>
@@ -3027,7 +3027,7 @@
       <c r="C19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="166" t="s">
+      <c r="D19" s="163" t="s">
         <v>162</v>
       </c>
       <c r="E19" s="30">
@@ -3036,7 +3036,7 @@
       <c r="F19" s="31">
         <v>124499.99999999999</v>
       </c>
-      <c r="G19" s="151">
+      <c r="G19" s="168">
         <f t="shared" si="7"/>
         <v>124499.99999999999</v>
       </c>
@@ -3085,18 +3085,16 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F20" s="31">
-        <v>167547.32772576308</v>
-      </c>
-      <c r="G20" s="151">
-        <v>165000</v>
-      </c>
+        <v>186123.747557536</v>
+      </c>
+      <c r="G20" s="149"/>
       <c r="H20" s="32">
         <f t="shared" si="0"/>
-        <v>2547.3277257630834</v>
+        <v>186123.747557536</v>
       </c>
       <c r="I20" s="32">
         <f t="shared" si="1"/>
-        <v>76.419831772892493</v>
+        <v>5583.7124267260797</v>
       </c>
       <c r="J20" s="32">
         <f t="shared" si="2"/>
@@ -3113,11 +3111,11 @@
       </c>
       <c r="N20" s="34">
         <f t="shared" si="5"/>
-        <v>186123.747557536</v>
+        <v>375207.45998426212</v>
       </c>
       <c r="O20" s="35">
         <f t="shared" si="6"/>
-        <v>189846.22250868671</v>
+        <v>382711.60918394738</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3137,19 +3135,18 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F21" s="31">
-        <v>136710</v>
-      </c>
-      <c r="G21" s="151">
-        <f>F21</f>
-        <v>136710</v>
+        <v>142290</v>
+      </c>
+      <c r="G21" s="168">
+        <v>139500</v>
       </c>
       <c r="H21" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2790</v>
       </c>
       <c r="I21" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>83.7</v>
       </c>
       <c r="J21" s="32">
         <f t="shared" si="2"/>
@@ -3166,11 +3163,11 @@
       </c>
       <c r="N21" s="34">
         <f t="shared" si="5"/>
-        <v>139500</v>
+        <v>142373.70000000001</v>
       </c>
       <c r="O21" s="35">
         <f t="shared" si="6"/>
-        <v>142290</v>
+        <v>145221.174</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3190,7 +3187,7 @@
       <c r="F22" s="31">
         <v>124499.99999999999</v>
       </c>
-      <c r="G22" s="151">
+      <c r="G22" s="168">
         <f t="shared" si="7"/>
         <v>124499.99999999999</v>
       </c>
@@ -3243,7 +3240,7 @@
       <c r="F23" s="31">
         <v>183500.00000000003</v>
       </c>
-      <c r="G23" s="151">
+      <c r="G23" s="168">
         <f t="shared" si="7"/>
         <v>183500.00000000003</v>
       </c>
@@ -3294,18 +3291,18 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F24" s="31">
-        <v>230987.89310901312</v>
-      </c>
-      <c r="G24" s="151">
+        <v>233732.52990228351</v>
+      </c>
+      <c r="G24" s="168">
         <v>139500</v>
       </c>
       <c r="H24" s="32">
         <f t="shared" si="0"/>
-        <v>91487.893109013123</v>
+        <v>94232.52990228351</v>
       </c>
       <c r="I24" s="32">
         <f t="shared" si="1"/>
-        <v>2744.6367932703934</v>
+        <v>2826.9758970685052</v>
       </c>
       <c r="J24" s="32">
         <f t="shared" si="2"/>
@@ -3322,11 +3319,11 @@
       </c>
       <c r="N24" s="34">
         <f t="shared" si="5"/>
-        <v>233732.52990228351</v>
+        <v>236559.50579935202</v>
       </c>
       <c r="O24" s="35">
         <f t="shared" si="6"/>
-        <v>238407.18050032918</v>
+        <v>241290.69591533905</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3344,11 +3341,11 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F25" s="31">
-        <v>122060.77512699997</v>
-      </c>
-      <c r="G25" s="151">
-        <f>122061</f>
-        <v>122061</v>
+        <v>124499.77512699996</v>
+      </c>
+      <c r="G25" s="168">
+        <f>126990</f>
+        <v>126990</v>
       </c>
       <c r="H25" s="32">
         <f t="shared" si="0"/>
@@ -3360,7 +3357,7 @@
       </c>
       <c r="J25" s="32">
         <f t="shared" si="2"/>
-        <v>0.22487300002831034</v>
+        <v>2490.2248730000429</v>
       </c>
       <c r="K25" s="32"/>
       <c r="L25" s="33">
@@ -3373,11 +3370,11 @@
       </c>
       <c r="N25" s="34">
         <f t="shared" si="5"/>
-        <v>124499.77512699996</v>
+        <v>122009.77512699994</v>
       </c>
       <c r="O25" s="35">
         <f t="shared" si="6"/>
-        <v>126989.77062953995</v>
+        <v>124449.97062953994</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3395,19 +3392,16 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F26" s="31">
-        <v>179516.58835500007</v>
-      </c>
-      <c r="G26" s="151">
-        <f>F26</f>
-        <v>179516.58835500007</v>
-      </c>
+        <v>183500.00000000003</v>
+      </c>
+      <c r="G26" s="149"/>
       <c r="H26" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="I26" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5505.0000000000009</v>
       </c>
       <c r="J26" s="32">
         <f t="shared" si="2"/>
@@ -3424,11 +3418,11 @@
       </c>
       <c r="N26" s="34">
         <f t="shared" si="5"/>
-        <v>183500.00000000003</v>
+        <v>372505.00000000006</v>
       </c>
       <c r="O26" s="35">
         <f t="shared" si="6"/>
-        <v>187170.00000000003</v>
+        <v>379955.10000000003</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3448,7 +3442,7 @@
       <c r="F27" s="31">
         <v>139500</v>
       </c>
-      <c r="G27" s="151">
+      <c r="G27" s="168">
         <f>F27</f>
         <v>139500</v>
       </c>
@@ -3497,16 +3491,16 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F28" s="31">
-        <v>119333.61747973312</v>
-      </c>
-      <c r="G28" s="151"/>
+        <v>247413.62600412511</v>
+      </c>
+      <c r="G28" s="149"/>
       <c r="H28" s="54">
         <f t="shared" si="0"/>
-        <v>119333.61747973312</v>
+        <v>247413.62600412511</v>
       </c>
       <c r="I28" s="32">
         <f t="shared" si="1"/>
-        <v>3580.0085243919934</v>
+        <v>7422.4087801237529</v>
       </c>
       <c r="J28" s="32">
         <f t="shared" si="2"/>
@@ -3523,11 +3517,11 @@
       </c>
       <c r="N28" s="34">
         <f t="shared" si="5"/>
-        <v>247413.62600412511</v>
+        <v>379336.03478424886</v>
       </c>
       <c r="O28" s="35">
         <f t="shared" si="6"/>
-        <v>252361.89852420762</v>
+        <v>386922.75547993381</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3547,11 +3541,11 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F29" s="31">
-        <v>179000.00000000006</v>
-      </c>
-      <c r="G29" s="151">
+        <v>183500.00000000003</v>
+      </c>
+      <c r="G29" s="168">
         <f>F29</f>
-        <v>179000.00000000006</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="H29" s="32">
         <f t="shared" si="0"/>
@@ -3602,7 +3596,7 @@
       <c r="F30" s="31">
         <v>139500</v>
       </c>
-      <c r="G30" s="151">
+      <c r="G30" s="168">
         <f>F30</f>
         <v>139500</v>
       </c>
@@ -3651,16 +3645,16 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F31" s="31">
-        <v>390587.31552705751</v>
-      </c>
-      <c r="G31" s="151"/>
+        <v>526804.93499286915</v>
+      </c>
+      <c r="G31" s="149"/>
       <c r="H31" s="32">
         <f t="shared" si="0"/>
-        <v>390587.31552705751</v>
+        <v>526804.93499286915</v>
       </c>
       <c r="I31" s="32">
         <f t="shared" si="1"/>
-        <v>11717.619465811726</v>
+        <v>15804.148049786074</v>
       </c>
       <c r="J31" s="32">
         <f t="shared" si="2"/>
@@ -3677,11 +3671,11 @@
       </c>
       <c r="N31" s="34">
         <f t="shared" si="5"/>
-        <v>526804.93499286915</v>
+        <v>667109.08304265526</v>
       </c>
       <c r="O31" s="35">
         <f t="shared" si="6"/>
-        <v>537341.03369272652</v>
+        <v>680451.26470350835</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -3701,16 +3695,18 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F32" s="18">
-        <v>474834.42272649496</v>
-      </c>
-      <c r="G32" s="151"/>
+        <v>672579.4554082898</v>
+      </c>
+      <c r="G32" s="168">
+        <v>351176</v>
+      </c>
       <c r="H32" s="32">
         <f t="shared" si="0"/>
-        <v>474834.42272649496</v>
+        <v>321403.4554082898</v>
       </c>
       <c r="I32" s="32">
         <f t="shared" si="1"/>
-        <v>14245.032681794848</v>
+        <v>9642.1036622486936</v>
       </c>
       <c r="J32" s="32">
         <f t="shared" si="2"/>
@@ -3727,11 +3723,11 @@
       </c>
       <c r="N32" s="34">
         <f t="shared" si="5"/>
-        <v>672579.4554082898</v>
+        <v>514545.5590705385</v>
       </c>
       <c r="O32" s="35">
         <f t="shared" si="6"/>
-        <v>686031.04451645561</v>
+        <v>524836.47025194927</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -3751,11 +3747,11 @@
       <c r="E33" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="F33" s="127">
-        <v>130777.73864328716</v>
-      </c>
-      <c r="G33" s="151">
-        <v>135000</v>
+      <c r="F33" s="126">
+        <v>135277.73864328716</v>
+      </c>
+      <c r="G33" s="168">
+        <v>135500</v>
       </c>
       <c r="H33" s="32">
         <f t="shared" si="0"/>
@@ -3767,7 +3763,7 @@
       </c>
       <c r="J33" s="32">
         <f t="shared" si="2"/>
-        <v>4222.2613567128428</v>
+        <v>222.26135671284283</v>
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="33">
@@ -3780,11 +3776,11 @@
       </c>
       <c r="N33" s="34">
         <f t="shared" si="5"/>
-        <v>135277.73864328716</v>
+        <v>139277.73864328716</v>
       </c>
       <c r="O33" s="35">
         <f t="shared" si="6"/>
-        <v>137983.29341615291</v>
+        <v>142063.29341615291</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -3807,7 +3803,7 @@
       <c r="F34" s="18">
         <v>124499.99999999999</v>
       </c>
-      <c r="G34" s="122">
+      <c r="G34" s="169">
         <f>F34</f>
         <v>124499.99999999999</v>
       </c>
@@ -3857,11 +3853,11 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F35" s="18">
-        <v>183500.08858581958</v>
-      </c>
-      <c r="G35" s="151">
+        <v>183500.00000000003</v>
+      </c>
+      <c r="G35" s="168">
         <f>F35</f>
-        <v>183500.08858581958</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="H35" s="32">
         <f t="shared" si="0"/>
@@ -3914,7 +3910,7 @@
       <c r="F36" s="18">
         <v>139500</v>
       </c>
-      <c r="G36" s="122">
+      <c r="G36" s="169">
         <f>F36</f>
         <v>139500</v>
       </c>
@@ -3968,7 +3964,7 @@
       <c r="F37" s="18">
         <v>124499.99999999999</v>
       </c>
-      <c r="G37" s="122">
+      <c r="G37" s="169">
         <f>F37</f>
         <v>124499.99999999999</v>
       </c>
@@ -4020,18 +4016,19 @@
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F38" s="18">
-        <v>344673.7297766995</v>
+        <v>351788.94167000049</v>
       </c>
       <c r="G38" s="169">
-        <v>107500</v>
+        <f>F38</f>
+        <v>351788.94167000049</v>
       </c>
       <c r="H38" s="32">
         <f t="shared" si="0"/>
-        <v>237173.7297766995</v>
+        <v>0</v>
       </c>
       <c r="I38" s="32">
         <f t="shared" si="1"/>
-        <v>7115.2118933009851</v>
+        <v>0</v>
       </c>
       <c r="J38" s="32">
         <f t="shared" si="2"/>
@@ -4048,11 +4045,11 @@
       </c>
       <c r="N38" s="34">
         <f t="shared" si="5"/>
-        <v>351788.94167000049</v>
+        <v>107499.99999999999</v>
       </c>
       <c r="O38" s="35">
         <f t="shared" si="6"/>
-        <v>358824.72050340049</v>
+        <v>109649.99999999999</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -4075,7 +4072,7 @@
       <c r="F39" s="18">
         <v>68000</v>
       </c>
-      <c r="G39" s="122">
+      <c r="G39" s="169">
         <f>F39</f>
         <v>68000</v>
       </c>
@@ -4125,19 +4122,18 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F40" s="18">
-        <v>139500</v>
-      </c>
-      <c r="G40" s="122">
-        <f>F40</f>
+        <v>142290</v>
+      </c>
+      <c r="G40" s="169">
         <v>139500</v>
       </c>
       <c r="H40" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2790</v>
       </c>
       <c r="I40" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>83.7</v>
       </c>
       <c r="J40" s="32">
         <f t="shared" si="2"/>
@@ -4154,11 +4150,11 @@
       </c>
       <c r="N40" s="34">
         <f t="shared" si="5"/>
-        <v>139500</v>
+        <v>142373.70000000001</v>
       </c>
       <c r="O40" s="35">
         <f t="shared" si="6"/>
-        <v>142290</v>
+        <v>145221.174</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
@@ -4181,7 +4177,7 @@
       <c r="F41" s="18">
         <v>124499.99999999999</v>
       </c>
-      <c r="G41" s="122">
+      <c r="G41" s="169">
         <f>F41</f>
         <v>124499.99999999999</v>
       </c>
@@ -4233,11 +4229,11 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F42" s="60">
-        <v>183500.43615587871</v>
-      </c>
-      <c r="G42" s="152">
+        <v>183500.00000000003</v>
+      </c>
+      <c r="G42" s="170">
         <f>F42</f>
-        <v>183500.43615587871</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="H42" s="32">
         <f t="shared" si="0"/>
@@ -4280,25 +4276,25 @@
       </c>
       <c r="F43" s="65">
         <f>SUM(F9:F42)</f>
-        <v>6081442.4703945303</v>
-      </c>
-      <c r="G43" s="144">
+        <v>6572422.9639698081</v>
+      </c>
+      <c r="G43" s="143">
         <f t="shared" ref="G43:N43" si="9">SUM(G9:G42)</f>
-        <v>4581518.1130966982</v>
+        <v>4798692.9416700006</v>
       </c>
       <c r="H43" s="66">
         <f t="shared" si="9"/>
-        <v>1504331.578103794</v>
+        <v>1777076.5837769073</v>
       </c>
       <c r="I43" s="67">
         <f t="shared" si="9"/>
-        <v>45129.94734311381</v>
+        <v>53312.29751330721</v>
       </c>
       <c r="J43" s="68">
         <f t="shared" si="9"/>
-        <v>4407.2208059622353</v>
-      </c>
-      <c r="K43" s="130">
+        <v>3346.5614770994143</v>
+      </c>
+      <c r="K43" s="129">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -4312,15 +4308,13 @@
       </c>
       <c r="N43" s="65">
         <f t="shared" si="9"/>
-        <v>6562554.304640945</v>
+        <v>6844542.3198131155</v>
       </c>
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G45" s="170" t="s">
-        <v>168</v>
-      </c>
+      <c r="G45" s="171"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4336,7 +4330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -4362,23 +4356,23 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="225"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="227"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="196"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="228" t="s">
+      <c r="E3" s="197" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="228"/>
-      <c r="G3" s="228"/>
-      <c r="H3" s="229"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="198"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
@@ -4423,13 +4417,13 @@
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H8" s="81"/>
     </row>
@@ -4446,16 +4440,16 @@
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="230" t="s">
+      <c r="A10" s="199" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="231"/>
-      <c r="C10" s="231"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="231"/>
-      <c r="F10" s="231"/>
-      <c r="G10" s="231"/>
-      <c r="H10" s="232"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
+      <c r="D10" s="200"/>
+      <c r="E10" s="200"/>
+      <c r="F10" s="200"/>
+      <c r="G10" s="200"/>
+      <c r="H10" s="201"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
@@ -4468,574 +4462,578 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="233" t="s">
+      <c r="A12" s="202" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="233"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="233"/>
-      <c r="E12" s="233"/>
-      <c r="F12" s="233"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="233"/>
+      <c r="B12" s="202"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="202"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="202"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="153" t="s">
-        <v>167</v>
-      </c>
-      <c r="B13" s="154"/>
-      <c r="C13" s="154"/>
-      <c r="D13" s="154"/>
-      <c r="E13" s="154"/>
-      <c r="F13" s="154"/>
-      <c r="G13" s="154"/>
-      <c r="H13" s="172">
-        <v>1552501</v>
+      <c r="A13" s="150" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="151"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="166">
+        <v>1043827.2</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="153" t="s">
+      <c r="A14" s="150" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="154"/>
-      <c r="G14" s="154"/>
-      <c r="H14" s="172">
-        <v>0.97</v>
+      <c r="B14" s="151"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="151"/>
+      <c r="H14" s="166">
+        <v>0.21</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="152" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="155"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="155"/>
-      <c r="E15" s="155"/>
-      <c r="F15" s="155"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="172">
-        <f>-337668.97</f>
-        <v>-337668.97</v>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
+      <c r="E15" s="152"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="152"/>
+      <c r="H15" s="166">
+        <v>-227032.41</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="156" t="s">
+      <c r="A16" s="153" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="157"/>
-      <c r="C16" s="157"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
-      <c r="F16" s="157"/>
-      <c r="G16" s="157"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="154"/>
       <c r="H16" s="84">
         <f>SUM(H13:H15)</f>
-        <v>1214833</v>
+        <v>816794.99999999988</v>
       </c>
       <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="234" t="s">
+      <c r="A17" s="203" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="234"/>
-      <c r="C17" s="234"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
-      <c r="F17" s="234"/>
-      <c r="G17" s="234"/>
-      <c r="H17" s="234"/>
+      <c r="B17" s="203"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="203"/>
+      <c r="H17" s="203"/>
     </row>
     <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="B18" s="154"/>
-      <c r="C18" s="154"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="154"/>
-      <c r="G18" s="154"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="151"/>
       <c r="H18" s="82"/>
     </row>
     <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="85" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="154"/>
-      <c r="C19" s="154"/>
-      <c r="D19" s="154"/>
-      <c r="E19" s="154"/>
-      <c r="F19" s="154"/>
-      <c r="G19" s="154"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
       <c r="H19" s="82"/>
     </row>
     <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="154"/>
-      <c r="B20" s="154"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="154"/>
-      <c r="G20" s="154"/>
+      <c r="A20" s="151"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="151"/>
       <c r="H20" s="82"/>
     </row>
     <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="154" t="s">
+      <c r="A21" s="151" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="154"/>
-      <c r="C21" s="154"/>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="154"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="151"/>
+      <c r="G21" s="151"/>
       <c r="H21" s="82">
         <f>SUM(H18:H20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="234" t="s">
+      <c r="A22" s="203" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="234"/>
-      <c r="C22" s="234"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="234"/>
-      <c r="F22" s="234"/>
-      <c r="G22" s="234"/>
-      <c r="H22" s="234"/>
+      <c r="B22" s="203"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="203"/>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="153" t="s">
+      <c r="A23" s="150" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="158" t="s">
-        <v>176</v>
-      </c>
-      <c r="C23" s="158"/>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
-      <c r="G23" s="154"/>
-      <c r="H23" s="171">
+      <c r="B23" s="155" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="155"/>
+      <c r="D23" s="155"/>
+      <c r="E23" s="155"/>
+      <c r="F23" s="155"/>
+      <c r="G23" s="151"/>
+      <c r="H23" s="166">
         <v>137308.57</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="153" t="s">
+      <c r="A24" s="150" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="154" t="str">
+      <c r="B24" s="151" t="str">
         <f>B23</f>
         <v>Debito 14/07</v>
       </c>
-      <c r="C24" s="158"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="154"/>
-      <c r="H24" s="171">
+      <c r="C24" s="155"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="166">
         <v>69862.55</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="153" t="s">
+      <c r="A25" s="150" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="154" t="str">
+      <c r="B25" s="151" t="str">
         <f>B24</f>
         <v>Debito 14/07</v>
       </c>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="154"/>
-      <c r="H25" s="171">
+      <c r="C25" s="155"/>
+      <c r="D25" s="155"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="155"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="166">
         <v>7762.51</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="153" t="s">
+      <c r="A26" s="150" t="s">
         <v>157</v>
       </c>
-      <c r="B26" s="154" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="158"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="158"/>
-      <c r="G26" s="154"/>
-      <c r="H26" s="171">
+      <c r="B26" s="151" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="155"/>
+      <c r="D26" s="155"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="155"/>
+      <c r="G26" s="151"/>
+      <c r="H26" s="166">
         <v>714361.65</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="153"/>
-      <c r="B27" s="154"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="158"/>
-      <c r="G27" s="154"/>
+      <c r="A27" s="150"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="155"/>
+      <c r="D27" s="155"/>
+      <c r="E27" s="155"/>
+      <c r="F27" s="155"/>
+      <c r="G27" s="151"/>
       <c r="H27" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="157" t="s">
+      <c r="A28" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="157"/>
-      <c r="C28" s="157"/>
-      <c r="D28" s="157"/>
-      <c r="E28" s="157"/>
-      <c r="F28" s="157"/>
-      <c r="G28" s="157"/>
+      <c r="B28" s="154"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
       <c r="H28" s="84">
         <f>SUM(H23:H27)</f>
         <v>929295.28</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="224" t="s">
+      <c r="A29" s="193" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="224"/>
-      <c r="C29" s="224"/>
-      <c r="D29" s="224"/>
-      <c r="E29" s="224"/>
-      <c r="F29" s="224"/>
-      <c r="G29" s="224"/>
-      <c r="H29" s="224"/>
+      <c r="B29" s="193"/>
+      <c r="C29" s="193"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="193"/>
+      <c r="F29" s="193"/>
+      <c r="G29" s="193"/>
+      <c r="H29" s="193"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="154" t="s">
+      <c r="A30" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="154"/>
-      <c r="C30" s="154"/>
-      <c r="D30" s="154"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="154"/>
-      <c r="G30" s="154"/>
-      <c r="H30" s="171">
-        <v>200.93</v>
+      <c r="B30" s="151"/>
+      <c r="C30" s="151"/>
+      <c r="D30" s="151"/>
+      <c r="E30" s="151" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" s="151"/>
+      <c r="G30" s="151"/>
+      <c r="H30" s="166">
+        <f>4203.98+290.93+200.93</f>
+        <v>4695.84</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="154" t="s">
+      <c r="A31" s="151" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="154" t="s">
+      <c r="B31" s="151" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="154"/>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="82">
-        <v>1229017.1599999999</v>
+      <c r="C31" s="151"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="151" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" s="151"/>
+      <c r="G31" s="151"/>
+      <c r="H31" s="166">
+        <v>1073579.78</v>
       </c>
       <c r="I31" s="87"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="159" t="s">
+      <c r="A32" s="156" t="s">
         <v>111</v>
       </c>
-      <c r="B32" s="154" t="s">
+      <c r="B32" s="151" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="154"/>
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="171">
+      <c r="C32" s="151"/>
+      <c r="D32" s="151"/>
+      <c r="E32" s="151"/>
+      <c r="F32" s="151"/>
+      <c r="G32" s="151"/>
+      <c r="H32" s="166">
         <v>203720.4</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="157" t="s">
+      <c r="A33" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="157"/>
-      <c r="C33" s="157"/>
-      <c r="D33" s="157"/>
-      <c r="E33" s="157"/>
-      <c r="F33" s="157"/>
-      <c r="G33" s="157"/>
-      <c r="H33" s="160">
+      <c r="B33" s="154"/>
+      <c r="C33" s="154"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="157">
         <f>SUM(H30:H32)</f>
-        <v>1432938.4899999998</v>
+        <v>1281996.02</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="224" t="s">
+      <c r="A34" s="193" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="224"/>
-      <c r="C34" s="224"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="224"/>
-      <c r="F34" s="224"/>
-      <c r="G34" s="224"/>
-      <c r="H34" s="224"/>
+      <c r="B34" s="193"/>
+      <c r="C34" s="193"/>
+      <c r="D34" s="193"/>
+      <c r="E34" s="193"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="193"/>
+      <c r="H34" s="193"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="85"/>
-      <c r="B35" s="161"/>
-      <c r="C35" s="154"/>
-      <c r="D35" s="154"/>
-      <c r="E35" s="154"/>
-      <c r="F35" s="154"/>
-      <c r="G35" s="154"/>
+      <c r="B35" s="158"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="151"/>
+      <c r="E35" s="151"/>
+      <c r="F35" s="151"/>
+      <c r="G35" s="151"/>
       <c r="H35" s="82"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="85" t="s">
         <v>158</v>
       </c>
-      <c r="B36" s="161"/>
-      <c r="C36" s="154"/>
-      <c r="D36" s="154"/>
-      <c r="E36" s="154"/>
-      <c r="F36" s="154"/>
-      <c r="G36" s="154"/>
-      <c r="H36" s="171">
+      <c r="B36" s="158"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="151"/>
+      <c r="E36" s="151"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="151"/>
+      <c r="H36" s="166">
         <v>140000</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="85" t="s">
-        <v>175</v>
-      </c>
-      <c r="B37" s="162"/>
+        <v>173</v>
+      </c>
+      <c r="B37" s="159"/>
       <c r="C37" s="85"/>
       <c r="D37" s="85"/>
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="171">
+      <c r="H37" s="166">
         <v>40000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
     <row r="38" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="183" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" s="184"/>
-      <c r="C38" s="184"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
-      <c r="F38" s="184"/>
-      <c r="G38" s="185"/>
-      <c r="H38" s="171">
+      <c r="A38" s="210" t="s">
+        <v>175</v>
+      </c>
+      <c r="B38" s="211"/>
+      <c r="C38" s="211"/>
+      <c r="D38" s="211"/>
+      <c r="E38" s="211"/>
+      <c r="F38" s="211"/>
+      <c r="G38" s="212"/>
+      <c r="H38" s="166">
         <v>32240.45</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="85" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" s="158"/>
+      <c r="C39" s="151"/>
+      <c r="D39" s="151"/>
+      <c r="E39" s="151"/>
+      <c r="F39" s="151"/>
+      <c r="G39" s="151"/>
+      <c r="H39" s="166">
+        <v>101540</v>
+      </c>
+      <c r="I39" s="148"/>
+      <c r="J39" s="213"/>
+    </row>
+    <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="210" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="161"/>
-      <c r="C39" s="154"/>
-      <c r="D39" s="154"/>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="154"/>
-      <c r="H39" s="171">
-        <v>101540</v>
-      </c>
-      <c r="I39" s="149"/>
-      <c r="J39" s="186"/>
-    </row>
-    <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="183" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40" s="184"/>
-      <c r="C40" s="184"/>
-      <c r="D40" s="184"/>
-      <c r="E40" s="184"/>
-      <c r="F40" s="184"/>
-      <c r="G40" s="185"/>
-      <c r="H40" s="171">
+      <c r="B40" s="211"/>
+      <c r="C40" s="211"/>
+      <c r="D40" s="211"/>
+      <c r="E40" s="211"/>
+      <c r="F40" s="211"/>
+      <c r="G40" s="212"/>
+      <c r="H40" s="166">
         <v>741000</v>
       </c>
-      <c r="J40" s="186"/>
+      <c r="J40" s="213"/>
     </row>
     <row r="41" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="B41" s="167"/>
-      <c r="C41" s="167"/>
-      <c r="D41" s="167"/>
-      <c r="E41" s="167"/>
-      <c r="F41" s="167"/>
-      <c r="G41" s="168"/>
-      <c r="H41" s="171">
+        <v>171</v>
+      </c>
+      <c r="B41" s="164"/>
+      <c r="C41" s="164"/>
+      <c r="D41" s="164"/>
+      <c r="E41" s="164"/>
+      <c r="F41" s="164"/>
+      <c r="G41" s="165"/>
+      <c r="H41" s="166">
         <v>36300</v>
       </c>
-      <c r="J41" s="186"/>
+      <c r="J41" s="213"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="154" t="s">
+      <c r="A42" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="154"/>
-      <c r="C42" s="154"/>
-      <c r="D42" s="154"/>
-      <c r="E42" s="154"/>
-      <c r="F42" s="154"/>
-      <c r="G42" s="154"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="151"/>
+      <c r="E42" s="151"/>
+      <c r="F42" s="151"/>
+      <c r="G42" s="151"/>
       <c r="H42" s="84">
         <f>SUM(H35:H41)</f>
         <v>1091080.45</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="224" t="s">
+      <c r="A43" s="193" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="224"/>
-      <c r="C43" s="224"/>
-      <c r="D43" s="224"/>
-      <c r="E43" s="224"/>
-      <c r="F43" s="224"/>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
+      <c r="B43" s="193"/>
+      <c r="C43" s="193"/>
+      <c r="D43" s="193"/>
+      <c r="E43" s="193"/>
+      <c r="F43" s="193"/>
+      <c r="G43" s="193"/>
+      <c r="H43" s="193"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="154" t="s">
+      <c r="A44" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="B44" s="154"/>
-      <c r="C44" s="154" t="s">
-        <v>171</v>
-      </c>
-      <c r="D44" s="163"/>
-      <c r="E44" s="154"/>
-      <c r="F44" s="154"/>
-      <c r="G44" s="154"/>
-      <c r="H44" s="171">
+      <c r="B44" s="151"/>
+      <c r="C44" s="151" t="s">
+        <v>169</v>
+      </c>
+      <c r="D44" s="160"/>
+      <c r="E44" s="151"/>
+      <c r="F44" s="151"/>
+      <c r="G44" s="151"/>
+      <c r="H44" s="166">
         <v>265000</v>
       </c>
       <c r="J44" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="164" t="s">
+      <c r="A45" s="161" t="s">
         <v>147</v>
       </c>
-      <c r="B45" s="154"/>
-      <c r="C45" s="204"/>
-      <c r="D45" s="205"/>
-      <c r="E45" s="165"/>
-      <c r="F45" s="158"/>
-      <c r="G45" s="154"/>
-      <c r="H45" s="171">
+      <c r="B45" s="151"/>
+      <c r="C45" s="231"/>
+      <c r="D45" s="232"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="151"/>
+      <c r="H45" s="166">
         <v>30000</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="154"/>
-      <c r="B46" s="154"/>
-      <c r="C46" s="158"/>
-      <c r="D46" s="158"/>
-      <c r="E46" s="158"/>
-      <c r="F46" s="158"/>
-      <c r="G46" s="154"/>
+      <c r="A46" s="151"/>
+      <c r="B46" s="151"/>
+      <c r="C46" s="155"/>
+      <c r="D46" s="155"/>
+      <c r="E46" s="155"/>
+      <c r="F46" s="155"/>
+      <c r="G46" s="151"/>
       <c r="H46" s="82"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="157" t="s">
+      <c r="A47" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="157"/>
-      <c r="C47" s="157"/>
-      <c r="D47" s="157"/>
-      <c r="E47" s="157"/>
-      <c r="F47" s="157"/>
-      <c r="G47" s="157"/>
+      <c r="B47" s="154"/>
+      <c r="C47" s="154"/>
+      <c r="D47" s="154"/>
+      <c r="E47" s="154"/>
+      <c r="F47" s="154"/>
+      <c r="G47" s="154"/>
       <c r="H47" s="84">
         <f>SUM(H44:H46)</f>
         <v>295000</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="235" t="s">
+      <c r="A48" s="204" t="s">
         <v>116</v>
       </c>
-      <c r="B48" s="236"/>
-      <c r="C48" s="236"/>
-      <c r="D48" s="236"/>
-      <c r="E48" s="236"/>
-      <c r="F48" s="236"/>
-      <c r="G48" s="236"/>
-      <c r="H48" s="237"/>
+      <c r="B48" s="205"/>
+      <c r="C48" s="205"/>
+      <c r="D48" s="205"/>
+      <c r="E48" s="205"/>
+      <c r="F48" s="205"/>
+      <c r="G48" s="205"/>
+      <c r="H48" s="206"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="154" t="s">
+      <c r="A49" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="B49" s="154"/>
-      <c r="C49" s="154"/>
-      <c r="D49" s="154"/>
-      <c r="E49" s="154"/>
-      <c r="F49" s="154"/>
-      <c r="G49" s="154"/>
-      <c r="H49" s="172">
+      <c r="B49" s="151"/>
+      <c r="C49" s="151"/>
+      <c r="D49" s="151"/>
+      <c r="E49" s="151"/>
+      <c r="F49" s="151"/>
+      <c r="G49" s="151"/>
+      <c r="H49" s="167">
         <v>89235.14</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="154"/>
-      <c r="B50" s="154"/>
-      <c r="C50" s="154"/>
-      <c r="D50" s="154"/>
-      <c r="E50" s="154"/>
-      <c r="F50" s="154"/>
-      <c r="G50" s="154"/>
+      <c r="A50" s="151"/>
+      <c r="B50" s="151"/>
+      <c r="C50" s="151"/>
+      <c r="D50" s="151"/>
+      <c r="E50" s="151"/>
+      <c r="F50" s="151"/>
+      <c r="G50" s="151"/>
       <c r="H50" s="82"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="157" t="s">
+      <c r="A51" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="157"/>
-      <c r="C51" s="157"/>
-      <c r="D51" s="157"/>
-      <c r="E51" s="157"/>
-      <c r="F51" s="157"/>
-      <c r="G51" s="157"/>
-      <c r="H51" s="160">
+      <c r="B51" s="154"/>
+      <c r="C51" s="154"/>
+      <c r="D51" s="154"/>
+      <c r="E51" s="154"/>
+      <c r="F51" s="154"/>
+      <c r="G51" s="154"/>
+      <c r="H51" s="157">
         <f>SUM(H49:H50)</f>
         <v>89235.14</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="235" t="s">
+      <c r="A52" s="204" t="s">
         <v>118</v>
       </c>
-      <c r="B52" s="236"/>
-      <c r="C52" s="236"/>
-      <c r="D52" s="236"/>
-      <c r="E52" s="236"/>
-      <c r="F52" s="236"/>
-      <c r="G52" s="236"/>
-      <c r="H52" s="237"/>
+      <c r="B52" s="205"/>
+      <c r="C52" s="205"/>
+      <c r="D52" s="205"/>
+      <c r="E52" s="205"/>
+      <c r="F52" s="205"/>
+      <c r="G52" s="205"/>
+      <c r="H52" s="206"/>
       <c r="I52" s="87"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -5046,10 +5044,12 @@
       <c r="C53" s="85"/>
       <c r="D53" s="85"/>
       <c r="E53" s="85"/>
-      <c r="F53" s="85"/>
+      <c r="F53" s="85" t="s">
+        <v>179</v>
+      </c>
       <c r="G53" s="85"/>
-      <c r="H53" s="172">
-        <v>49889.86</v>
+      <c r="H53" s="166">
+        <v>55029.24</v>
       </c>
       <c r="I53" s="87"/>
     </row>
@@ -5061,9 +5061,11 @@
       <c r="C54" s="85"/>
       <c r="D54" s="85"/>
       <c r="E54" s="85"/>
-      <c r="F54" s="85"/>
+      <c r="F54" s="85" t="s">
+        <v>178</v>
+      </c>
       <c r="G54" s="85"/>
-      <c r="H54" s="172">
+      <c r="H54" s="166">
         <v>3498.02</v>
       </c>
       <c r="I54" s="87"/>
@@ -5080,22 +5082,22 @@
       <c r="G55" s="85"/>
       <c r="H55" s="84">
         <f>SUM(H53:H54)</f>
-        <v>53387.88</v>
+        <v>58527.259999999995</v>
       </c>
       <c r="I55" s="87"/>
       <c r="K55" s="83"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="206" t="s">
+      <c r="A56" s="207" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="207"/>
-      <c r="C56" s="207"/>
-      <c r="D56" s="207"/>
-      <c r="E56" s="207"/>
-      <c r="F56" s="207"/>
-      <c r="G56" s="207"/>
-      <c r="H56" s="238"/>
+      <c r="B56" s="208"/>
+      <c r="C56" s="208"/>
+      <c r="D56" s="208"/>
+      <c r="E56" s="208"/>
+      <c r="F56" s="208"/>
+      <c r="G56" s="208"/>
+      <c r="H56" s="209"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="86"/>
@@ -5131,12 +5133,12 @@
     </row>
     <row r="60" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A60" s="93"/>
-      <c r="B60" s="132"/>
-      <c r="C60" s="132"/>
-      <c r="D60" s="132"/>
-      <c r="E60" s="132"/>
-      <c r="F60" s="132"/>
-      <c r="G60" s="132"/>
+      <c r="B60" s="131"/>
+      <c r="C60" s="131"/>
+      <c r="D60" s="131"/>
+      <c r="E60" s="131"/>
+      <c r="F60" s="131"/>
+      <c r="G60" s="131"/>
       <c r="H60" s="94"/>
     </row>
     <row r="61" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5150,16 +5152,16 @@
       <c r="H61" s="92"/>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="206" t="s">
+      <c r="A62" s="207" t="s">
         <v>152</v>
       </c>
-      <c r="B62" s="207"/>
-      <c r="C62" s="207"/>
-      <c r="D62" s="207"/>
-      <c r="E62" s="207"/>
-      <c r="F62" s="207"/>
-      <c r="G62" s="207"/>
-      <c r="H62" s="128"/>
+      <c r="B62" s="208"/>
+      <c r="C62" s="208"/>
+      <c r="D62" s="208"/>
+      <c r="E62" s="208"/>
+      <c r="F62" s="208"/>
+      <c r="G62" s="208"/>
+      <c r="H62" s="127"/>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="91"/>
@@ -5182,15 +5184,15 @@
       <c r="H64" s="92"/>
     </row>
     <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="129" t="s">
+      <c r="A65" s="128" t="s">
         <v>100</v>
       </c>
-      <c r="B65" s="132"/>
-      <c r="C65" s="132"/>
-      <c r="D65" s="132"/>
-      <c r="E65" s="132"/>
-      <c r="F65" s="132"/>
-      <c r="G65" s="132"/>
+      <c r="B65" s="131"/>
+      <c r="C65" s="131"/>
+      <c r="D65" s="131"/>
+      <c r="E65" s="131"/>
+      <c r="F65" s="131"/>
+      <c r="G65" s="131"/>
       <c r="H65" s="94">
         <f>SUM(H63:H64)</f>
         <v>0</v>
@@ -5207,26 +5209,26 @@
       <c r="H66" s="92"/>
     </row>
     <row r="67" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A67" s="198" t="s">
+      <c r="A67" s="225" t="s">
         <v>120</v>
       </c>
-      <c r="B67" s="198"/>
-      <c r="C67" s="198"/>
-      <c r="D67" s="198"/>
-      <c r="E67" s="198"/>
-      <c r="F67" s="198"/>
-      <c r="G67" s="198"/>
+      <c r="B67" s="225"/>
+      <c r="C67" s="225"/>
+      <c r="D67" s="225"/>
+      <c r="E67" s="225"/>
+      <c r="F67" s="225"/>
+      <c r="G67" s="225"/>
       <c r="H67" s="95"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="183"/>
-      <c r="B68" s="184"/>
-      <c r="C68" s="184"/>
-      <c r="D68" s="184"/>
-      <c r="E68" s="184"/>
-      <c r="F68" s="184"/>
-      <c r="G68" s="185"/>
-      <c r="H68" s="124"/>
+      <c r="A68" s="210"/>
+      <c r="B68" s="211"/>
+      <c r="C68" s="211"/>
+      <c r="D68" s="211"/>
+      <c r="E68" s="211"/>
+      <c r="F68" s="211"/>
+      <c r="G68" s="212"/>
+      <c r="H68" s="123"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="96"/>
@@ -5236,46 +5238,46 @@
       <c r="E69" s="97"/>
       <c r="F69" s="97"/>
       <c r="G69" s="98"/>
-      <c r="H69" s="124"/>
+      <c r="H69" s="123"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="199"/>
-      <c r="B70" s="200"/>
-      <c r="C70" s="200"/>
-      <c r="D70" s="200"/>
-      <c r="E70" s="200"/>
-      <c r="F70" s="200"/>
-      <c r="G70" s="201"/>
+      <c r="A70" s="226"/>
+      <c r="B70" s="227"/>
+      <c r="C70" s="227"/>
+      <c r="D70" s="227"/>
+      <c r="E70" s="227"/>
+      <c r="F70" s="227"/>
+      <c r="G70" s="228"/>
       <c r="H70" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="133"/>
-      <c r="B71" s="134"/>
-      <c r="C71" s="134"/>
-      <c r="D71" s="134"/>
-      <c r="E71" s="134"/>
-      <c r="F71" s="134"/>
-      <c r="G71" s="135"/>
+      <c r="A71" s="132"/>
+      <c r="B71" s="133"/>
+      <c r="C71" s="133"/>
+      <c r="D71" s="133"/>
+      <c r="E71" s="133"/>
+      <c r="F71" s="133"/>
+      <c r="G71" s="134"/>
       <c r="H71" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="133"/>
-      <c r="B72" s="134"/>
-      <c r="C72" s="134"/>
-      <c r="D72" s="134"/>
-      <c r="E72" s="134"/>
-      <c r="F72" s="134"/>
-      <c r="G72" s="135"/>
+      <c r="A72" s="132"/>
+      <c r="B72" s="133"/>
+      <c r="C72" s="133"/>
+      <c r="D72" s="133"/>
+      <c r="E72" s="133"/>
+      <c r="F72" s="133"/>
+      <c r="G72" s="134"/>
       <c r="H72" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="137" t="s">
+      <c r="A73" s="136" t="s">
         <v>100</v>
       </c>
       <c r="B73" s="85"/>
@@ -5290,133 +5292,133 @@
       </c>
     </row>
     <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="138"/>
-      <c r="B74" s="138"/>
-      <c r="C74" s="138"/>
-      <c r="D74" s="138"/>
-      <c r="E74" s="138"/>
-      <c r="F74" s="138"/>
-      <c r="G74" s="138"/>
-      <c r="H74" s="139"/>
+      <c r="A74" s="137"/>
+      <c r="B74" s="137"/>
+      <c r="C74" s="137"/>
+      <c r="D74" s="137"/>
+      <c r="E74" s="137"/>
+      <c r="F74" s="137"/>
+      <c r="G74" s="137"/>
+      <c r="H74" s="138"/>
       <c r="I74" s="87"/>
     </row>
     <row r="75" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="202" t="s">
+      <c r="A75" s="229" t="s">
         <v>121</v>
       </c>
-      <c r="B75" s="203"/>
-      <c r="C75" s="203"/>
-      <c r="D75" s="203"/>
-      <c r="E75" s="203"/>
-      <c r="F75" s="203"/>
-      <c r="G75" s="203"/>
-      <c r="H75" s="140">
+      <c r="B75" s="230"/>
+      <c r="C75" s="230"/>
+      <c r="D75" s="230"/>
+      <c r="E75" s="230"/>
+      <c r="F75" s="230"/>
+      <c r="G75" s="230"/>
+      <c r="H75" s="139">
         <f>H73</f>
         <v>0</v>
       </c>
       <c r="I75" s="87"/>
     </row>
     <row r="76" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="195" t="s">
+      <c r="A76" s="222" t="s">
         <v>122</v>
       </c>
-      <c r="B76" s="196"/>
-      <c r="C76" s="196"/>
-      <c r="D76" s="196"/>
-      <c r="E76" s="196"/>
-      <c r="F76" s="196"/>
-      <c r="G76" s="197"/>
-      <c r="H76" s="140"/>
+      <c r="B76" s="223"/>
+      <c r="C76" s="223"/>
+      <c r="D76" s="223"/>
+      <c r="E76" s="223"/>
+      <c r="F76" s="223"/>
+      <c r="G76" s="224"/>
+      <c r="H76" s="139"/>
       <c r="I76" s="88"/>
     </row>
     <row r="77" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="208" t="s">
+      <c r="A77" s="233" t="s">
         <v>142</v>
       </c>
-      <c r="B77" s="209"/>
-      <c r="C77" s="209"/>
-      <c r="D77" s="209"/>
-      <c r="E77" s="209"/>
-      <c r="F77" s="209"/>
-      <c r="G77" s="210"/>
-      <c r="H77" s="140"/>
+      <c r="B77" s="234"/>
+      <c r="C77" s="234"/>
+      <c r="D77" s="234"/>
+      <c r="E77" s="234"/>
+      <c r="F77" s="234"/>
+      <c r="G77" s="235"/>
+      <c r="H77" s="139"/>
       <c r="I77" s="87"/>
       <c r="J77" s="83"/>
     </row>
     <row r="78" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A78" s="202" t="s">
+      <c r="A78" s="229" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="203"/>
-      <c r="C78" s="203"/>
-      <c r="D78" s="203"/>
-      <c r="E78" s="203"/>
-      <c r="F78" s="203"/>
-      <c r="G78" s="203"/>
-      <c r="H78" s="140">
+      <c r="B78" s="230"/>
+      <c r="C78" s="230"/>
+      <c r="D78" s="230"/>
+      <c r="E78" s="230"/>
+      <c r="F78" s="230"/>
+      <c r="G78" s="230"/>
+      <c r="H78" s="139">
         <f>H59+H55+H51+H47+H42+H33+H16+H21+H28+H65</f>
-        <v>5105770.24</v>
+        <v>4561929.1500000004</v>
       </c>
       <c r="I78" s="83"/>
     </row>
     <row r="79" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A79" s="211" t="s">
+      <c r="A79" s="236" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="212"/>
-      <c r="C79" s="212"/>
-      <c r="D79" s="212"/>
-      <c r="E79" s="212"/>
-      <c r="F79" s="212"/>
-      <c r="G79" s="213"/>
-      <c r="H79" s="141">
+      <c r="B79" s="237"/>
+      <c r="C79" s="237"/>
+      <c r="D79" s="237"/>
+      <c r="E79" s="237"/>
+      <c r="F79" s="237"/>
+      <c r="G79" s="238"/>
+      <c r="H79" s="140">
         <f>H78+H76</f>
-        <v>5105770.24</v>
+        <v>4561929.1500000004</v>
       </c>
       <c r="I79" s="83"/>
-      <c r="K79" s="149"/>
+      <c r="K79" s="148"/>
     </row>
     <row r="80" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A80" s="211" t="s">
+      <c r="A80" s="236" t="s">
         <v>125</v>
       </c>
-      <c r="B80" s="212"/>
-      <c r="C80" s="212"/>
-      <c r="D80" s="212"/>
-      <c r="E80" s="212"/>
-      <c r="F80" s="212"/>
-      <c r="G80" s="213"/>
-      <c r="H80" s="142">
+      <c r="B80" s="237"/>
+      <c r="C80" s="237"/>
+      <c r="D80" s="237"/>
+      <c r="E80" s="237"/>
+      <c r="F80" s="237"/>
+      <c r="G80" s="238"/>
+      <c r="H80" s="141">
         <f>H75+H77</f>
         <v>0</v>
       </c>
       <c r="I80" s="83"/>
     </row>
     <row r="81" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="214" t="s">
+      <c r="A81" s="183" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="215"/>
-      <c r="C81" s="215"/>
-      <c r="D81" s="215"/>
-      <c r="E81" s="215"/>
-      <c r="F81" s="215"/>
-      <c r="G81" s="215"/>
-      <c r="H81" s="143">
+      <c r="B81" s="184"/>
+      <c r="C81" s="184"/>
+      <c r="D81" s="184"/>
+      <c r="E81" s="184"/>
+      <c r="F81" s="184"/>
+      <c r="G81" s="184"/>
+      <c r="H81" s="142">
         <f>H78+H75</f>
-        <v>5105770.24</v>
+        <v>4561929.1500000004</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="216" t="s">
+      <c r="A82" s="185" t="s">
         <v>127</v>
       </c>
-      <c r="B82" s="217"/>
-      <c r="C82" s="217"/>
-      <c r="D82" s="217"/>
-      <c r="E82" s="217"/>
-      <c r="F82" s="217"/>
-      <c r="G82" s="217"/>
+      <c r="B82" s="186"/>
+      <c r="C82" s="186"/>
+      <c r="D82" s="186"/>
+      <c r="E82" s="186"/>
+      <c r="F82" s="186"/>
+      <c r="G82" s="186"/>
       <c r="H82" s="100">
         <v>0</v>
       </c>
@@ -5432,26 +5434,26 @@
       <c r="H83" s="102"/>
     </row>
     <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="218" t="s">
+      <c r="A84" s="187" t="s">
         <v>161</v>
       </c>
-      <c r="B84" s="219"/>
-      <c r="C84" s="219"/>
-      <c r="D84" s="219"/>
-      <c r="E84" s="219"/>
-      <c r="F84" s="219"/>
-      <c r="G84" s="219"/>
-      <c r="H84" s="220"/>
+      <c r="B84" s="188"/>
+      <c r="C84" s="188"/>
+      <c r="D84" s="188"/>
+      <c r="E84" s="188"/>
+      <c r="F84" s="188"/>
+      <c r="G84" s="188"/>
+      <c r="H84" s="189"/>
     </row>
     <row r="85" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="221"/>
-      <c r="B85" s="222"/>
-      <c r="C85" s="222"/>
-      <c r="D85" s="222"/>
-      <c r="E85" s="222"/>
-      <c r="F85" s="222"/>
-      <c r="G85" s="222"/>
-      <c r="H85" s="223"/>
+      <c r="A85" s="190"/>
+      <c r="B85" s="191"/>
+      <c r="C85" s="191"/>
+      <c r="D85" s="191"/>
+      <c r="E85" s="191"/>
+      <c r="F85" s="191"/>
+      <c r="G85" s="191"/>
+      <c r="H85" s="192"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
@@ -5464,16 +5466,16 @@
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A87" s="187" t="s">
+      <c r="A87" s="214" t="s">
         <v>128</v>
       </c>
-      <c r="B87" s="188"/>
-      <c r="C87" s="188"/>
-      <c r="D87" s="188"/>
-      <c r="E87" s="188"/>
-      <c r="F87" s="188"/>
-      <c r="G87" s="188"/>
-      <c r="H87" s="189"/>
+      <c r="B87" s="215"/>
+      <c r="C87" s="215"/>
+      <c r="D87" s="215"/>
+      <c r="E87" s="215"/>
+      <c r="F87" s="215"/>
+      <c r="G87" s="215"/>
+      <c r="H87" s="216"/>
     </row>
     <row r="88" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A88" s="103" t="s">
@@ -5486,7 +5488,7 @@
       <c r="F88" s="104"/>
       <c r="G88" s="104"/>
       <c r="H88" s="105">
-        <v>1280791.0346397704</v>
+        <v>-834604.30226353183</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -5501,7 +5503,7 @@
       <c r="G89" s="106"/>
       <c r="H89" s="18">
         <f>Planilla!G43</f>
-        <v>4581518.1130966982</v>
+        <v>4798692.9416700006</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -5514,9 +5516,9 @@
       <c r="E90" s="108"/>
       <c r="F90" s="108"/>
       <c r="G90" s="108"/>
-      <c r="H90" s="123">
+      <c r="H90" s="122">
         <f>-H81</f>
-        <v>-5105770.24</v>
+        <v>-4561929.1500000004</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -5530,81 +5532,86 @@
       <c r="F91" s="108"/>
       <c r="G91" s="108"/>
       <c r="H91" s="31">
-        <f>D105</f>
+        <f>D106</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="107" t="s">
-        <v>153</v>
-      </c>
-      <c r="B92" s="109"/>
+        <v>177</v>
+      </c>
+      <c r="B92" s="108"/>
       <c r="C92" s="108"/>
       <c r="D92" s="108"/>
       <c r="E92" s="108"/>
       <c r="F92" s="108"/>
       <c r="G92" s="108"/>
-      <c r="H92" s="131">
+      <c r="H92" s="122">
+        <f>-(3244+6707+6908+7115)</f>
+        <v>-23974</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="107" t="s">
+        <v>153</v>
+      </c>
+      <c r="B93" s="109"/>
+      <c r="C93" s="108"/>
+      <c r="D93" s="108"/>
+      <c r="E93" s="108"/>
+      <c r="F93" s="108"/>
+      <c r="G93" s="108"/>
+      <c r="H93" s="130">
         <f>-H65</f>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A93" s="110" t="s">
+    <row r="94" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A94" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="B93" s="111"/>
-      <c r="C93" s="111"/>
-      <c r="D93" s="111"/>
-      <c r="E93" s="111"/>
-      <c r="F93" s="111"/>
-      <c r="G93" s="111"/>
-      <c r="H93" s="112">
-        <f>SUM(H88:H92)</f>
-        <v>756538.90773646813</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="95" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="190" t="s">
+      <c r="B94" s="111"/>
+      <c r="C94" s="111"/>
+      <c r="D94" s="111"/>
+      <c r="E94" s="111"/>
+      <c r="F94" s="111"/>
+      <c r="G94" s="111"/>
+      <c r="H94" s="112">
+        <f>SUM(H88:H93)</f>
+        <v>-621814.51059353165</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="217" t="s">
         <v>133</v>
       </c>
-      <c r="B95" s="191"/>
-      <c r="C95" s="191"/>
-      <c r="D95" s="191"/>
-      <c r="E95" s="191"/>
-      <c r="F95" s="191"/>
-      <c r="G95" s="191"/>
-      <c r="H95" s="192"/>
-    </row>
-    <row r="96" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="113" t="s">
+      <c r="B96" s="218"/>
+      <c r="C96" s="218"/>
+      <c r="D96" s="218"/>
+      <c r="E96" s="218"/>
+      <c r="F96" s="218"/>
+      <c r="G96" s="218"/>
+      <c r="H96" s="219"/>
+    </row>
+    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="113"/>
-      <c r="C96" s="113"/>
-      <c r="D96" s="113"/>
-      <c r="E96" s="113"/>
-      <c r="F96" s="113"/>
-      <c r="G96" s="113"/>
-      <c r="H96" s="114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="6"/>
-      <c r="B97" s="115"/>
-      <c r="C97" s="108"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="18"/>
+      <c r="B97" s="113"/>
+      <c r="C97" s="113"/>
+      <c r="D97" s="113"/>
+      <c r="E97" s="113"/>
+      <c r="F97" s="113"/>
+      <c r="G97" s="113"/>
+      <c r="H97" s="114">
+        <v>0</v>
+      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
-      <c r="B98" s="116"/>
-      <c r="C98" s="6"/>
+      <c r="B98" s="115"/>
+      <c r="C98" s="108"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -5613,7 +5620,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
+      <c r="B99" s="116"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -5622,32 +5629,36 @@
       <c r="H99" s="18"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="117" t="s">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="18"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="B100" s="117"/>
-      <c r="C100" s="117"/>
-      <c r="D100" s="117"/>
-      <c r="E100" s="117"/>
-      <c r="F100" s="117"/>
-      <c r="G100" s="117"/>
-      <c r="H100" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="125" t="s">
+      <c r="B101" s="117"/>
+      <c r="C101" s="117"/>
+      <c r="D101" s="117"/>
+      <c r="E101" s="117"/>
+      <c r="F101" s="117"/>
+      <c r="G101" s="117"/>
+      <c r="H101" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="B102" s="126"/>
-      <c r="C102" s="126"/>
-      <c r="D102" s="126"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="18"/>
+      <c r="B103" s="125"/>
+      <c r="C103" s="125"/>
+      <c r="D103" s="125"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
@@ -5656,61 +5667,83 @@
       <c r="D104" s="18"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="119" t="s">
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="18"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="B105" s="126"/>
-      <c r="C105" s="126"/>
-      <c r="D105" s="136">
-        <f>SUM(D103:D104)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="125" t="s">
+      <c r="B106" s="125"/>
+      <c r="C106" s="125"/>
+      <c r="D106" s="135">
+        <f>SUM(D104:D105)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="B107" s="119"/>
-      <c r="C107" s="119"/>
-      <c r="D107" s="119"/>
-    </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="6"/>
-      <c r="B108" s="99"/>
-      <c r="C108" s="99"/>
-      <c r="D108" s="121"/>
+      <c r="B108" s="119"/>
+      <c r="C108" s="119"/>
+      <c r="D108" s="119"/>
     </row>
     <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="127"/>
+      <c r="B109" s="99"/>
+      <c r="C109" s="99"/>
+      <c r="D109" s="121"/>
     </row>
     <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
-      <c r="D110" s="127"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D110" s="126"/>
+    </row>
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
-      <c r="D111" s="127"/>
+      <c r="D111" s="126"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="120" t="s">
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="126"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="B112" s="120"/>
-      <c r="C112" s="193">
-        <f>SUM(D108:D111)</f>
-        <v>0</v>
-      </c>
-      <c r="D112" s="194"/>
+      <c r="B113" s="120"/>
+      <c r="C113" s="220">
+        <f>SUM(D109:D112)</f>
+        <v>0</v>
+      </c>
+      <c r="D113" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A96:H96"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A80:G80"/>
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="A84:H85"/>
@@ -5727,22 +5760,6 @@
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A80:G80"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
+++ b/YRIGOYEN 9115/Julio/YRIGOYEN-EXPENSAS-Julio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B59582E-ADA9-4FF7-B475-F929478080A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77A75CC-1038-445A-8745-5DAC4C9B91B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$113</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -513,9 +513,6 @@
     <t>Suplencia Semana de Vacaciones - Sra Silvia</t>
   </si>
   <si>
-    <t>QUIEN NO INFORME EL PAGO DE LA MANERA SOLICITADA CORRE EL RIESGO DE NO VER EL MISMO IMPUTADO. SE SOSTIENE EL MONTO DE EXPENSAS YA QUE SE PROCEDERA A LIMPIAR LOS TANQUES DE AGUA Y DESPUES DE LA ASAMBLEA SE DECIDIRA LA OBRA QUE SE REALIZARA EN LOS MISMOS.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nazareno e Ivon Iriarte
 </t>
   </si>
@@ -532,9 +529,6 @@
     <t>Sueldo encargada - Jimena Borges y SAC</t>
   </si>
   <si>
-    <t>VTO: 14/08</t>
-  </si>
-  <si>
     <t>PERIODO: JULIO</t>
   </si>
   <si>
@@ -572,6 +566,12 @@
   </si>
   <si>
     <t>Debito 10/07</t>
+  </si>
+  <si>
+    <t>VTO: 18/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cutreta mariano el mes pasado pago el 14 (a nosotros nos impacto el 15) no debe tener deuda pq le cobramos incorrectamente intereses</t>
   </si>
 </sst>
 </file>
@@ -819,7 +819,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -868,14 +868,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="43">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -994,17 +988,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1399,7 +1382,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1433,41 +1416,41 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1481,10 +1464,10 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1504,26 +1487,26 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1537,9 +1520,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="26" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="26" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1565,14 +1548,14 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1584,15 +1567,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1600,46 +1583,46 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="31" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="32" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="32" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1658,42 +1641,42 @@
     <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1703,41 +1686,20 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1760,10 +1722,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1775,28 +1737,28 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1805,78 +1767,79 @@
     <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2328,7 +2291,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="str">
         <f>Gastos!G8</f>
-        <v>VTO: 14/08</v>
+        <v>VTO: 18/08</v>
       </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2361,13 +2324,13 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="173" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="175"/>
+      <c r="F3" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="172"/>
       <c r="K3" s="146"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -2382,11 +2345,11 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="144"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="177"/>
-      <c r="H4" s="177"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="178"/>
+      <c r="F4" s="173"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="175"/>
       <c r="K4" s="146"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -2395,20 +2358,20 @@
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="182">
+      <c r="B5" s="179">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="182"/>
+      <c r="C5" s="179"/>
       <c r="D5" s="16"/>
       <c r="E5" s="145">
         <v>0</v>
       </c>
-      <c r="F5" s="176"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="178"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="175"/>
       <c r="K5" s="147"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -2423,11 +2386,11 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="144"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="180"/>
-      <c r="H6" s="180"/>
-      <c r="I6" s="180"/>
-      <c r="J6" s="181"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="177"/>
+      <c r="J6" s="178"/>
       <c r="K6" s="147"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -2436,11 +2399,11 @@
     </row>
     <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
-      <c r="B7" s="182">
+      <c r="B7" s="179">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="182"/>
+      <c r="C7" s="179"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -2518,7 +2481,7 @@
       <c r="F9" s="31">
         <v>540000</v>
       </c>
-      <c r="G9" s="172">
+      <c r="G9" s="167">
         <f>F9</f>
         <v>540000</v>
       </c>
@@ -2569,7 +2532,7 @@
       <c r="F10" s="31">
         <v>144000</v>
       </c>
-      <c r="G10" s="168">
+      <c r="G10" s="149">
         <f>F10</f>
         <v>144000</v>
       </c>
@@ -2620,7 +2583,7 @@
       <c r="F11" s="31">
         <v>130507</v>
       </c>
-      <c r="G11" s="168">
+      <c r="G11" s="149">
         <v>130508</v>
       </c>
       <c r="H11" s="32">
@@ -2670,7 +2633,7 @@
       <c r="F12" s="31">
         <v>107499.99999999999</v>
       </c>
-      <c r="G12" s="168">
+      <c r="G12" s="149">
         <f>F12</f>
         <v>107499.99999999999</v>
       </c>
@@ -2724,7 +2687,7 @@
       <c r="F13" s="31">
         <v>88230</v>
       </c>
-      <c r="G13" s="168">
+      <c r="G13" s="149">
         <f>F13</f>
         <v>88230</v>
       </c>
@@ -2775,7 +2738,7 @@
       <c r="F14" s="31">
         <v>139366.92475261347</v>
       </c>
-      <c r="G14" s="168">
+      <c r="G14" s="149">
         <v>140000</v>
       </c>
       <c r="H14" s="32">
@@ -2825,7 +2788,7 @@
       <c r="F15" s="31">
         <v>124499.99999999999</v>
       </c>
-      <c r="G15" s="168">
+      <c r="G15" s="149">
         <f>F15</f>
         <v>124499.99999999999</v>
       </c>
@@ -2878,7 +2841,7 @@
       <c r="F16" s="31">
         <v>107499.99999999999</v>
       </c>
-      <c r="G16" s="168">
+      <c r="G16" s="149">
         <f>F16</f>
         <v>107499.99999999999</v>
       </c>
@@ -2931,7 +2894,7 @@
       <c r="F17" s="31">
         <v>262018.28991180353</v>
       </c>
-      <c r="G17" s="168">
+      <c r="G17" s="149">
         <v>50000</v>
       </c>
       <c r="H17" s="32">
@@ -2983,7 +2946,7 @@
       <c r="F18" s="31">
         <v>139500</v>
       </c>
-      <c r="G18" s="168">
+      <c r="G18" s="149">
         <f t="shared" ref="G18:G23" si="7">F18</f>
         <v>139500</v>
       </c>
@@ -3028,7 +2991,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="163" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E19" s="30">
         <v>2.4899999999999999E-2</v>
@@ -3036,7 +2999,7 @@
       <c r="F19" s="31">
         <v>124499.99999999999</v>
       </c>
-      <c r="G19" s="168">
+      <c r="G19" s="149">
         <f t="shared" si="7"/>
         <v>124499.99999999999</v>
       </c>
@@ -3137,7 +3100,7 @@
       <c r="F21" s="31">
         <v>142290</v>
       </c>
-      <c r="G21" s="168">
+      <c r="G21" s="149">
         <v>139500</v>
       </c>
       <c r="H21" s="32">
@@ -3187,7 +3150,7 @@
       <c r="F22" s="31">
         <v>124499.99999999999</v>
       </c>
-      <c r="G22" s="168">
+      <c r="G22" s="149">
         <f t="shared" si="7"/>
         <v>124499.99999999999</v>
       </c>
@@ -3240,7 +3203,7 @@
       <c r="F23" s="31">
         <v>183500.00000000003</v>
       </c>
-      <c r="G23" s="168">
+      <c r="G23" s="149">
         <f t="shared" si="7"/>
         <v>183500.00000000003</v>
       </c>
@@ -3293,7 +3256,7 @@
       <c r="F24" s="31">
         <v>233732.52990228351</v>
       </c>
-      <c r="G24" s="168">
+      <c r="G24" s="149">
         <v>139500</v>
       </c>
       <c r="H24" s="32">
@@ -3343,7 +3306,7 @@
       <c r="F25" s="31">
         <v>124499.77512699996</v>
       </c>
-      <c r="G25" s="168">
+      <c r="G25" s="149">
         <f>126990</f>
         <v>126990</v>
       </c>
@@ -3394,14 +3357,17 @@
       <c r="F26" s="31">
         <v>183500.00000000003</v>
       </c>
-      <c r="G26" s="149"/>
+      <c r="G26" s="149">
+        <f>F26</f>
+        <v>183500.00000000003</v>
+      </c>
       <c r="H26" s="32">
         <f t="shared" si="0"/>
-        <v>183500.00000000003</v>
+        <v>0</v>
       </c>
       <c r="I26" s="32">
         <f t="shared" si="1"/>
-        <v>5505.0000000000009</v>
+        <v>0</v>
       </c>
       <c r="J26" s="32">
         <f t="shared" si="2"/>
@@ -3418,11 +3384,11 @@
       </c>
       <c r="N26" s="34">
         <f t="shared" si="5"/>
-        <v>372505.00000000006</v>
+        <v>183500.00000000003</v>
       </c>
       <c r="O26" s="35">
         <f t="shared" si="6"/>
-        <v>379955.10000000003</v>
+        <v>187170.00000000003</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3442,7 +3408,7 @@
       <c r="F27" s="31">
         <v>139500</v>
       </c>
-      <c r="G27" s="168">
+      <c r="G27" s="149">
         <f>F27</f>
         <v>139500</v>
       </c>
@@ -3543,7 +3509,7 @@
       <c r="F29" s="31">
         <v>183500.00000000003</v>
       </c>
-      <c r="G29" s="168">
+      <c r="G29" s="149">
         <f>F29</f>
         <v>183500.00000000003</v>
       </c>
@@ -3596,7 +3562,7 @@
       <c r="F30" s="31">
         <v>139500</v>
       </c>
-      <c r="G30" s="168">
+      <c r="G30" s="149">
         <f>F30</f>
         <v>139500</v>
       </c>
@@ -3647,14 +3613,16 @@
       <c r="F31" s="31">
         <v>526804.93499286915</v>
       </c>
-      <c r="G31" s="149"/>
+      <c r="G31" s="149">
+        <v>398399</v>
+      </c>
       <c r="H31" s="32">
         <f t="shared" si="0"/>
-        <v>526804.93499286915</v>
+        <v>128405.93499286915</v>
       </c>
       <c r="I31" s="32">
         <f t="shared" si="1"/>
-        <v>15804.148049786074</v>
+        <v>3852.1780497860746</v>
       </c>
       <c r="J31" s="32">
         <f t="shared" si="2"/>
@@ -3671,11 +3639,11 @@
       </c>
       <c r="N31" s="34">
         <f t="shared" si="5"/>
-        <v>667109.08304265526</v>
+        <v>256758.11304265523</v>
       </c>
       <c r="O31" s="35">
         <f t="shared" si="6"/>
-        <v>680451.26470350835</v>
+        <v>261893.27530350833</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
@@ -3697,7 +3665,7 @@
       <c r="F32" s="18">
         <v>672579.4554082898</v>
       </c>
-      <c r="G32" s="168">
+      <c r="G32" s="149">
         <v>351176</v>
       </c>
       <c r="H32" s="32">
@@ -3750,7 +3718,7 @@
       <c r="F33" s="126">
         <v>135277.73864328716</v>
       </c>
-      <c r="G33" s="168">
+      <c r="G33" s="149">
         <v>135500</v>
       </c>
       <c r="H33" s="32">
@@ -3803,8 +3771,8 @@
       <c r="F34" s="18">
         <v>124499.99999999999</v>
       </c>
-      <c r="G34" s="169">
-        <f>F34</f>
+      <c r="G34" s="168">
+        <f t="shared" ref="G34:G39" si="9">F34</f>
         <v>124499.99999999999</v>
       </c>
       <c r="H34" s="32">
@@ -3855,8 +3823,8 @@
       <c r="F35" s="18">
         <v>183500.00000000003</v>
       </c>
-      <c r="G35" s="168">
-        <f>F35</f>
+      <c r="G35" s="149">
+        <f t="shared" si="9"/>
         <v>183500.00000000003</v>
       </c>
       <c r="H35" s="32">
@@ -3910,8 +3878,8 @@
       <c r="F36" s="18">
         <v>139500</v>
       </c>
-      <c r="G36" s="169">
-        <f>F36</f>
+      <c r="G36" s="168">
+        <f t="shared" si="9"/>
         <v>139500</v>
       </c>
       <c r="H36" s="32">
@@ -3956,7 +3924,7 @@
         <v>76</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E37" s="30">
         <v>2.4899999999999999E-2</v>
@@ -3964,8 +3932,8 @@
       <c r="F37" s="18">
         <v>124499.99999999999</v>
       </c>
-      <c r="G37" s="169">
-        <f>F37</f>
+      <c r="G37" s="168">
+        <f t="shared" si="9"/>
         <v>124499.99999999999</v>
       </c>
       <c r="H37" s="32">
@@ -4010,7 +3978,7 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E38" s="30">
         <v>2.1499999999999998E-2</v>
@@ -4018,8 +3986,8 @@
       <c r="F38" s="18">
         <v>351788.94167000049</v>
       </c>
-      <c r="G38" s="169">
-        <f>F38</f>
+      <c r="G38" s="168">
+        <f t="shared" si="9"/>
         <v>351788.94167000049</v>
       </c>
       <c r="H38" s="32">
@@ -4072,8 +4040,8 @@
       <c r="F39" s="18">
         <v>68000</v>
       </c>
-      <c r="G39" s="169">
-        <f>F39</f>
+      <c r="G39" s="168">
+        <f t="shared" si="9"/>
         <v>68000</v>
       </c>
       <c r="H39" s="32">
@@ -4114,7 +4082,7 @@
       <c r="B40" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="56" t="s">
+      <c r="C40" s="230" t="s">
         <v>83</v>
       </c>
       <c r="D40" s="6"/>
@@ -4124,7 +4092,7 @@
       <c r="F40" s="18">
         <v>142290</v>
       </c>
-      <c r="G40" s="169">
+      <c r="G40" s="168">
         <v>139500</v>
       </c>
       <c r="H40" s="32">
@@ -4156,6 +4124,9 @@
         <f t="shared" si="6"/>
         <v>145221.174</v>
       </c>
+      <c r="P40" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
@@ -4177,7 +4148,7 @@
       <c r="F41" s="18">
         <v>124499.99999999999</v>
       </c>
-      <c r="G41" s="169">
+      <c r="G41" s="168">
         <f>F41</f>
         <v>124499.99999999999</v>
       </c>
@@ -4231,7 +4202,7 @@
       <c r="F42" s="60">
         <v>183500.00000000003</v>
       </c>
-      <c r="G42" s="170">
+      <c r="G42" s="169">
         <f>F42</f>
         <v>183500.00000000003</v>
       </c>
@@ -4279,42 +4250,42 @@
         <v>6572422.9639698081</v>
       </c>
       <c r="G43" s="143">
-        <f t="shared" ref="G43:N43" si="9">SUM(G9:G42)</f>
-        <v>4798692.9416700006</v>
+        <f t="shared" ref="G43:N43" si="10">SUM(G9:G42)</f>
+        <v>5380591.9416700006</v>
       </c>
       <c r="H43" s="66">
-        <f t="shared" si="9"/>
-        <v>1777076.5837769073</v>
+        <f t="shared" si="10"/>
+        <v>1195177.5837769071</v>
       </c>
       <c r="I43" s="67">
-        <f t="shared" si="9"/>
-        <v>53312.29751330721</v>
+        <f t="shared" si="10"/>
+        <v>35855.327513307209</v>
       </c>
       <c r="J43" s="68">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3346.5614770994143</v>
       </c>
       <c r="K43" s="129">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L43" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5017500</v>
       </c>
       <c r="M43" s="65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N43" s="65">
-        <f t="shared" si="9"/>
-        <v>6844542.3198131155</v>
+        <f t="shared" si="10"/>
+        <v>6245186.3498131158</v>
       </c>
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G45" s="171"/>
+      <c r="G45" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4330,7 +4301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -4356,23 +4327,23 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="196"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="186"/>
+      <c r="F2" s="186"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="187"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="197" t="s">
+      <c r="E3" s="188" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="198"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="189"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
@@ -4417,13 +4388,13 @@
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="H8" s="81"/>
     </row>
@@ -4440,16 +4411,16 @@
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="199" t="s">
+      <c r="A10" s="190" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
-      <c r="D10" s="200"/>
-      <c r="E10" s="200"/>
-      <c r="F10" s="200"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="201"/>
+      <c r="B10" s="191"/>
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="191"/>
+      <c r="G10" s="191"/>
+      <c r="H10" s="192"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
@@ -4462,20 +4433,20 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="202" t="s">
+      <c r="A12" s="193" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="202"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="202"/>
-      <c r="G12" s="202"/>
-      <c r="H12" s="202"/>
+      <c r="B12" s="193"/>
+      <c r="C12" s="193"/>
+      <c r="D12" s="193"/>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193"/>
+      <c r="G12" s="193"/>
+      <c r="H12" s="193"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="150" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" s="151"/>
       <c r="C13" s="151"/>
@@ -4483,7 +4454,7 @@
       <c r="E13" s="151"/>
       <c r="F13" s="151"/>
       <c r="G13" s="151"/>
-      <c r="H13" s="166">
+      <c r="H13" s="82">
         <v>1043827.2</v>
       </c>
     </row>
@@ -4497,7 +4468,7 @@
       <c r="E14" s="151"/>
       <c r="F14" s="151"/>
       <c r="G14" s="151"/>
-      <c r="H14" s="166">
+      <c r="H14" s="82">
         <v>0.21</v>
       </c>
     </row>
@@ -4511,7 +4482,7 @@
       <c r="E15" s="152"/>
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
-      <c r="H15" s="166">
+      <c r="H15" s="82">
         <v>-227032.41</v>
       </c>
     </row>
@@ -4532,16 +4503,16 @@
       <c r="I16" s="83"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="203" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="203"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="203"/>
-      <c r="H17" s="203"/>
+      <c r="A17" s="194" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="194"/>
+      <c r="C17" s="194"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="194"/>
+      <c r="G17" s="194"/>
+      <c r="H17" s="194"/>
     </row>
     <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="85" t="s">
@@ -4593,30 +4564,30 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="203" t="s">
+      <c r="A22" s="194" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="203"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="203"/>
+      <c r="B22" s="194"/>
+      <c r="C22" s="194"/>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="194"/>
+      <c r="G22" s="194"/>
+      <c r="H22" s="194"/>
     </row>
     <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="150" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="155" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C23" s="155"/>
       <c r="D23" s="155"/>
       <c r="E23" s="155"/>
       <c r="F23" s="155"/>
       <c r="G23" s="151"/>
-      <c r="H23" s="166">
+      <c r="H23" s="82">
         <v>137308.57</v>
       </c>
     </row>
@@ -4633,7 +4604,7 @@
       <c r="E24" s="155"/>
       <c r="F24" s="155"/>
       <c r="G24" s="151"/>
-      <c r="H24" s="166">
+      <c r="H24" s="82">
         <v>69862.55</v>
       </c>
     </row>
@@ -4650,7 +4621,7 @@
       <c r="E25" s="155"/>
       <c r="F25" s="155"/>
       <c r="G25" s="151"/>
-      <c r="H25" s="166">
+      <c r="H25" s="82">
         <v>7762.51</v>
       </c>
     </row>
@@ -4659,14 +4630,14 @@
         <v>157</v>
       </c>
       <c r="B26" s="151" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C26" s="155"/>
       <c r="D26" s="155"/>
       <c r="E26" s="155"/>
       <c r="F26" s="155"/>
       <c r="G26" s="151"/>
-      <c r="H26" s="166">
+      <c r="H26" s="82">
         <v>714361.65</v>
       </c>
     </row>
@@ -4698,16 +4669,16 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="193" t="s">
+      <c r="A29" s="184" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="193"/>
-      <c r="C29" s="193"/>
-      <c r="D29" s="193"/>
-      <c r="E29" s="193"/>
-      <c r="F29" s="193"/>
-      <c r="G29" s="193"/>
-      <c r="H29" s="193"/>
+      <c r="B29" s="184"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="184"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="151" t="s">
@@ -4717,11 +4688,11 @@
       <c r="C30" s="151"/>
       <c r="D30" s="151"/>
       <c r="E30" s="151" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F30" s="151"/>
       <c r="G30" s="151"/>
-      <c r="H30" s="166">
+      <c r="H30" s="82">
         <f>4203.98+290.93+200.93</f>
         <v>4695.84</v>
       </c>
@@ -4736,11 +4707,11 @@
       <c r="C31" s="151"/>
       <c r="D31" s="151"/>
       <c r="E31" s="151" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F31" s="151"/>
       <c r="G31" s="151"/>
-      <c r="H31" s="166">
+      <c r="H31" s="82">
         <v>1073579.78</v>
       </c>
       <c r="I31" s="87"/>
@@ -4757,7 +4728,7 @@
       <c r="E32" s="151"/>
       <c r="F32" s="151"/>
       <c r="G32" s="151"/>
-      <c r="H32" s="166">
+      <c r="H32" s="82">
         <v>203720.4</v>
       </c>
     </row>
@@ -4777,16 +4748,16 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="193" t="s">
+      <c r="A34" s="184" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="193"/>
-      <c r="C34" s="193"/>
-      <c r="D34" s="193"/>
-      <c r="E34" s="193"/>
-      <c r="F34" s="193"/>
-      <c r="G34" s="193"/>
-      <c r="H34" s="193"/>
+      <c r="B34" s="184"/>
+      <c r="C34" s="184"/>
+      <c r="D34" s="184"/>
+      <c r="E34" s="184"/>
+      <c r="F34" s="184"/>
+      <c r="G34" s="184"/>
+      <c r="H34" s="184"/>
     </row>
     <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="85"/>
@@ -4808,13 +4779,13 @@
       <c r="E36" s="151"/>
       <c r="F36" s="151"/>
       <c r="G36" s="151"/>
-      <c r="H36" s="166">
+      <c r="H36" s="82">
         <v>140000</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="85" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B37" s="159"/>
       <c r="C37" s="85"/>
@@ -4822,28 +4793,28 @@
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="166">
+      <c r="H37" s="82">
         <v>40000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
     <row r="38" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="210" t="s">
-        <v>175</v>
-      </c>
-      <c r="B38" s="211"/>
-      <c r="C38" s="211"/>
-      <c r="D38" s="211"/>
-      <c r="E38" s="211"/>
-      <c r="F38" s="211"/>
-      <c r="G38" s="212"/>
-      <c r="H38" s="166">
+      <c r="A38" s="201" t="s">
+        <v>173</v>
+      </c>
+      <c r="B38" s="202"/>
+      <c r="C38" s="202"/>
+      <c r="D38" s="202"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="202"/>
+      <c r="G38" s="203"/>
+      <c r="H38" s="82">
         <v>32240.45</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="85" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B39" s="158"/>
       <c r="C39" s="151"/>
@@ -4851,30 +4822,30 @@
       <c r="E39" s="151"/>
       <c r="F39" s="151"/>
       <c r="G39" s="151"/>
-      <c r="H39" s="166">
+      <c r="H39" s="82">
         <v>101540</v>
       </c>
       <c r="I39" s="148"/>
-      <c r="J39" s="213"/>
+      <c r="J39" s="204"/>
     </row>
     <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="210" t="s">
-        <v>172</v>
-      </c>
-      <c r="B40" s="211"/>
-      <c r="C40" s="211"/>
-      <c r="D40" s="211"/>
-      <c r="E40" s="211"/>
-      <c r="F40" s="211"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="166">
+      <c r="A40" s="201" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="202"/>
+      <c r="C40" s="202"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="202"/>
+      <c r="F40" s="202"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="82">
         <v>741000</v>
       </c>
-      <c r="J40" s="213"/>
+      <c r="J40" s="204"/>
     </row>
     <row r="41" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="96" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B41" s="164"/>
       <c r="C41" s="164"/>
@@ -4882,10 +4853,10 @@
       <c r="E41" s="164"/>
       <c r="F41" s="164"/>
       <c r="G41" s="165"/>
-      <c r="H41" s="166">
+      <c r="H41" s="82">
         <v>36300</v>
       </c>
-      <c r="J41" s="213"/>
+      <c r="J41" s="204"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="151" t="s">
@@ -4903,16 +4874,16 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="193" t="s">
+      <c r="A43" s="184" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="193"/>
-      <c r="C43" s="193"/>
-      <c r="D43" s="193"/>
-      <c r="E43" s="193"/>
-      <c r="F43" s="193"/>
-      <c r="G43" s="193"/>
-      <c r="H43" s="193"/>
+      <c r="B43" s="184"/>
+      <c r="C43" s="184"/>
+      <c r="D43" s="184"/>
+      <c r="E43" s="184"/>
+      <c r="F43" s="184"/>
+      <c r="G43" s="184"/>
+      <c r="H43" s="184"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="151" t="s">
@@ -4920,17 +4891,17 @@
       </c>
       <c r="B44" s="151"/>
       <c r="C44" s="151" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D44" s="160"/>
       <c r="E44" s="151"/>
       <c r="F44" s="151"/>
       <c r="G44" s="151"/>
-      <c r="H44" s="166">
+      <c r="H44" s="82">
         <v>265000</v>
       </c>
       <c r="J44" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4938,12 +4909,12 @@
         <v>147</v>
       </c>
       <c r="B45" s="151"/>
-      <c r="C45" s="231"/>
-      <c r="D45" s="232"/>
+      <c r="C45" s="222"/>
+      <c r="D45" s="223"/>
       <c r="E45" s="162"/>
       <c r="F45" s="155"/>
       <c r="G45" s="151"/>
-      <c r="H45" s="166">
+      <c r="H45" s="82">
         <v>30000</v>
       </c>
     </row>
@@ -4973,16 +4944,16 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="204" t="s">
+      <c r="A48" s="195" t="s">
         <v>116</v>
       </c>
-      <c r="B48" s="205"/>
-      <c r="C48" s="205"/>
-      <c r="D48" s="205"/>
-      <c r="E48" s="205"/>
-      <c r="F48" s="205"/>
-      <c r="G48" s="205"/>
-      <c r="H48" s="206"/>
+      <c r="B48" s="196"/>
+      <c r="C48" s="196"/>
+      <c r="D48" s="196"/>
+      <c r="E48" s="196"/>
+      <c r="F48" s="196"/>
+      <c r="G48" s="196"/>
+      <c r="H48" s="197"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="151" t="s">
@@ -4994,8 +4965,8 @@
       <c r="E49" s="151"/>
       <c r="F49" s="151"/>
       <c r="G49" s="151"/>
-      <c r="H49" s="167">
-        <v>89235.14</v>
+      <c r="H49" s="82">
+        <v>60887.77</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -5020,20 +4991,20 @@
       <c r="G51" s="154"/>
       <c r="H51" s="157">
         <f>SUM(H49:H50)</f>
-        <v>89235.14</v>
+        <v>60887.77</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="204" t="s">
+      <c r="A52" s="195" t="s">
         <v>118</v>
       </c>
-      <c r="B52" s="205"/>
-      <c r="C52" s="205"/>
-      <c r="D52" s="205"/>
-      <c r="E52" s="205"/>
-      <c r="F52" s="205"/>
-      <c r="G52" s="205"/>
-      <c r="H52" s="206"/>
+      <c r="B52" s="196"/>
+      <c r="C52" s="196"/>
+      <c r="D52" s="196"/>
+      <c r="E52" s="196"/>
+      <c r="F52" s="196"/>
+      <c r="G52" s="196"/>
+      <c r="H52" s="197"/>
       <c r="I52" s="87"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -5045,10 +5016,10 @@
       <c r="D53" s="85"/>
       <c r="E53" s="85"/>
       <c r="F53" s="85" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G53" s="85"/>
-      <c r="H53" s="166">
+      <c r="H53" s="82">
         <v>55029.24</v>
       </c>
       <c r="I53" s="87"/>
@@ -5062,10 +5033,10 @@
       <c r="D54" s="85"/>
       <c r="E54" s="85"/>
       <c r="F54" s="85" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G54" s="85"/>
-      <c r="H54" s="166">
+      <c r="H54" s="82">
         <v>3498.02</v>
       </c>
       <c r="I54" s="87"/>
@@ -5088,16 +5059,16 @@
       <c r="K55" s="83"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="207" t="s">
+      <c r="A56" s="198" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="208"/>
-      <c r="C56" s="208"/>
-      <c r="D56" s="208"/>
-      <c r="E56" s="208"/>
-      <c r="F56" s="208"/>
-      <c r="G56" s="208"/>
-      <c r="H56" s="209"/>
+      <c r="B56" s="199"/>
+      <c r="C56" s="199"/>
+      <c r="D56" s="199"/>
+      <c r="E56" s="199"/>
+      <c r="F56" s="199"/>
+      <c r="G56" s="199"/>
+      <c r="H56" s="200"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="86"/>
@@ -5152,15 +5123,15 @@
       <c r="H61" s="92"/>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="207" t="s">
+      <c r="A62" s="198" t="s">
         <v>152</v>
       </c>
-      <c r="B62" s="208"/>
-      <c r="C62" s="208"/>
-      <c r="D62" s="208"/>
-      <c r="E62" s="208"/>
-      <c r="F62" s="208"/>
-      <c r="G62" s="208"/>
+      <c r="B62" s="199"/>
+      <c r="C62" s="199"/>
+      <c r="D62" s="199"/>
+      <c r="E62" s="199"/>
+      <c r="F62" s="199"/>
+      <c r="G62" s="199"/>
       <c r="H62" s="127"/>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5209,25 +5180,25 @@
       <c r="H66" s="92"/>
     </row>
     <row r="67" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A67" s="225" t="s">
+      <c r="A67" s="216" t="s">
         <v>120</v>
       </c>
-      <c r="B67" s="225"/>
-      <c r="C67" s="225"/>
-      <c r="D67" s="225"/>
-      <c r="E67" s="225"/>
-      <c r="F67" s="225"/>
-      <c r="G67" s="225"/>
+      <c r="B67" s="216"/>
+      <c r="C67" s="216"/>
+      <c r="D67" s="216"/>
+      <c r="E67" s="216"/>
+      <c r="F67" s="216"/>
+      <c r="G67" s="216"/>
       <c r="H67" s="95"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="210"/>
-      <c r="B68" s="211"/>
-      <c r="C68" s="211"/>
-      <c r="D68" s="211"/>
-      <c r="E68" s="211"/>
-      <c r="F68" s="211"/>
-      <c r="G68" s="212"/>
+      <c r="A68" s="201"/>
+      <c r="B68" s="202"/>
+      <c r="C68" s="202"/>
+      <c r="D68" s="202"/>
+      <c r="E68" s="202"/>
+      <c r="F68" s="202"/>
+      <c r="G68" s="203"/>
       <c r="H68" s="123"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -5241,13 +5212,13 @@
       <c r="H69" s="123"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="226"/>
-      <c r="B70" s="227"/>
-      <c r="C70" s="227"/>
-      <c r="D70" s="227"/>
-      <c r="E70" s="227"/>
-      <c r="F70" s="227"/>
-      <c r="G70" s="228"/>
+      <c r="A70" s="217"/>
+      <c r="B70" s="218"/>
+      <c r="C70" s="218"/>
+      <c r="D70" s="218"/>
+      <c r="E70" s="218"/>
+      <c r="F70" s="218"/>
+      <c r="G70" s="219"/>
       <c r="H70" s="82">
         <v>0</v>
       </c>
@@ -5303,15 +5274,15 @@
       <c r="I74" s="87"/>
     </row>
     <row r="75" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="229" t="s">
+      <c r="A75" s="220" t="s">
         <v>121</v>
       </c>
-      <c r="B75" s="230"/>
-      <c r="C75" s="230"/>
-      <c r="D75" s="230"/>
-      <c r="E75" s="230"/>
-      <c r="F75" s="230"/>
-      <c r="G75" s="230"/>
+      <c r="B75" s="221"/>
+      <c r="C75" s="221"/>
+      <c r="D75" s="221"/>
+      <c r="E75" s="221"/>
+      <c r="F75" s="221"/>
+      <c r="G75" s="221"/>
       <c r="H75" s="139">
         <f>H73</f>
         <v>0</v>
@@ -5319,106 +5290,113 @@
       <c r="I75" s="87"/>
     </row>
     <row r="76" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="222" t="s">
+      <c r="A76" s="213" t="s">
         <v>122</v>
       </c>
-      <c r="B76" s="223"/>
-      <c r="C76" s="223"/>
-      <c r="D76" s="223"/>
-      <c r="E76" s="223"/>
-      <c r="F76" s="223"/>
-      <c r="G76" s="224"/>
-      <c r="H76" s="139"/>
+      <c r="B76" s="214"/>
+      <c r="C76" s="214"/>
+      <c r="D76" s="214"/>
+      <c r="E76" s="214"/>
+      <c r="F76" s="214"/>
+      <c r="G76" s="215"/>
+      <c r="H76" s="139">
+        <f>J79-4553581.78+20000</f>
+        <v>466418.21999999974</v>
+      </c>
       <c r="I76" s="88"/>
     </row>
     <row r="77" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="233" t="s">
+      <c r="A77" s="224" t="s">
         <v>142</v>
       </c>
-      <c r="B77" s="234"/>
-      <c r="C77" s="234"/>
-      <c r="D77" s="234"/>
-      <c r="E77" s="234"/>
-      <c r="F77" s="234"/>
-      <c r="G77" s="235"/>
+      <c r="B77" s="225"/>
+      <c r="C77" s="225"/>
+      <c r="D77" s="225"/>
+      <c r="E77" s="225"/>
+      <c r="F77" s="225"/>
+      <c r="G77" s="226"/>
       <c r="H77" s="139"/>
       <c r="I77" s="87"/>
       <c r="J77" s="83"/>
     </row>
     <row r="78" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A78" s="229" t="s">
+      <c r="A78" s="220" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="230"/>
-      <c r="C78" s="230"/>
-      <c r="D78" s="230"/>
-      <c r="E78" s="230"/>
-      <c r="F78" s="230"/>
-      <c r="G78" s="230"/>
+      <c r="B78" s="221"/>
+      <c r="C78" s="221"/>
+      <c r="D78" s="221"/>
+      <c r="E78" s="221"/>
+      <c r="F78" s="221"/>
+      <c r="G78" s="221"/>
       <c r="H78" s="139">
         <f>H59+H55+H51+H47+H42+H33+H16+H21+H28+H65</f>
-        <v>4561929.1500000004</v>
+        <v>4533581.78</v>
       </c>
       <c r="I78" s="83"/>
     </row>
     <row r="79" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A79" s="236" t="s">
+      <c r="A79" s="227" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="237"/>
-      <c r="C79" s="237"/>
-      <c r="D79" s="237"/>
-      <c r="E79" s="237"/>
-      <c r="F79" s="237"/>
-      <c r="G79" s="238"/>
+      <c r="B79" s="228"/>
+      <c r="C79" s="228"/>
+      <c r="D79" s="228"/>
+      <c r="E79" s="228"/>
+      <c r="F79" s="228"/>
+      <c r="G79" s="229"/>
       <c r="H79" s="140">
         <f>H78+H76</f>
-        <v>4561929.1500000004</v>
+        <v>5000000</v>
       </c>
       <c r="I79" s="83"/>
+      <c r="J79">
+        <v>5000000</v>
+      </c>
       <c r="K79" s="148"/>
     </row>
     <row r="80" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A80" s="236" t="s">
+      <c r="A80" s="227" t="s">
         <v>125</v>
       </c>
-      <c r="B80" s="237"/>
-      <c r="C80" s="237"/>
-      <c r="D80" s="237"/>
-      <c r="E80" s="237"/>
-      <c r="F80" s="237"/>
-      <c r="G80" s="238"/>
+      <c r="B80" s="228"/>
+      <c r="C80" s="228"/>
+      <c r="D80" s="228"/>
+      <c r="E80" s="228"/>
+      <c r="F80" s="228"/>
+      <c r="G80" s="229"/>
       <c r="H80" s="141">
         <f>H75+H77</f>
         <v>0</v>
       </c>
       <c r="I80" s="83"/>
+      <c r="J80" s="148"/>
     </row>
     <row r="81" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="183" t="s">
+      <c r="A81" s="180" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="184"/>
-      <c r="C81" s="184"/>
-      <c r="D81" s="184"/>
-      <c r="E81" s="184"/>
-      <c r="F81" s="184"/>
-      <c r="G81" s="184"/>
+      <c r="B81" s="181"/>
+      <c r="C81" s="181"/>
+      <c r="D81" s="181"/>
+      <c r="E81" s="181"/>
+      <c r="F81" s="181"/>
+      <c r="G81" s="181"/>
       <c r="H81" s="142">
         <f>H78+H75</f>
-        <v>4561929.1500000004</v>
+        <v>4533581.78</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="185" t="s">
+      <c r="A82" s="182" t="s">
         <v>127</v>
       </c>
-      <c r="B82" s="186"/>
-      <c r="C82" s="186"/>
-      <c r="D82" s="186"/>
-      <c r="E82" s="186"/>
-      <c r="F82" s="186"/>
-      <c r="G82" s="186"/>
+      <c r="B82" s="183"/>
+      <c r="C82" s="183"/>
+      <c r="D82" s="183"/>
+      <c r="E82" s="183"/>
+      <c r="F82" s="183"/>
+      <c r="G82" s="183"/>
       <c r="H82" s="100">
         <v>0</v>
       </c>
@@ -5433,82 +5411,90 @@
       <c r="G83" s="101"/>
       <c r="H83" s="102"/>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="187" t="s">
-        <v>161</v>
-      </c>
-      <c r="B84" s="188"/>
-      <c r="C84" s="188"/>
-      <c r="D84" s="188"/>
-      <c r="E84" s="188"/>
-      <c r="F84" s="188"/>
-      <c r="G84" s="188"/>
-      <c r="H84" s="189"/>
-    </row>
-    <row r="85" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="190"/>
-      <c r="B85" s="191"/>
-      <c r="C85" s="191"/>
-      <c r="D85" s="191"/>
-      <c r="E85" s="191"/>
-      <c r="F85" s="191"/>
-      <c r="G85" s="191"/>
-      <c r="H85" s="192"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-    </row>
-    <row r="87" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A87" s="214" t="s">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+    </row>
+    <row r="85" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A85" s="205" t="s">
         <v>128</v>
       </c>
-      <c r="B87" s="215"/>
-      <c r="C87" s="215"/>
-      <c r="D87" s="215"/>
-      <c r="E87" s="215"/>
-      <c r="F87" s="215"/>
-      <c r="G87" s="215"/>
-      <c r="H87" s="216"/>
-    </row>
-    <row r="88" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A88" s="103" t="s">
+      <c r="B85" s="206"/>
+      <c r="C85" s="206"/>
+      <c r="D85" s="206"/>
+      <c r="E85" s="206"/>
+      <c r="F85" s="206"/>
+      <c r="G85" s="206"/>
+      <c r="H85" s="207"/>
+    </row>
+    <row r="86" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A86" s="103" t="s">
         <v>129</v>
       </c>
-      <c r="B88" s="104"/>
-      <c r="C88" s="104"/>
-      <c r="D88" s="104"/>
-      <c r="E88" s="104"/>
-      <c r="F88" s="104"/>
-      <c r="G88" s="104"/>
-      <c r="H88" s="105">
+      <c r="B86" s="104"/>
+      <c r="C86" s="104"/>
+      <c r="D86" s="104"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="104"/>
+      <c r="G86" s="104"/>
+      <c r="H86" s="105">
         <v>-834604.30226353183</v>
       </c>
     </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="106"/>
+      <c r="C87" s="106"/>
+      <c r="D87" s="106"/>
+      <c r="E87" s="106"/>
+      <c r="F87" s="106"/>
+      <c r="G87" s="106"/>
+      <c r="H87" s="18">
+        <f>Planilla!G43</f>
+        <v>5380591.9416700006</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="107" t="s">
+        <v>136</v>
+      </c>
+      <c r="B88" s="108"/>
+      <c r="C88" s="108"/>
+      <c r="D88" s="108"/>
+      <c r="E88" s="108"/>
+      <c r="F88" s="108"/>
+      <c r="G88" s="108"/>
+      <c r="H88" s="122">
+        <f>-H81</f>
+        <v>-4533581.78</v>
+      </c>
+    </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B89" s="106"/>
-      <c r="C89" s="106"/>
-      <c r="D89" s="106"/>
-      <c r="E89" s="106"/>
-      <c r="F89" s="106"/>
-      <c r="G89" s="106"/>
-      <c r="H89" s="18">
-        <f>Planilla!G43</f>
-        <v>4798692.9416700006</v>
+      <c r="A89" s="107" t="s">
+        <v>131</v>
+      </c>
+      <c r="B89" s="108"/>
+      <c r="C89" s="108"/>
+      <c r="D89" s="108"/>
+      <c r="E89" s="108"/>
+      <c r="F89" s="108"/>
+      <c r="G89" s="108"/>
+      <c r="H89" s="31">
+        <f>D104</f>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="107" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="B90" s="108"/>
       <c r="C90" s="108"/>
@@ -5517,101 +5503,91 @@
       <c r="F90" s="108"/>
       <c r="G90" s="108"/>
       <c r="H90" s="122">
-        <f>-H81</f>
-        <v>-4561929.1500000004</v>
+        <f>-(3244+6707+6908+7115)</f>
+        <v>-23974</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="107" t="s">
-        <v>131</v>
-      </c>
-      <c r="B91" s="108"/>
+        <v>153</v>
+      </c>
+      <c r="B91" s="109"/>
       <c r="C91" s="108"/>
       <c r="D91" s="108"/>
       <c r="E91" s="108"/>
       <c r="F91" s="108"/>
       <c r="G91" s="108"/>
-      <c r="H91" s="31">
-        <f>D106</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="107" t="s">
-        <v>177</v>
-      </c>
-      <c r="B92" s="108"/>
-      <c r="C92" s="108"/>
-      <c r="D92" s="108"/>
-      <c r="E92" s="108"/>
-      <c r="F92" s="108"/>
-      <c r="G92" s="108"/>
-      <c r="H92" s="122">
-        <f>-(3244+6707+6908+7115)</f>
-        <v>-23974</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="107" t="s">
-        <v>153</v>
-      </c>
-      <c r="B93" s="109"/>
-      <c r="C93" s="108"/>
-      <c r="D93" s="108"/>
-      <c r="E93" s="108"/>
-      <c r="F93" s="108"/>
-      <c r="G93" s="108"/>
-      <c r="H93" s="130">
+      <c r="H91" s="130">
         <f>-H65</f>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A94" s="110" t="s">
+    <row r="92" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A92" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="B94" s="111"/>
-      <c r="C94" s="111"/>
-      <c r="D94" s="111"/>
-      <c r="E94" s="111"/>
-      <c r="F94" s="111"/>
-      <c r="G94" s="111"/>
-      <c r="H94" s="112">
-        <f>SUM(H88:H93)</f>
-        <v>-621814.51059353165</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="217" t="s">
+      <c r="B92" s="111"/>
+      <c r="C92" s="111"/>
+      <c r="D92" s="111"/>
+      <c r="E92" s="111"/>
+      <c r="F92" s="111"/>
+      <c r="G92" s="111"/>
+      <c r="H92" s="112">
+        <f>SUM(H86:H91)</f>
+        <v>-11568.140593531542</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="208" t="s">
         <v>133</v>
       </c>
-      <c r="B96" s="218"/>
-      <c r="C96" s="218"/>
-      <c r="D96" s="218"/>
-      <c r="E96" s="218"/>
-      <c r="F96" s="218"/>
-      <c r="G96" s="218"/>
-      <c r="H96" s="219"/>
-    </row>
-    <row r="97" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="113" t="s">
+      <c r="B94" s="209"/>
+      <c r="C94" s="209"/>
+      <c r="D94" s="209"/>
+      <c r="E94" s="209"/>
+      <c r="F94" s="209"/>
+      <c r="G94" s="209"/>
+      <c r="H94" s="210"/>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="B97" s="113"/>
-      <c r="C97" s="113"/>
-      <c r="D97" s="113"/>
-      <c r="E97" s="113"/>
-      <c r="F97" s="113"/>
-      <c r="G97" s="113"/>
-      <c r="H97" s="114">
-        <v>0</v>
-      </c>
+      <c r="B95" s="113"/>
+      <c r="C95" s="113"/>
+      <c r="D95" s="113"/>
+      <c r="E95" s="113"/>
+      <c r="F95" s="113"/>
+      <c r="G95" s="113"/>
+      <c r="H95" s="114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="6"/>
+      <c r="B96" s="115"/>
+      <c r="C96" s="108"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="18"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="6"/>
+      <c r="B97" s="116"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="18"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
-      <c r="B98" s="115"/>
-      <c r="C98" s="108"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -5619,120 +5595,99 @@
       <c r="H98" s="18"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="6"/>
-      <c r="B99" s="116"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="18"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="18"/>
+      <c r="A99" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="B99" s="117"/>
+      <c r="C99" s="117"/>
+      <c r="D99" s="117"/>
+      <c r="E99" s="117"/>
+      <c r="F99" s="117"/>
+      <c r="G99" s="117"/>
+      <c r="H99" s="118">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="117" t="s">
-        <v>132</v>
-      </c>
-      <c r="B101" s="117"/>
-      <c r="C101" s="117"/>
-      <c r="D101" s="117"/>
-      <c r="E101" s="117"/>
-      <c r="F101" s="117"/>
-      <c r="G101" s="117"/>
-      <c r="H101" s="118">
-        <v>0</v>
-      </c>
+      <c r="A101" s="124" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" s="125"/>
+      <c r="C101" s="125"/>
+      <c r="D101" s="125"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="18"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="B103" s="125"/>
-      <c r="C103" s="125"/>
-      <c r="D103" s="125"/>
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="18"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="18"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="18"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="119" t="s">
+      <c r="A104" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="B106" s="125"/>
-      <c r="C106" s="125"/>
-      <c r="D106" s="135">
-        <f>SUM(D104:D105)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="124" t="s">
+      <c r="B104" s="125"/>
+      <c r="C104" s="125"/>
+      <c r="D104" s="135">
+        <f>SUM(D102:D103)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="B108" s="119"/>
-      <c r="C108" s="119"/>
-      <c r="D108" s="119"/>
+      <c r="B106" s="119"/>
+      <c r="C106" s="119"/>
+      <c r="D106" s="119"/>
+    </row>
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="6"/>
+      <c r="B107" s="99"/>
+      <c r="C107" s="99"/>
+      <c r="D107" s="121"/>
+    </row>
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="126"/>
     </row>
     <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
-      <c r="B109" s="99"/>
-      <c r="C109" s="99"/>
-      <c r="D109" s="121"/>
-    </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="126"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
       <c r="D110" s="126"/>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="126"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="126"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="120" t="s">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="B113" s="120"/>
-      <c r="C113" s="220">
-        <f>SUM(D109:D112)</f>
-        <v>0</v>
-      </c>
-      <c r="D113" s="221"/>
+      <c r="B111" s="120"/>
+      <c r="C111" s="211">
+        <f>SUM(D107:D110)</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="212"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A38:G38"/>
+  <mergeCells count="31">
     <mergeCell ref="J39:J41"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A96:H96"/>
-    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="C111:D111"/>
     <mergeCell ref="A76:G76"/>
     <mergeCell ref="A67:G67"/>
     <mergeCell ref="A68:G68"/>
@@ -5746,7 +5701,6 @@
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A84:H85"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="E3:H3"/>
@@ -5760,6 +5714,7 @@
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
